--- a/samples/TSLA-2026-03-10/TSLA-financial-model.xlsx
+++ b/samples/TSLA-2026-03-10/TSLA-financial-model.xlsx
@@ -2358,23 +2358,24 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="15">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0\x"/>
-    <numFmt numFmtId="169" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
-    <numFmt numFmtId="172" formatCode="0.0000"/>
-    <numFmt numFmtId="173" formatCode="0.00"/>
-    <numFmt numFmtId="174" formatCode="\$#,##0"/>
-    <numFmt numFmtId="175" formatCode="\$#,##0.0;&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="176" formatCode="0%"/>
-    <numFmt numFmtId="177" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="0.0\x"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0"/>
+    <numFmt numFmtId="171" formatCode="\$#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0.0"/>
+    <numFmt numFmtId="173" formatCode="0.0"/>
+    <numFmt numFmtId="174" formatCode="0.0000"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0.0;&quot;($&quot;#,##0.0\);\-"/>
+    <numFmt numFmtId="177" formatCode="0%"/>
+    <numFmt numFmtId="178" formatCode="0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2500,6 +2501,14 @@
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2688,7 +2697,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E75B6"/>
-        <bgColor rgb="FF0066CC"/>
+        <bgColor rgb="FF4472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -2773,7 +2782,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="109">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2854,11 +2863,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2890,7 +2911,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2906,7 +2927,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2914,15 +2935,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2930,7 +2951,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2938,7 +2959,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2946,11 +2967,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2958,7 +2983,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2970,7 +2995,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2982,7 +3007,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2990,7 +3015,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2998,23 +3031,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3026,23 +3047,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="28" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3050,7 +3075,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3066,7 +3091,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3082,11 +3107,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3094,15 +3115,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3110,7 +3131,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3122,11 +3147,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3134,39 +3159,39 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="32" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="11" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3174,15 +3199,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="33" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="34" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3190,7 +3215,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3220,14 +3245,14 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF006600"/>
       <rgbColor rgb="FFB0B0B0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF5B9BD5"/>
+      <rgbColor rgb="FFA5A5A5"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFD6E4F0"/>
       <rgbColor rgb="FF4A1A6B"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF2E75B6"/>
       <rgbColor rgb="FFE8D5F5"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -3245,16 +3270,16 @@
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFCE4EC"/>
-      <rgbColor rgb="FF2E75B6"/>
+      <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFCC6600"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF6A3D9A"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -3444,9 +3469,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B3:C36"/>
+  <dimension ref="B1:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3454,18 +3480,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
   </cols>
   <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="2"/>
     </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="3"/>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3514,6 +3545,8 @@
         <v>13</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -3623,6 +3656,8 @@
         <v>40</v>
       </c>
     </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
         <v>41</v>
@@ -3676,6 +3711,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFA5A5A5"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I14"/>
@@ -3690,6 +3726,7 @@
         <v>235</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>236</v>
@@ -3720,22 +3757,22 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="51" t="s">
         <v>245</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="52" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="19" t="n">
         <v>1280</v>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="E4" s="20" t="n">
+      <c r="E4" s="22" t="n">
         <v>65</v>
       </c>
-      <c r="F4" s="20" t="n">
+      <c r="F4" s="22" t="n">
         <v>166</v>
       </c>
       <c r="G4" s="15" t="n">
@@ -3755,25 +3792,25 @@
       <c r="B5" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C5" s="37" t="n">
         <v>110</v>
       </c>
-      <c r="D5" s="49" t="n">
+      <c r="D5" s="53" t="n">
         <v>0.9</v>
       </c>
-      <c r="E5" s="49" t="n">
+      <c r="E5" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="53" t="n">
         <v>22</v>
       </c>
-      <c r="G5" s="50" t="n">
+      <c r="G5" s="54" t="n">
         <v>0.3</v>
       </c>
-      <c r="H5" s="50" t="n">
+      <c r="H5" s="54" t="n">
         <v>0.2</v>
       </c>
-      <c r="I5" s="50" t="n">
+      <c r="I5" s="54" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -3784,25 +3821,25 @@
       <c r="B6" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="37" t="n">
         <v>18</v>
       </c>
-      <c r="D6" s="49" t="n">
+      <c r="D6" s="53" t="n">
         <v>1.2</v>
       </c>
-      <c r="E6" s="49" t="n">
+      <c r="E6" s="53" t="n">
         <v>-15</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="53" t="n">
         <v>-10</v>
       </c>
-      <c r="G6" s="50" t="n">
+      <c r="G6" s="54" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="50" t="n">
+      <c r="H6" s="54" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I6" s="50" t="n">
+      <c r="I6" s="54" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -3813,25 +3850,25 @@
       <c r="B7" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C7" s="34" t="n">
+      <c r="C7" s="37" t="n">
         <v>12</v>
       </c>
-      <c r="D7" s="49" t="n">
+      <c r="D7" s="53" t="n">
         <v>1.5</v>
       </c>
-      <c r="E7" s="49" t="n">
+      <c r="E7" s="53" t="n">
         <v>-20</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="53" t="n">
         <v>-8</v>
       </c>
-      <c r="G7" s="50" t="n">
+      <c r="G7" s="54" t="n">
         <v>0.25</v>
       </c>
-      <c r="H7" s="50" t="n">
+      <c r="H7" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="I7" s="50" t="n">
+      <c r="I7" s="54" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3842,25 +3879,25 @@
       <c r="B8" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="C8" s="34" t="n">
+      <c r="C8" s="37" t="n">
         <v>280</v>
       </c>
-      <c r="D8" s="49" t="n">
+      <c r="D8" s="53" t="n">
         <v>0.9</v>
       </c>
-      <c r="E8" s="49" t="n">
+      <c r="E8" s="53" t="n">
         <v>8</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="50" t="n">
+      <c r="G8" s="54" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="50" t="n">
+      <c r="H8" s="54" t="n">
         <v>0.185</v>
       </c>
-      <c r="I8" s="50" t="n">
+      <c r="I8" s="54" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3871,25 +3908,25 @@
       <c r="B9" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="34" t="n">
+      <c r="C9" s="37" t="n">
         <v>65</v>
       </c>
-      <c r="D9" s="49" t="n">
+      <c r="D9" s="53" t="n">
         <v>0.2</v>
       </c>
-      <c r="E9" s="49" t="n">
+      <c r="E9" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="53" t="n">
         <v>4.5</v>
       </c>
-      <c r="G9" s="50" t="n">
+      <c r="G9" s="54" t="n">
         <v>0.03</v>
       </c>
-      <c r="H9" s="50" t="n">
+      <c r="H9" s="54" t="n">
         <v>0.17</v>
       </c>
-      <c r="I9" s="50" t="n">
+      <c r="I9" s="54" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3900,25 +3937,25 @@
       <c r="B10" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="C10" s="34" t="n">
+      <c r="C10" s="37" t="n">
         <v>55</v>
       </c>
-      <c r="D10" s="49" t="n">
+      <c r="D10" s="53" t="n">
         <v>0.3</v>
       </c>
-      <c r="E10" s="49" t="n">
+      <c r="E10" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="50" t="n">
+      <c r="G10" s="54" t="n">
         <v>0.02</v>
       </c>
-      <c r="H10" s="50" t="n">
+      <c r="H10" s="54" t="n">
         <v>0.155</v>
       </c>
-      <c r="I10" s="50" t="n">
+      <c r="I10" s="54" t="n">
         <v>0.07</v>
       </c>
     </row>
@@ -3929,57 +3966,58 @@
       <c r="B11" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="C11" s="34" t="n">
+      <c r="C11" s="37" t="n">
         <v>40</v>
       </c>
-      <c r="D11" s="49" t="n">
+      <c r="D11" s="53" t="n">
         <v>0.2</v>
       </c>
-      <c r="E11" s="49" t="n">
+      <c r="E11" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="50" t="n">
+      <c r="G11" s="54" t="n">
         <v>0.01</v>
       </c>
-      <c r="H11" s="50" t="n">
+      <c r="H11" s="54" t="n">
         <v>0.12</v>
       </c>
-      <c r="I11" s="50" t="n">
+      <c r="I11" s="54" t="n">
         <v>0.04</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="51" t="n">
+      <c r="C13" s="55" t="n">
         <f aca="false">MEDIAN(C5:C11)</f>
         <v>55</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="56" t="n">
         <f aca="false">MEDIAN(D5:D11)</f>
         <v>0.9</v>
       </c>
-      <c r="E13" s="52" t="n">
+      <c r="E13" s="56" t="n">
         <f aca="false">MEDIAN(E5:E11)</f>
         <v>5</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="56" t="n">
         <f aca="false">MEDIAN(F5:F11)</f>
         <v>6</v>
       </c>
-      <c r="G13" s="38" t="n">
+      <c r="G13" s="41" t="n">
         <f aca="false">MEDIAN(G5:G11)</f>
         <v>0.05</v>
       </c>
-      <c r="H13" s="38" t="n">
+      <c r="H13" s="41" t="n">
         <f aca="false">MEDIAN(H5:H11)</f>
         <v>0.155</v>
       </c>
-      <c r="I13" s="38" t="n">
+      <c r="I13" s="41" t="n">
         <f aca="false">MEDIAN(I5:I11)</f>
         <v>0.04</v>
       </c>
@@ -3988,32 +4026,32 @@
       <c r="A14" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C14" s="53" t="n">
-        <f aca="false">(C4-C13)/C13</f>
+      <c r="C14" s="57" t="n">
+        <f aca="false">IFERROR((C4-C13)/C13,0)</f>
         <v>22.2727272727273</v>
       </c>
-      <c r="D14" s="53" t="n">
-        <f aca="false">(D4-D13)/D13</f>
+      <c r="D14" s="57" t="n">
+        <f aca="false">IFERROR((D4-D13)/D13,0)</f>
         <v>12.3333333333333</v>
       </c>
-      <c r="E14" s="53" t="n">
-        <f aca="false">(E4-E13)/E13</f>
+      <c r="E14" s="57" t="n">
+        <f aca="false">IFERROR((E4-E13)/E13,0)</f>
         <v>12</v>
       </c>
-      <c r="F14" s="53" t="n">
-        <f aca="false">(F4-F13)/F13</f>
+      <c r="F14" s="57" t="n">
+        <f aca="false">IFERROR((F4-F13)/F13,0)</f>
         <v>26.6666666666667</v>
       </c>
-      <c r="G14" s="53" t="n">
-        <f aca="false">(G4-G13)/G13</f>
+      <c r="G14" s="57" t="n">
+        <f aca="false">IFERROR((G4-G13)/G13,0)</f>
         <v>2</v>
       </c>
-      <c r="H14" s="53" t="n">
-        <f aca="false">(H4-H13)/H13</f>
+      <c r="H14" s="57" t="n">
+        <f aca="false">IFERROR((H4-H13)/H13,0)</f>
         <v>0.174193548387097</v>
       </c>
-      <c r="I14" s="53" t="n">
-        <f aca="false">(I4-I13)/I13</f>
+      <c r="I14" s="57" t="n">
+        <f aca="false">IFERROR((I4-I13)/I13,0)</f>
         <v>-0.925</v>
       </c>
     </row>
@@ -4031,9 +4069,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF70AD47"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4050,6 +4089,7 @@
         <v>260</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>261</v>
@@ -4077,10 +4117,10 @@
       <c r="B4" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="54" t="n">
+      <c r="C4" s="58" t="n">
         <v>6.5</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -4097,10 +4137,10 @@
       <c r="B5" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="54" t="n">
+      <c r="C5" s="58" t="n">
         <v>6.5</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -4117,10 +4157,10 @@
       <c r="B6" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C6" s="54" t="n">
+      <c r="C6" s="58" t="n">
         <v>6.5</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -4137,10 +4177,10 @@
       <c r="B7" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="56" t="n">
+      <c r="C7" s="60" t="n">
         <v>7.5</v>
       </c>
-      <c r="D7" s="57" t="s">
+      <c r="D7" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -4157,10 +4197,10 @@
       <c r="B8" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="54" t="n">
+      <c r="C8" s="58" t="n">
         <v>6.5</v>
       </c>
-      <c r="D8" s="57" t="s">
+      <c r="D8" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -4177,10 +4217,10 @@
       <c r="B9" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="56" t="n">
+      <c r="C9" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -4197,10 +4237,10 @@
       <c r="B10" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C10" s="56" t="n">
+      <c r="C10" s="60" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="62" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -4217,10 +4257,10 @@
       <c r="B11" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="54" t="n">
+      <c r="C11" s="58" t="n">
         <v>6.8</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -4237,10 +4277,10 @@
       <c r="B12" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C12" s="56" t="n">
+      <c r="C12" s="60" t="n">
         <v>7.8</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -4257,10 +4297,10 @@
       <c r="B13" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="54" t="n">
+      <c r="C13" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="57" t="s">
+      <c r="D13" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -4277,10 +4317,10 @@
       <c r="B14" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="54" t="n">
+      <c r="C14" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="57" t="s">
+      <c r="D14" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -4297,10 +4337,10 @@
       <c r="B15" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C15" s="54" t="n">
+      <c r="C15" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="55" t="s">
+      <c r="D15" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -4317,10 +4357,10 @@
       <c r="B16" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C16" s="54" t="n">
+      <c r="C16" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -4337,10 +4377,10 @@
       <c r="B17" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="54" t="n">
+      <c r="C17" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="55" t="s">
+      <c r="D17" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -4357,10 +4397,10 @@
       <c r="B18" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C18" s="54" t="n">
+      <c r="C18" s="58" t="n">
         <v>6.5</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="61" t="s">
         <v>278</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -4377,10 +4417,10 @@
       <c r="B19" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="54" t="n">
+      <c r="C19" s="58" t="n">
         <v>6.8</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="59" t="s">
         <v>268</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -4390,15 +4430,19 @@
         <v>316</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="C21" s="59" t="n">
+      <c r="C21" s="63" t="n">
         <f aca="false">AVERAGE(C4:C20)</f>
         <v>6.5875</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4413,6 +4457,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFFFC000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F11"/>
@@ -4429,6 +4474,7 @@
         <v>318</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>319</v>
@@ -4456,13 +4502,13 @@
       <c r="B4" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="50" t="n">
+      <c r="E4" s="54" t="n">
         <v>0.6</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -4476,13 +4522,13 @@
       <c r="B5" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="54" t="n">
         <v>0.95</v>
       </c>
       <c r="F5" s="11" t="s">
@@ -4496,13 +4542,13 @@
       <c r="B6" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="50" t="n">
+      <c r="E6" s="54" t="n">
         <v>0.65</v>
       </c>
       <c r="F6" s="11" t="s">
@@ -4516,13 +4562,13 @@
       <c r="B7" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="65" t="s">
         <v>335</v>
       </c>
-      <c r="E7" s="50" t="n">
+      <c r="E7" s="54" t="n">
         <v>0.42</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -4536,13 +4582,13 @@
       <c r="B8" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="65" t="s">
         <v>335</v>
       </c>
-      <c r="E8" s="50" t="n">
+      <c r="E8" s="54" t="n">
         <v>0.35</v>
       </c>
       <c r="F8" s="11" t="s">
@@ -4556,13 +4602,13 @@
       <c r="B9" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="64" t="s">
         <v>268</v>
       </c>
-      <c r="E9" s="50" t="n">
+      <c r="E9" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="F9" s="11" t="s">
@@ -4576,13 +4622,13 @@
       <c r="B10" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="61" t="s">
         <v>275</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="66" t="s">
         <v>344</v>
       </c>
-      <c r="E10" s="50" t="n">
+      <c r="E10" s="54" t="n">
         <v>0.4</v>
       </c>
       <c r="F10" s="11" t="s">
@@ -4596,13 +4642,13 @@
       <c r="B11" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="66" t="s">
         <v>344</v>
       </c>
-      <c r="E11" s="50" t="n">
+      <c r="E11" s="54" t="n">
         <v>0.7</v>
       </c>
       <c r="F11" s="11" t="s">
@@ -4623,6 +4669,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D14"/>
@@ -4638,6 +4685,7 @@
         <v>349</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>350</v>
@@ -4679,7 +4727,7 @@
       <c r="A6" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="B6" s="63" t="n">
+      <c r="B6" s="67" t="n">
         <v>2.8</v>
       </c>
       <c r="C6" s="11"/>
@@ -4692,7 +4740,7 @@
         <v>358</v>
       </c>
       <c r="B7" s="18" t="n">
-        <f aca="false">(B4*B6-B5)/B6</f>
+        <f aca="false">IFERROR((B4*B6-B5)/B6,0)</f>
         <v>0.525</v>
       </c>
       <c r="C7" s="11"/>
@@ -4705,7 +4753,7 @@
         <v>360</v>
       </c>
       <c r="B8" s="18" t="n">
-        <f aca="false">B7/2</f>
+        <f aca="false">IFERROR(B7/2,0)</f>
         <v>0.2625</v>
       </c>
       <c r="C8" s="11"/>
@@ -4713,11 +4761,12 @@
         <v>361</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="B10" s="64" t="n">
+      <c r="B10" s="68" t="n">
         <v>1000000</v>
       </c>
       <c r="C10" s="11"/>
@@ -4729,7 +4778,7 @@
       <c r="A11" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="B11" s="65" t="n">
+      <c r="B11" s="69" t="n">
         <f aca="false">B10*B8</f>
         <v>262500</v>
       </c>
@@ -4742,8 +4791,8 @@
       <c r="A12" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="B12" s="40" t="n">
-        <f aca="false">B11/Assumptions!E29</f>
+      <c r="B12" s="43" t="n">
+        <f aca="false">IFERROR(B11/Assumptions!E29,0)</f>
         <v>8750000</v>
       </c>
       <c r="C12" s="11"/>
@@ -4751,6 +4800,7 @@
         <v>367</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
         <v>368</v>
@@ -4794,2371 +4844,2382 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="70" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="66"/>
-      <c r="C1" s="66"/>
-      <c r="D1" s="66"/>
-      <c r="E1" s="66"/>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="67" t="s">
+      <c r="A2" s="71" t="s">
         <v>371</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="72" t="s">
         <v>372</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-    </row>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="69" t="s">
+      <c r="A5" s="73" t="s">
         <v>373</v>
       </c>
-      <c r="B5" s="69"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69"/>
-      <c r="I5" s="69"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="74" t="s">
         <v>374</v>
       </c>
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="74" t="s">
         <v>375</v>
       </c>
-      <c r="C6" s="70" t="s">
+      <c r="C6" s="74" t="s">
         <v>376</v>
       </c>
-      <c r="D6" s="70" t="s">
+      <c r="D6" s="74" t="s">
         <v>377</v>
       </c>
-      <c r="E6" s="70" t="s">
+      <c r="E6" s="74" t="s">
         <v>378</v>
       </c>
-      <c r="F6" s="70" t="s">
+      <c r="F6" s="74" t="s">
         <v>264</v>
       </c>
-      <c r="G6" s="70" t="s">
+      <c r="G6" s="74" t="s">
         <v>379</v>
       </c>
-      <c r="H6" s="70" t="s">
+      <c r="H6" s="74" t="s">
         <v>380</v>
       </c>
-      <c r="I6" s="70" t="s">
+      <c r="I6" s="74" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="75" t="s">
         <v>382</v>
       </c>
-      <c r="B7" s="72" t="s">
+      <c r="B7" s="76" t="s">
         <v>383</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="76" t="s">
         <v>384</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="76" t="s">
         <v>385</v>
       </c>
-      <c r="E7" s="73" t="s">
+      <c r="E7" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G7" s="74" t="s">
+      <c r="G7" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H7" s="72" t="s">
+      <c r="H7" s="76" t="s">
         <v>388</v>
       </c>
-      <c r="I7" s="72" t="s">
+      <c r="I7" s="76" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="79" t="s">
         <v>382</v>
       </c>
-      <c r="B8" s="76" t="s">
+      <c r="B8" s="80" t="s">
         <v>390</v>
       </c>
-      <c r="C8" s="76" t="s">
+      <c r="C8" s="80" t="s">
         <v>391</v>
       </c>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="80" t="s">
         <v>392</v>
       </c>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F8" s="76" t="s">
+      <c r="F8" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H8" s="76" t="s">
+      <c r="H8" s="80" t="s">
         <v>393</v>
       </c>
-      <c r="I8" s="76" t="s">
+      <c r="I8" s="80" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="75" t="s">
         <v>382</v>
       </c>
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="76" t="s">
         <v>395</v>
       </c>
-      <c r="C9" s="72" t="s">
+      <c r="C9" s="76" t="s">
         <v>396</v>
       </c>
-      <c r="D9" s="72" t="s">
+      <c r="D9" s="76" t="s">
         <v>397</v>
       </c>
-      <c r="E9" s="73" t="s">
+      <c r="E9" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G9" s="74" t="s">
+      <c r="G9" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H9" s="72" t="s">
+      <c r="H9" s="76" t="s">
         <v>398</v>
       </c>
-      <c r="I9" s="72" t="s">
+      <c r="I9" s="76" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="75" t="s">
+      <c r="A10" s="79" t="s">
         <v>400</v>
       </c>
-      <c r="B10" s="76" t="s">
+      <c r="B10" s="80" t="s">
         <v>401</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="80" t="s">
         <v>402</v>
       </c>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="80" t="s">
         <v>403</v>
       </c>
-      <c r="E10" s="77" t="s">
+      <c r="E10" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F10" s="76" t="s">
+      <c r="F10" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H10" s="76" t="s">
+      <c r="H10" s="80" t="s">
         <v>404</v>
       </c>
-      <c r="I10" s="76" t="s">
+      <c r="I10" s="80" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="75" t="s">
         <v>400</v>
       </c>
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="76" t="s">
         <v>406</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="76" t="s">
         <v>407</v>
       </c>
-      <c r="D11" s="72" t="s">
+      <c r="D11" s="76" t="s">
         <v>408</v>
       </c>
-      <c r="E11" s="73" t="s">
+      <c r="E11" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G11" s="74" t="s">
+      <c r="G11" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H11" s="72" t="s">
+      <c r="H11" s="76" t="s">
         <v>409</v>
       </c>
-      <c r="I11" s="72" t="s">
+      <c r="I11" s="76" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="79" t="s">
         <v>400</v>
       </c>
-      <c r="B12" s="76" t="s">
+      <c r="B12" s="80" t="s">
         <v>411</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="80" t="s">
         <v>412</v>
       </c>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="80" t="s">
         <v>413</v>
       </c>
-      <c r="E12" s="77" t="s">
+      <c r="E12" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G12" s="74" t="s">
+      <c r="G12" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="80" t="s">
         <v>414</v>
       </c>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="80" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="75" t="s">
         <v>416</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="76" t="s">
         <v>417</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="76" t="s">
         <v>418</v>
       </c>
-      <c r="D13" s="72" t="s">
+      <c r="D13" s="76" t="s">
         <v>419</v>
       </c>
-      <c r="E13" s="73" t="s">
+      <c r="E13" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H13" s="72" t="s">
+      <c r="H13" s="76" t="s">
         <v>420</v>
       </c>
-      <c r="I13" s="72" t="s">
+      <c r="I13" s="76" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="75" t="s">
+      <c r="A14" s="79" t="s">
         <v>416</v>
       </c>
-      <c r="B14" s="76" t="s">
+      <c r="B14" s="80" t="s">
         <v>422</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="80" t="s">
         <v>423</v>
       </c>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="80" t="s">
         <v>424</v>
       </c>
-      <c r="E14" s="77" t="s">
+      <c r="E14" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F14" s="76" t="s">
+      <c r="F14" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G14" s="74" t="s">
+      <c r="G14" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H14" s="76" t="s">
+      <c r="H14" s="80" t="s">
         <v>425</v>
       </c>
-      <c r="I14" s="76" t="s">
+      <c r="I14" s="80" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="75" t="s">
         <v>416</v>
       </c>
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="76" t="s">
         <v>427</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="76" t="s">
         <v>428</v>
       </c>
-      <c r="D15" s="72" t="s">
+      <c r="D15" s="76" t="s">
         <v>429</v>
       </c>
-      <c r="E15" s="73" t="s">
+      <c r="E15" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G15" s="74" t="s">
+      <c r="G15" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H15" s="72" t="s">
+      <c r="H15" s="76" t="s">
         <v>430</v>
       </c>
-      <c r="I15" s="72" t="s">
+      <c r="I15" s="76" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="75" t="s">
+      <c r="A16" s="79" t="s">
         <v>432</v>
       </c>
-      <c r="B16" s="76" t="s">
+      <c r="B16" s="80" t="s">
         <v>433</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="80" t="s">
         <v>434</v>
       </c>
-      <c r="D16" s="76" t="s">
+      <c r="D16" s="80" t="s">
         <v>435</v>
       </c>
-      <c r="E16" s="77" t="s">
+      <c r="E16" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F16" s="76" t="s">
+      <c r="F16" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="G16" s="74" t="s">
+      <c r="G16" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H16" s="76" t="s">
+      <c r="H16" s="80" t="s">
         <v>436</v>
       </c>
-      <c r="I16" s="76" t="s">
+      <c r="I16" s="80" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="71" t="s">
+      <c r="A17" s="75" t="s">
         <v>432</v>
       </c>
-      <c r="B17" s="72" t="s">
+      <c r="B17" s="76" t="s">
         <v>438</v>
       </c>
-      <c r="C17" s="72" t="s">
+      <c r="C17" s="76" t="s">
         <v>439</v>
       </c>
-      <c r="D17" s="72" t="s">
+      <c r="D17" s="76" t="s">
         <v>440</v>
       </c>
-      <c r="E17" s="78" t="s">
+      <c r="E17" s="82" t="s">
         <v>441</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G17" s="72" t="s">
+      <c r="G17" s="76" t="s">
         <v>442</v>
       </c>
-      <c r="H17" s="72" t="s">
+      <c r="H17" s="76" t="s">
         <v>443</v>
       </c>
-      <c r="I17" s="72" t="s">
+      <c r="I17" s="76" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="75" t="s">
+      <c r="A18" s="79" t="s">
         <v>432</v>
       </c>
-      <c r="B18" s="76" t="s">
+      <c r="B18" s="80" t="s">
         <v>445</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="80" t="s">
         <v>446</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="80" t="s">
         <v>447</v>
       </c>
-      <c r="E18" s="77" t="s">
+      <c r="E18" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G18" s="74" t="s">
+      <c r="G18" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="80" t="s">
         <v>448</v>
       </c>
-      <c r="I18" s="76" t="s">
+      <c r="I18" s="80" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="75" t="s">
         <v>432</v>
       </c>
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="76" t="s">
         <v>450</v>
       </c>
-      <c r="C19" s="72" t="s">
+      <c r="C19" s="76" t="s">
         <v>451</v>
       </c>
-      <c r="D19" s="72" t="s">
+      <c r="D19" s="76" t="s">
         <v>452</v>
       </c>
-      <c r="E19" s="78" t="s">
+      <c r="E19" s="82" t="s">
         <v>441</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H19" s="72" t="s">
+      <c r="H19" s="76" t="s">
         <v>453</v>
       </c>
-      <c r="I19" s="72" t="s">
+      <c r="I19" s="76" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="75" t="s">
+      <c r="A20" s="79" t="s">
         <v>455</v>
       </c>
-      <c r="B20" s="76" t="s">
+      <c r="B20" s="80" t="s">
         <v>456</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="80" t="s">
         <v>457</v>
       </c>
-      <c r="D20" s="76" t="s">
+      <c r="D20" s="80" t="s">
         <v>458</v>
       </c>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F20" s="76" t="s">
+      <c r="F20" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G20" s="76" t="s">
+      <c r="G20" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="H20" s="76" t="s">
+      <c r="H20" s="80" t="s">
         <v>459</v>
       </c>
-      <c r="I20" s="76" t="s">
+      <c r="I20" s="80" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="71" t="s">
+      <c r="A21" s="75" t="s">
         <v>455</v>
       </c>
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="76" t="s">
         <v>461</v>
       </c>
-      <c r="C21" s="72" t="s">
+      <c r="C21" s="76" t="s">
         <v>462</v>
       </c>
-      <c r="D21" s="72" t="s">
+      <c r="D21" s="76" t="s">
         <v>463</v>
       </c>
-      <c r="E21" s="73" t="s">
+      <c r="E21" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G21" s="74" t="s">
+      <c r="G21" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H21" s="72" t="s">
+      <c r="H21" s="76" t="s">
         <v>464</v>
       </c>
-      <c r="I21" s="72" t="s">
+      <c r="I21" s="76" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="75" t="s">
+      <c r="A22" s="79" t="s">
         <v>455</v>
       </c>
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="80" t="s">
         <v>466</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="80" t="s">
         <v>467</v>
       </c>
-      <c r="D22" s="76" t="s">
+      <c r="D22" s="80" t="s">
         <v>468</v>
       </c>
-      <c r="E22" s="77" t="s">
+      <c r="E22" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F22" s="76" t="s">
+      <c r="F22" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G22" s="74" t="s">
+      <c r="G22" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H22" s="76" t="s">
+      <c r="H22" s="80" t="s">
         <v>469</v>
       </c>
-      <c r="I22" s="76" t="s">
+      <c r="I22" s="80" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="71" t="s">
+      <c r="A23" s="75" t="s">
         <v>471</v>
       </c>
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="76" t="s">
         <v>472</v>
       </c>
-      <c r="C23" s="72" t="s">
+      <c r="C23" s="76" t="s">
         <v>473</v>
       </c>
-      <c r="D23" s="72" t="s">
+      <c r="D23" s="76" t="s">
         <v>474</v>
       </c>
-      <c r="E23" s="79" t="s">
+      <c r="E23" s="83" t="s">
         <v>475</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H23" s="72" t="s">
+      <c r="H23" s="76" t="s">
         <v>476</v>
       </c>
-      <c r="I23" s="72" t="s">
+      <c r="I23" s="76" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="75" t="s">
+      <c r="A24" s="79" t="s">
         <v>471</v>
       </c>
-      <c r="B24" s="76" t="s">
+      <c r="B24" s="80" t="s">
         <v>478</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="80" t="s">
         <v>479</v>
       </c>
-      <c r="D24" s="76" t="s">
+      <c r="D24" s="80" t="s">
         <v>480</v>
       </c>
-      <c r="E24" s="80" t="s">
+      <c r="E24" s="84" t="s">
         <v>475</v>
       </c>
-      <c r="F24" s="76" t="s">
+      <c r="F24" s="80" t="s">
         <v>288</v>
       </c>
-      <c r="G24" s="74" t="s">
+      <c r="G24" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="80" t="s">
         <v>481</v>
       </c>
-      <c r="I24" s="76" t="s">
+      <c r="I24" s="80" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="75" t="s">
         <v>471</v>
       </c>
-      <c r="B25" s="72" t="s">
+      <c r="B25" s="76" t="s">
         <v>483</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="76" t="s">
         <v>484</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="D25" s="76" t="s">
         <v>485</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F25" s="72" t="s">
+      <c r="F25" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G25" s="74" t="s">
+      <c r="G25" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H25" s="72" t="s">
+      <c r="H25" s="76" t="s">
         <v>486</v>
       </c>
-      <c r="I25" s="72" t="s">
+      <c r="I25" s="76" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="79" t="s">
         <v>488</v>
       </c>
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="80" t="s">
         <v>489</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="80" t="s">
         <v>490</v>
       </c>
-      <c r="D26" s="76" t="s">
+      <c r="D26" s="80" t="s">
         <v>491</v>
       </c>
-      <c r="E26" s="77" t="s">
+      <c r="E26" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F26" s="76" t="s">
+      <c r="F26" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G26" s="74" t="s">
+      <c r="G26" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H26" s="76" t="s">
+      <c r="H26" s="80" t="s">
         <v>492</v>
       </c>
-      <c r="I26" s="76" t="s">
+      <c r="I26" s="80" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="71" t="s">
+      <c r="A27" s="75" t="s">
         <v>488</v>
       </c>
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="76" t="s">
         <v>494</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="76" t="s">
         <v>495</v>
       </c>
-      <c r="D27" s="72" t="s">
+      <c r="D27" s="76" t="s">
         <v>496</v>
       </c>
-      <c r="E27" s="78" t="s">
+      <c r="E27" s="82" t="s">
         <v>441</v>
       </c>
-      <c r="F27" s="72" t="s">
+      <c r="F27" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G27" s="74" t="s">
+      <c r="G27" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H27" s="72" t="s">
+      <c r="H27" s="76" t="s">
         <v>497</v>
       </c>
-      <c r="I27" s="72" t="s">
+      <c r="I27" s="76" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="75" t="s">
+      <c r="A28" s="79" t="s">
         <v>499</v>
       </c>
-      <c r="B28" s="76" t="s">
+      <c r="B28" s="80" t="s">
         <v>500</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="80" t="s">
         <v>501</v>
       </c>
-      <c r="D28" s="76" t="s">
+      <c r="D28" s="80" t="s">
         <v>480</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F28" s="76" t="s">
+      <c r="F28" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G28" s="74" t="s">
+      <c r="G28" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H28" s="76" t="s">
+      <c r="H28" s="80" t="s">
         <v>502</v>
       </c>
-      <c r="I28" s="76" t="s">
+      <c r="I28" s="80" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="75" t="s">
         <v>499</v>
       </c>
-      <c r="B29" s="72" t="s">
+      <c r="B29" s="76" t="s">
         <v>504</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="76" t="s">
         <v>505</v>
       </c>
-      <c r="D29" s="72" t="s">
+      <c r="D29" s="76" t="s">
         <v>506</v>
       </c>
-      <c r="E29" s="73" t="s">
+      <c r="E29" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F29" s="72" t="s">
+      <c r="F29" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G29" s="74" t="s">
+      <c r="G29" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H29" s="72" t="s">
+      <c r="H29" s="76" t="s">
         <v>507</v>
       </c>
-      <c r="I29" s="72" t="s">
+      <c r="I29" s="76" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="75" t="s">
+      <c r="A30" s="79" t="s">
         <v>499</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="80" t="s">
         <v>509</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="80" t="s">
         <v>510</v>
       </c>
-      <c r="D30" s="76" t="s">
+      <c r="D30" s="80" t="s">
         <v>510</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F30" s="76" t="s">
+      <c r="F30" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="G30" s="76" t="s">
+      <c r="G30" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="H30" s="76" t="s">
+      <c r="H30" s="80" t="s">
         <v>511</v>
       </c>
-      <c r="I30" s="76" t="s">
+      <c r="I30" s="80" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="71" t="s">
+      <c r="A31" s="75" t="s">
         <v>513</v>
       </c>
-      <c r="B31" s="72" t="s">
+      <c r="B31" s="76" t="s">
         <v>514</v>
       </c>
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="76" t="s">
         <v>515</v>
       </c>
-      <c r="D31" s="72" t="s">
+      <c r="D31" s="76" t="s">
         <v>516</v>
       </c>
-      <c r="E31" s="78" t="s">
+      <c r="E31" s="82" t="s">
         <v>441</v>
       </c>
-      <c r="F31" s="72" t="s">
+      <c r="F31" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G31" s="74" t="s">
+      <c r="G31" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H31" s="72" t="s">
+      <c r="H31" s="76" t="s">
         <v>517</v>
       </c>
-      <c r="I31" s="72" t="s">
+      <c r="I31" s="76" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="75" t="s">
+      <c r="A32" s="79" t="s">
         <v>513</v>
       </c>
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="80" t="s">
         <v>519</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="80" t="s">
         <v>520</v>
       </c>
-      <c r="D32" s="76" t="s">
+      <c r="D32" s="80" t="s">
         <v>424</v>
       </c>
-      <c r="E32" s="81" t="s">
+      <c r="E32" s="85" t="s">
         <v>441</v>
       </c>
-      <c r="F32" s="76" t="s">
+      <c r="F32" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G32" s="74" t="s">
+      <c r="G32" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H32" s="76" t="s">
+      <c r="H32" s="80" t="s">
         <v>521</v>
       </c>
-      <c r="I32" s="76" t="s">
+      <c r="I32" s="80" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="71" t="s">
+      <c r="A33" s="75" t="s">
         <v>513</v>
       </c>
-      <c r="B33" s="72" t="s">
+      <c r="B33" s="76" t="s">
         <v>523</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="76" t="s">
         <v>524</v>
       </c>
-      <c r="D33" s="72" t="s">
+      <c r="D33" s="76" t="s">
         <v>525</v>
       </c>
-      <c r="E33" s="73" t="s">
+      <c r="E33" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F33" s="72" t="s">
+      <c r="F33" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G33" s="74" t="s">
+      <c r="G33" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H33" s="72" t="s">
+      <c r="H33" s="76" t="s">
         <v>526</v>
       </c>
-      <c r="I33" s="72" t="s">
+      <c r="I33" s="76" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="75" t="s">
+      <c r="A34" s="79" t="s">
         <v>528</v>
       </c>
-      <c r="B34" s="76" t="s">
+      <c r="B34" s="80" t="s">
         <v>529</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="80" t="s">
         <v>530</v>
       </c>
-      <c r="D34" s="76" t="s">
+      <c r="D34" s="80" t="s">
         <v>531</v>
       </c>
-      <c r="E34" s="77" t="s">
+      <c r="E34" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F34" s="76" t="s">
+      <c r="F34" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="G34" s="74" t="s">
+      <c r="G34" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H34" s="76" t="s">
+      <c r="H34" s="80" t="s">
         <v>532</v>
       </c>
-      <c r="I34" s="76" t="s">
+      <c r="I34" s="80" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="71" t="s">
+      <c r="A35" s="75" t="s">
         <v>528</v>
       </c>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="76" t="s">
         <v>534</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="76" t="s">
         <v>535</v>
       </c>
-      <c r="D35" s="72" t="s">
+      <c r="D35" s="76" t="s">
         <v>536</v>
       </c>
-      <c r="E35" s="73" t="s">
+      <c r="E35" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F35" s="72" t="s">
+      <c r="F35" s="76" t="s">
         <v>268</v>
       </c>
-      <c r="G35" s="74" t="s">
+      <c r="G35" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H35" s="72" t="s">
+      <c r="H35" s="76" t="s">
         <v>537</v>
       </c>
-      <c r="I35" s="72" t="s">
+      <c r="I35" s="76" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="75" t="s">
+      <c r="A36" s="79" t="s">
         <v>528</v>
       </c>
-      <c r="B36" s="76" t="s">
+      <c r="B36" s="80" t="s">
         <v>539</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="80" t="s">
         <v>540</v>
       </c>
-      <c r="D36" s="76" t="s">
+      <c r="D36" s="80" t="s">
         <v>541</v>
       </c>
-      <c r="E36" s="77" t="s">
+      <c r="E36" s="81" t="s">
         <v>386</v>
       </c>
-      <c r="F36" s="76" t="s">
+      <c r="F36" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="G36" s="74" t="s">
+      <c r="G36" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H36" s="76" t="s">
+      <c r="H36" s="80" t="s">
         <v>542</v>
       </c>
-      <c r="I36" s="76" t="s">
+      <c r="I36" s="80" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="71" t="s">
+      <c r="A37" s="75" t="s">
         <v>544</v>
       </c>
-      <c r="B37" s="72" t="s">
+      <c r="B37" s="76" t="s">
         <v>545</v>
       </c>
-      <c r="C37" s="72" t="s">
+      <c r="C37" s="76" t="s">
         <v>546</v>
       </c>
-      <c r="D37" s="72" t="s">
+      <c r="D37" s="76" t="s">
         <v>547</v>
       </c>
-      <c r="E37" s="73" t="s">
+      <c r="E37" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F37" s="72" t="s">
+      <c r="F37" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G37" s="74" t="s">
+      <c r="G37" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H37" s="72" t="s">
+      <c r="H37" s="76" t="s">
         <v>548</v>
       </c>
-      <c r="I37" s="72" t="s">
+      <c r="I37" s="76" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="75" t="s">
+      <c r="A38" s="79" t="s">
         <v>544</v>
       </c>
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="80" t="s">
         <v>550</v>
       </c>
-      <c r="C38" s="76" t="s">
+      <c r="C38" s="80" t="s">
         <v>551</v>
       </c>
-      <c r="D38" s="76" t="s">
+      <c r="D38" s="80" t="s">
         <v>552</v>
       </c>
-      <c r="E38" s="81" t="s">
+      <c r="E38" s="85" t="s">
         <v>441</v>
       </c>
-      <c r="F38" s="76" t="s">
+      <c r="F38" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="G38" s="74" t="s">
+      <c r="G38" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H38" s="76" t="s">
+      <c r="H38" s="80" t="s">
         <v>553</v>
       </c>
-      <c r="I38" s="76" t="s">
+      <c r="I38" s="80" t="s">
         <v>554</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="71" t="s">
+      <c r="A39" s="75" t="s">
         <v>544</v>
       </c>
-      <c r="B39" s="72" t="s">
+      <c r="B39" s="76" t="s">
         <v>555</v>
       </c>
-      <c r="C39" s="72" t="s">
+      <c r="C39" s="76" t="s">
         <v>556</v>
       </c>
-      <c r="D39" s="72" t="s">
+      <c r="D39" s="76" t="s">
         <v>557</v>
       </c>
-      <c r="E39" s="73" t="s">
+      <c r="E39" s="77" t="s">
         <v>386</v>
       </c>
-      <c r="F39" s="72" t="s">
+      <c r="F39" s="76" t="s">
         <v>278</v>
       </c>
-      <c r="G39" s="74" t="s">
+      <c r="G39" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="H39" s="72" t="s">
+      <c r="H39" s="76" t="s">
         <v>558</v>
       </c>
-      <c r="I39" s="72" t="s">
+      <c r="I39" s="76" t="s">
         <v>559</v>
       </c>
     </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="69" t="s">
+      <c r="A42" s="73" t="s">
         <v>560</v>
       </c>
-      <c r="B42" s="69"/>
-      <c r="C42" s="69"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="73"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="70" t="s">
+      <c r="A43" s="74" t="s">
         <v>561</v>
       </c>
-      <c r="B43" s="70" t="s">
+      <c r="B43" s="74" t="s">
         <v>562</v>
       </c>
-      <c r="C43" s="70" t="s">
+      <c r="C43" s="74" t="s">
         <v>563</v>
       </c>
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="74" t="s">
         <v>564</v>
       </c>
-      <c r="E43" s="70" t="s">
+      <c r="E43" s="74" t="s">
         <v>565</v>
       </c>
-      <c r="F43" s="70" t="s">
+      <c r="F43" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="G43" s="70" t="s">
+      <c r="G43" s="74" t="s">
         <v>566</v>
       </c>
-      <c r="H43" s="70" t="s">
+      <c r="H43" s="74" t="s">
         <v>567</v>
       </c>
-      <c r="I43" s="70" t="s">
+      <c r="I43" s="74" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="75" t="s">
+      <c r="A44" s="79" t="s">
         <v>569</v>
       </c>
-      <c r="B44" s="76" t="s">
+      <c r="B44" s="80" t="s">
         <v>570</v>
       </c>
-      <c r="C44" s="76" t="s">
+      <c r="C44" s="80" t="s">
         <v>571</v>
       </c>
-      <c r="D44" s="76" t="s">
+      <c r="D44" s="80" t="s">
         <v>572</v>
       </c>
-      <c r="E44" s="82" t="n">
+      <c r="E44" s="86" t="n">
         <v>8</v>
       </c>
-      <c r="F44" s="83" t="n">
+      <c r="F44" s="87" t="n">
         <v>0.3</v>
       </c>
-      <c r="G44" s="84" t="n">
+      <c r="G44" s="88" t="n">
         <f aca="false">E44*F44</f>
         <v>2.4</v>
       </c>
-      <c r="H44" s="76" t="s">
+      <c r="H44" s="80" t="s">
         <v>573</v>
       </c>
-      <c r="I44" s="77" t="s">
+      <c r="I44" s="81" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="75" t="s">
+      <c r="A45" s="79" t="s">
         <v>575</v>
       </c>
-      <c r="B45" s="76" t="s">
+      <c r="B45" s="80" t="s">
         <v>576</v>
       </c>
-      <c r="C45" s="76" t="s">
+      <c r="C45" s="80" t="s">
         <v>577</v>
       </c>
-      <c r="D45" s="76" t="s">
+      <c r="D45" s="80" t="s">
         <v>578</v>
       </c>
-      <c r="E45" s="82" t="n">
+      <c r="E45" s="86" t="n">
         <v>15</v>
       </c>
-      <c r="F45" s="83" t="n">
+      <c r="F45" s="87" t="n">
         <v>0.55</v>
       </c>
-      <c r="G45" s="84" t="n">
+      <c r="G45" s="88" t="n">
         <f aca="false">E45*F45</f>
         <v>8.25</v>
       </c>
-      <c r="H45" s="76" t="s">
+      <c r="H45" s="80" t="s">
         <v>579</v>
       </c>
-      <c r="I45" s="77" t="s">
+      <c r="I45" s="81" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="75" t="s">
+      <c r="A46" s="79" t="s">
         <v>580</v>
       </c>
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="80" t="s">
         <v>581</v>
       </c>
-      <c r="C46" s="76" t="s">
+      <c r="C46" s="80" t="s">
         <v>582</v>
       </c>
-      <c r="D46" s="76" t="s">
+      <c r="D46" s="80" t="s">
         <v>583</v>
       </c>
-      <c r="E46" s="82" t="n">
+      <c r="E46" s="86" t="n">
         <v>4.2</v>
       </c>
-      <c r="F46" s="83" t="n">
+      <c r="F46" s="87" t="n">
         <v>0.65</v>
       </c>
-      <c r="G46" s="84" t="n">
+      <c r="G46" s="88" t="n">
         <f aca="false">E46*F46</f>
         <v>2.73</v>
       </c>
-      <c r="H46" s="76" t="s">
+      <c r="H46" s="80" t="s">
         <v>584</v>
       </c>
-      <c r="I46" s="77" t="s">
+      <c r="I46" s="81" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="75" t="s">
+      <c r="A47" s="79" t="s">
         <v>586</v>
       </c>
-      <c r="B47" s="76" t="s">
+      <c r="B47" s="80" t="s">
         <v>587</v>
       </c>
-      <c r="C47" s="76" t="s">
+      <c r="C47" s="80" t="s">
         <v>588</v>
       </c>
-      <c r="D47" s="76" t="s">
+      <c r="D47" s="80" t="s">
         <v>589</v>
       </c>
-      <c r="E47" s="82" t="n">
+      <c r="E47" s="86" t="n">
         <v>2.5</v>
       </c>
-      <c r="F47" s="83" t="n">
+      <c r="F47" s="87" t="n">
         <v>0.5</v>
       </c>
-      <c r="G47" s="84" t="n">
+      <c r="G47" s="88" t="n">
         <f aca="false">E47*F47</f>
         <v>1.25</v>
       </c>
-      <c r="H47" s="76" t="s">
+      <c r="H47" s="80" t="s">
         <v>590</v>
       </c>
-      <c r="I47" s="77" t="s">
+      <c r="I47" s="81" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="75" t="s">
+      <c r="A48" s="79" t="s">
         <v>591</v>
       </c>
-      <c r="B48" s="76" t="s">
+      <c r="B48" s="80" t="s">
         <v>592</v>
       </c>
-      <c r="C48" s="76" t="s">
+      <c r="C48" s="80" t="s">
         <v>593</v>
       </c>
-      <c r="D48" s="76" t="s">
+      <c r="D48" s="80" t="s">
         <v>594</v>
       </c>
-      <c r="E48" s="82" t="n">
+      <c r="E48" s="86" t="n">
         <v>-6</v>
       </c>
-      <c r="F48" s="83" t="n">
+      <c r="F48" s="87" t="n">
         <v>0.45</v>
       </c>
-      <c r="G48" s="84" t="n">
+      <c r="G48" s="88" t="n">
         <f aca="false">E48*F48</f>
         <v>-2.7</v>
       </c>
-      <c r="H48" s="76" t="s">
+      <c r="H48" s="80" t="s">
         <v>595</v>
       </c>
-      <c r="I48" s="81" t="s">
+      <c r="I48" s="85" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="75" t="s">
+      <c r="A49" s="79" t="s">
         <v>597</v>
       </c>
-      <c r="B49" s="76" t="s">
+      <c r="B49" s="80" t="s">
         <v>598</v>
       </c>
-      <c r="C49" s="76" t="s">
+      <c r="C49" s="80" t="s">
         <v>599</v>
       </c>
-      <c r="D49" s="76" t="s">
+      <c r="D49" s="80" t="s">
         <v>600</v>
       </c>
-      <c r="E49" s="82" t="n">
+      <c r="E49" s="86" t="n">
         <v>-5</v>
       </c>
-      <c r="F49" s="83" t="n">
+      <c r="F49" s="87" t="n">
         <v>0.6</v>
       </c>
-      <c r="G49" s="84" t="n">
+      <c r="G49" s="88" t="n">
         <f aca="false">E49*F49</f>
         <v>-3</v>
       </c>
-      <c r="H49" s="76" t="s">
+      <c r="H49" s="80" t="s">
         <v>601</v>
       </c>
-      <c r="I49" s="81" t="s">
+      <c r="I49" s="85" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="75" t="s">
+      <c r="A50" s="79" t="s">
         <v>603</v>
       </c>
-      <c r="B50" s="76" t="s">
+      <c r="B50" s="80" t="s">
         <v>604</v>
       </c>
-      <c r="C50" s="76" t="s">
+      <c r="C50" s="80" t="s">
         <v>605</v>
       </c>
-      <c r="D50" s="76" t="s">
+      <c r="D50" s="80" t="s">
         <v>606</v>
       </c>
-      <c r="E50" s="82" t="n">
+      <c r="E50" s="86" t="n">
         <v>12</v>
       </c>
-      <c r="F50" s="83" t="n">
+      <c r="F50" s="87" t="n">
         <v>0.15</v>
       </c>
-      <c r="G50" s="84" t="n">
+      <c r="G50" s="88" t="n">
         <f aca="false">E50*F50</f>
         <v>1.8</v>
       </c>
-      <c r="H50" s="76" t="s">
+      <c r="H50" s="80" t="s">
         <v>607</v>
       </c>
-      <c r="I50" s="77" t="s">
+      <c r="I50" s="81" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="75" t="s">
+      <c r="A51" s="79" t="s">
         <v>609</v>
       </c>
-      <c r="B51" s="76" t="s">
+      <c r="B51" s="80" t="s">
         <v>610</v>
       </c>
-      <c r="C51" s="76" t="s">
+      <c r="C51" s="80" t="s">
         <v>611</v>
       </c>
-      <c r="D51" s="76" t="s">
+      <c r="D51" s="80" t="s">
         <v>612</v>
       </c>
-      <c r="E51" s="82" t="n">
+      <c r="E51" s="86" t="n">
         <v>3.5</v>
       </c>
-      <c r="F51" s="83" t="n">
+      <c r="F51" s="87" t="n">
         <v>0.4</v>
       </c>
-      <c r="G51" s="84" t="n">
+      <c r="G51" s="88" t="n">
         <f aca="false">E51*F51</f>
         <v>1.4</v>
       </c>
-      <c r="H51" s="76" t="s">
+      <c r="H51" s="80" t="s">
         <v>595</v>
       </c>
-      <c r="I51" s="77" t="s">
+      <c r="I51" s="81" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="75" t="s">
+      <c r="A52" s="79" t="s">
         <v>613</v>
       </c>
-      <c r="B52" s="76" t="s">
+      <c r="B52" s="80" t="s">
         <v>614</v>
       </c>
-      <c r="C52" s="76" t="s">
+      <c r="C52" s="80" t="s">
         <v>615</v>
       </c>
-      <c r="D52" s="76" t="s">
+      <c r="D52" s="80" t="s">
         <v>616</v>
       </c>
-      <c r="E52" s="82" t="n">
+      <c r="E52" s="86" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F52" s="83" t="n">
+      <c r="F52" s="87" t="n">
         <v>0.35</v>
       </c>
-      <c r="G52" s="84" t="n">
+      <c r="G52" s="88" t="n">
         <f aca="false">E52*F52</f>
         <v>-0.525</v>
       </c>
-      <c r="H52" s="76" t="s">
+      <c r="H52" s="80" t="s">
         <v>617</v>
       </c>
-      <c r="I52" s="81" t="s">
+      <c r="I52" s="85" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="75" t="s">
+      <c r="A53" s="79" t="s">
         <v>618</v>
       </c>
-      <c r="B53" s="76" t="s">
+      <c r="B53" s="80" t="s">
         <v>619</v>
       </c>
-      <c r="C53" s="76" t="s">
+      <c r="C53" s="80" t="s">
         <v>620</v>
       </c>
-      <c r="D53" s="76" t="s">
+      <c r="D53" s="80" t="s">
         <v>621</v>
       </c>
-      <c r="E53" s="82" t="n">
+      <c r="E53" s="86" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="83" t="n">
+      <c r="F53" s="87" t="n">
         <v>0.2</v>
       </c>
-      <c r="G53" s="84" t="n">
+      <c r="G53" s="88" t="n">
         <f aca="false">E53*F53</f>
         <v>4</v>
       </c>
-      <c r="H53" s="76" t="s">
+      <c r="H53" s="80" t="s">
         <v>617</v>
       </c>
-      <c r="I53" s="77" t="s">
+      <c r="I53" s="81" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="85" t="s">
+      <c r="A54" s="89" t="s">
         <v>622</v>
       </c>
-      <c r="B54" s="86"/>
-      <c r="C54" s="86"/>
-      <c r="D54" s="86"/>
-      <c r="E54" s="86"/>
-      <c r="F54" s="86"/>
-      <c r="G54" s="87" t="n">
+      <c r="B54" s="90"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="90"/>
+      <c r="E54" s="90"/>
+      <c r="F54" s="90"/>
+      <c r="G54" s="91" t="n">
         <f aca="false">SUM(G44:G53)</f>
         <v>15.605</v>
       </c>
-      <c r="H54" s="86"/>
-      <c r="I54" s="86"/>
-    </row>
+      <c r="H54" s="90"/>
+      <c r="I54" s="90"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="69" t="s">
+      <c r="A57" s="73" t="s">
         <v>623</v>
       </c>
-      <c r="B57" s="69"/>
-      <c r="C57" s="69"/>
-      <c r="D57" s="69"/>
-      <c r="E57" s="69"/>
-      <c r="F57" s="69"/>
-      <c r="G57" s="69"/>
-      <c r="H57" s="69"/>
-      <c r="I57" s="69"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="73"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73"/>
     </row>
     <row r="58" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="70" t="s">
+      <c r="A58" s="74" t="s">
         <v>624</v>
       </c>
-      <c r="B58" s="70" t="s">
+      <c r="B58" s="74" t="s">
         <v>625</v>
       </c>
-      <c r="C58" s="70" t="s">
+      <c r="C58" s="74" t="s">
         <v>626</v>
       </c>
-      <c r="D58" s="70" t="s">
+      <c r="D58" s="74" t="s">
         <v>627</v>
       </c>
-      <c r="E58" s="70" t="s">
+      <c r="E58" s="74" t="s">
         <v>628</v>
       </c>
-      <c r="F58" s="70" t="s">
+      <c r="F58" s="74" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="88" t="s">
+      <c r="A59" s="92" t="s">
         <v>630</v>
       </c>
-      <c r="B59" s="89" t="s">
+      <c r="B59" s="93" t="s">
         <v>631</v>
       </c>
-      <c r="C59" s="89" t="s">
+      <c r="C59" s="93" t="s">
         <v>632</v>
       </c>
-      <c r="D59" s="90" t="s">
+      <c r="D59" s="94" t="s">
         <v>268</v>
       </c>
-      <c r="E59" s="89" t="s">
+      <c r="E59" s="93" t="s">
         <v>633</v>
       </c>
-      <c r="F59" s="89" t="s">
+      <c r="F59" s="93" t="s">
         <v>634</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="91" t="s">
+      <c r="A60" s="95" t="s">
         <v>635</v>
       </c>
-      <c r="B60" s="76" t="s">
+      <c r="B60" s="80" t="s">
         <v>636</v>
       </c>
-      <c r="C60" s="76" t="s">
+      <c r="C60" s="80" t="s">
         <v>637</v>
       </c>
-      <c r="D60" s="77" t="s">
+      <c r="D60" s="81" t="s">
         <v>268</v>
       </c>
-      <c r="E60" s="76" t="s">
+      <c r="E60" s="80" t="s">
         <v>638</v>
       </c>
-      <c r="F60" s="76" t="s">
+      <c r="F60" s="80" t="s">
         <v>639</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="88" t="s">
+      <c r="A61" s="92" t="s">
         <v>640</v>
       </c>
-      <c r="B61" s="89" t="s">
+      <c r="B61" s="93" t="s">
         <v>641</v>
       </c>
-      <c r="C61" s="89" t="s">
+      <c r="C61" s="93" t="s">
         <v>642</v>
       </c>
-      <c r="D61" s="92" t="s">
+      <c r="D61" s="96" t="s">
         <v>278</v>
       </c>
-      <c r="E61" s="89" t="s">
+      <c r="E61" s="93" t="s">
         <v>643</v>
       </c>
-      <c r="F61" s="89" t="s">
+      <c r="F61" s="93" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="91" t="s">
+      <c r="A62" s="95" t="s">
         <v>645</v>
       </c>
-      <c r="B62" s="76" t="s">
+      <c r="B62" s="80" t="s">
         <v>646</v>
       </c>
-      <c r="C62" s="76" t="s">
+      <c r="C62" s="80" t="s">
         <v>647</v>
       </c>
-      <c r="D62" s="80" t="s">
+      <c r="D62" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="E62" s="76" t="s">
+      <c r="E62" s="80" t="s">
         <v>648</v>
       </c>
-      <c r="F62" s="76" t="s">
+      <c r="F62" s="80" t="s">
         <v>649</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="88" t="s">
+      <c r="A63" s="92" t="s">
         <v>650</v>
       </c>
-      <c r="B63" s="89" t="s">
+      <c r="B63" s="93" t="s">
         <v>651</v>
       </c>
-      <c r="C63" s="89" t="s">
+      <c r="C63" s="93" t="s">
         <v>652</v>
       </c>
-      <c r="D63" s="90" t="s">
+      <c r="D63" s="94" t="s">
         <v>268</v>
       </c>
-      <c r="E63" s="89" t="s">
+      <c r="E63" s="93" t="s">
         <v>653</v>
       </c>
-      <c r="F63" s="89" t="s">
+      <c r="F63" s="93" t="s">
         <v>654</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="91" t="s">
+      <c r="A64" s="95" t="s">
         <v>655</v>
       </c>
-      <c r="B64" s="76" t="s">
+      <c r="B64" s="80" t="s">
         <v>656</v>
       </c>
-      <c r="C64" s="76" t="s">
+      <c r="C64" s="80" t="s">
         <v>657</v>
       </c>
-      <c r="D64" s="80" t="s">
+      <c r="D64" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="E64" s="76" t="s">
+      <c r="E64" s="80" t="s">
         <v>658</v>
       </c>
-      <c r="F64" s="76" t="s">
+      <c r="F64" s="80" t="s">
         <v>659</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="88" t="s">
+      <c r="A65" s="92" t="s">
         <v>660</v>
       </c>
-      <c r="B65" s="89" t="s">
+      <c r="B65" s="93" t="s">
         <v>661</v>
       </c>
-      <c r="C65" s="89" t="s">
+      <c r="C65" s="93" t="s">
         <v>662</v>
       </c>
-      <c r="D65" s="90" t="s">
+      <c r="D65" s="94" t="s">
         <v>268</v>
       </c>
-      <c r="E65" s="89" t="s">
+      <c r="E65" s="93" t="s">
         <v>663</v>
       </c>
-      <c r="F65" s="89" t="s">
+      <c r="F65" s="93" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="91" t="s">
+      <c r="A66" s="95" t="s">
         <v>665</v>
       </c>
-      <c r="B66" s="76" t="s">
+      <c r="B66" s="80" t="s">
         <v>666</v>
       </c>
-      <c r="C66" s="76" t="s">
+      <c r="C66" s="80" t="s">
         <v>667</v>
       </c>
-      <c r="D66" s="80" t="s">
+      <c r="D66" s="84" t="s">
         <v>278</v>
       </c>
-      <c r="E66" s="76" t="s">
+      <c r="E66" s="80" t="s">
         <v>668</v>
       </c>
-      <c r="F66" s="76" t="s">
+      <c r="F66" s="80" t="s">
         <v>669</v>
       </c>
     </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="69" t="s">
+      <c r="A69" s="73" t="s">
         <v>670</v>
       </c>
-      <c r="B69" s="69"/>
-      <c r="C69" s="69"/>
-      <c r="D69" s="69"/>
-      <c r="E69" s="69"/>
-      <c r="F69" s="69"/>
-      <c r="G69" s="69"/>
-      <c r="H69" s="69"/>
-      <c r="I69" s="69"/>
+      <c r="B69" s="73"/>
+      <c r="C69" s="73"/>
+      <c r="D69" s="73"/>
+      <c r="E69" s="73"/>
+      <c r="F69" s="73"/>
+      <c r="G69" s="73"/>
+      <c r="H69" s="73"/>
+      <c r="I69" s="73"/>
     </row>
     <row r="70" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="70" t="s">
+      <c r="A70" s="74" t="s">
         <v>671</v>
       </c>
-      <c r="B70" s="70" t="s">
+      <c r="B70" s="74" t="s">
         <v>672</v>
       </c>
-      <c r="C70" s="70" t="s">
+      <c r="C70" s="74" t="s">
         <v>673</v>
       </c>
-      <c r="D70" s="70" t="s">
+      <c r="D70" s="74" t="s">
         <v>674</v>
       </c>
-      <c r="E70" s="70" t="s">
+      <c r="E70" s="74" t="s">
         <v>675</v>
       </c>
-      <c r="F70" s="70" t="s">
+      <c r="F70" s="74" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="71" t="s">
+      <c r="A71" s="75" t="s">
         <v>677</v>
       </c>
-      <c r="B71" s="93" t="n">
+      <c r="B71" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="C71" s="93" t="n">
+      <c r="C71" s="97" t="n">
         <v>9</v>
       </c>
-      <c r="D71" s="93" t="n">
+      <c r="D71" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="E71" s="94" t="n">
+      <c r="E71" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F71" s="79" t="s">
+      <c r="F71" s="83" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="75" t="s">
+      <c r="A72" s="79" t="s">
         <v>679</v>
       </c>
-      <c r="B72" s="95" t="n">
+      <c r="B72" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="96" t="n">
+      <c r="C72" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="D72" s="96" t="n">
+      <c r="D72" s="100" t="n">
         <v>5</v>
       </c>
-      <c r="E72" s="94" t="n">
+      <c r="E72" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F72" s="97" t="s">
+      <c r="F72" s="101" t="s">
         <v>680</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="71" t="s">
+      <c r="A73" s="75" t="s">
         <v>681</v>
       </c>
-      <c r="B73" s="95" t="n">
+      <c r="B73" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="95" t="n">
+      <c r="C73" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="98" t="n">
+      <c r="D73" s="102" t="n">
         <v>7</v>
       </c>
-      <c r="E73" s="94" t="n">
+      <c r="E73" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F73" s="97" t="s">
+      <c r="F73" s="101" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="75" t="s">
+      <c r="A74" s="79" t="s">
         <v>683</v>
       </c>
-      <c r="B74" s="96" t="n">
+      <c r="B74" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="C74" s="96" t="n">
+      <c r="C74" s="100" t="n">
         <v>5</v>
       </c>
-      <c r="D74" s="96" t="n">
+      <c r="D74" s="100" t="n">
         <v>6</v>
       </c>
-      <c r="E74" s="94" t="n">
+      <c r="E74" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F74" s="99" t="s">
+      <c r="F74" s="103" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="71" t="s">
+      <c r="A75" s="75" t="s">
         <v>685</v>
       </c>
-      <c r="B75" s="95" t="n">
+      <c r="B75" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="C75" s="95" t="n">
+      <c r="C75" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="95" t="n">
+      <c r="D75" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="E75" s="94" t="n">
+      <c r="E75" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F75" s="88" t="s">
+      <c r="F75" s="92" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="75" t="s">
+      <c r="A76" s="79" t="s">
         <v>687</v>
       </c>
-      <c r="B76" s="95" t="n">
+      <c r="B76" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="95" t="n">
+      <c r="C76" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="96" t="n">
+      <c r="D76" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="E76" s="94" t="n">
+      <c r="E76" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F76" s="97" t="s">
+      <c r="F76" s="101" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="71" t="s">
+      <c r="A77" s="75" t="s">
         <v>689</v>
       </c>
-      <c r="B77" s="93" t="n">
+      <c r="B77" s="97" t="n">
         <v>8</v>
       </c>
-      <c r="C77" s="98" t="n">
+      <c r="C77" s="102" t="n">
         <v>5</v>
       </c>
-      <c r="D77" s="98" t="n">
+      <c r="D77" s="102" t="n">
         <v>6</v>
       </c>
-      <c r="E77" s="94" t="n">
+      <c r="E77" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F77" s="79" t="s">
+      <c r="F77" s="83" t="s">
         <v>690</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="75" t="s">
+      <c r="A78" s="79" t="s">
         <v>691</v>
       </c>
-      <c r="B78" s="95" t="n">
+      <c r="B78" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="95" t="n">
+      <c r="C78" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="96" t="n">
+      <c r="D78" s="100" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="94" t="n">
+      <c r="E78" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F78" s="88" t="s">
+      <c r="F78" s="92" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="71" t="s">
+      <c r="A79" s="75" t="s">
         <v>693</v>
       </c>
-      <c r="B79" s="95" t="n">
+      <c r="B79" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="C79" s="95" t="n">
+      <c r="C79" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="95" t="n">
+      <c r="D79" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="94" t="n">
+      <c r="E79" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F79" s="88" t="s">
+      <c r="F79" s="92" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="75" t="s">
+      <c r="A80" s="79" t="s">
         <v>695</v>
       </c>
-      <c r="B80" s="95" t="n">
+      <c r="B80" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="95" t="n">
+      <c r="C80" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="D80" s="96" t="n">
+      <c r="D80" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="94" t="n">
+      <c r="E80" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F80" s="88" t="s">
+      <c r="F80" s="92" t="s">
         <v>696</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="71" t="s">
+      <c r="A81" s="75" t="s">
         <v>697</v>
       </c>
-      <c r="B81" s="95" t="n">
+      <c r="B81" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="C81" s="95" t="n">
+      <c r="C81" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="95" t="n">
+      <c r="D81" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="E81" s="94" t="n">
+      <c r="E81" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F81" s="88" t="s">
+      <c r="F81" s="92" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="75" t="s">
+      <c r="A82" s="79" t="s">
         <v>699</v>
       </c>
-      <c r="B82" s="95" t="n">
+      <c r="B82" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="C82" s="95" t="n">
+      <c r="C82" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="96" t="n">
+      <c r="D82" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="94" t="n">
+      <c r="E82" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F82" s="88" t="s">
+      <c r="F82" s="92" t="s">
         <v>700</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="71" t="s">
+      <c r="A83" s="75" t="s">
         <v>701</v>
       </c>
-      <c r="B83" s="95" t="n">
+      <c r="B83" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="C83" s="95" t="n">
+      <c r="C83" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="95" t="n">
+      <c r="D83" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="E83" s="94" t="n">
+      <c r="E83" s="98" t="n">
         <v>9</v>
       </c>
-      <c r="F83" s="88" t="s">
+      <c r="F83" s="92" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="75" t="s">
+      <c r="A84" s="79" t="s">
         <v>703</v>
       </c>
-      <c r="B84" s="95" t="n">
+      <c r="B84" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="C84" s="96" t="n">
+      <c r="C84" s="100" t="n">
         <v>4</v>
       </c>
-      <c r="D84" s="96" t="n">
+      <c r="D84" s="100" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="94" t="n">
+      <c r="E84" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F84" s="99" t="s">
+      <c r="F84" s="103" t="s">
         <v>704</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="71" t="s">
+      <c r="A85" s="75" t="s">
         <v>705</v>
       </c>
-      <c r="B85" s="95" t="n">
+      <c r="B85" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="C85" s="95" t="n">
+      <c r="C85" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="D85" s="98" t="n">
+      <c r="D85" s="102" t="n">
         <v>6</v>
       </c>
-      <c r="E85" s="94" t="n">
+      <c r="E85" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F85" s="97" t="s">
+      <c r="F85" s="101" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="75" t="s">
+      <c r="A86" s="79" t="s">
         <v>707</v>
       </c>
-      <c r="B86" s="95" t="n">
+      <c r="B86" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="C86" s="95" t="n">
+      <c r="C86" s="99" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="95" t="n">
+      <c r="D86" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="E86" s="94" t="n">
+      <c r="E86" s="98" t="n">
         <v>8</v>
       </c>
-      <c r="F86" s="88" t="s">
+      <c r="F86" s="92" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="100" t="s">
+      <c r="A87" s="104" t="s">
         <v>709</v>
       </c>
-      <c r="B87" s="101" t="n">
+      <c r="B87" s="105" t="n">
         <f aca="false">AVERAGE(B71:B86)</f>
         <v>2.375</v>
       </c>
-      <c r="C87" s="101" t="n">
+      <c r="C87" s="105" t="n">
         <f aca="false">AVERAGE(C71:C86)</f>
         <v>2.3125</v>
       </c>
-      <c r="D87" s="101" t="n">
+      <c r="D87" s="105" t="n">
         <f aca="false">AVERAGE(D71:D86)</f>
         <v>4.625</v>
       </c>
-      <c r="E87" s="101" t="n">
+      <c r="E87" s="105" t="n">
         <f aca="false">AVERAGE(E71:E86)</f>
         <v>8.5625</v>
       </c>
-      <c r="F87" s="86"/>
-    </row>
+      <c r="F87" s="90"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="69" t="s">
+      <c r="A90" s="73" t="s">
         <v>710</v>
       </c>
-      <c r="B90" s="69"/>
-      <c r="C90" s="69"/>
-      <c r="D90" s="69"/>
-      <c r="E90" s="69"/>
-      <c r="F90" s="69"/>
-      <c r="G90" s="69"/>
-      <c r="H90" s="69"/>
-      <c r="I90" s="69"/>
+      <c r="B90" s="73"/>
+      <c r="C90" s="73"/>
+      <c r="D90" s="73"/>
+      <c r="E90" s="73"/>
+      <c r="F90" s="73"/>
+      <c r="G90" s="73"/>
+      <c r="H90" s="73"/>
+      <c r="I90" s="73"/>
     </row>
     <row r="91" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="70" t="s">
+      <c r="A91" s="74" t="s">
         <v>711</v>
       </c>
-      <c r="B91" s="70" t="s">
+      <c r="B91" s="74" t="s">
         <v>712</v>
       </c>
-      <c r="C91" s="70" t="s">
+      <c r="C91" s="74" t="s">
         <v>713</v>
       </c>
-      <c r="D91" s="70" t="s">
+      <c r="D91" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="E91" s="70" t="s">
+      <c r="E91" s="74" t="s">
         <v>714</v>
       </c>
-      <c r="F91" s="70" t="s">
+      <c r="F91" s="74" t="s">
         <v>715</v>
       </c>
-      <c r="G91" s="70" t="s">
+      <c r="G91" s="74" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="75" t="s">
+      <c r="A92" s="79" t="s">
         <v>330</v>
       </c>
-      <c r="B92" s="76" t="s">
+      <c r="B92" s="80" t="s">
         <v>717</v>
       </c>
-      <c r="C92" s="77" t="s">
+      <c r="C92" s="81" t="s">
         <v>718</v>
       </c>
-      <c r="D92" s="83" t="n">
+      <c r="D92" s="87" t="n">
         <v>0.45</v>
       </c>
-      <c r="E92" s="76" t="s">
+      <c r="E92" s="80" t="s">
         <v>719</v>
       </c>
-      <c r="F92" s="74" t="s">
+      <c r="F92" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G92" s="76" t="s">
+      <c r="G92" s="80" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="75" t="s">
+      <c r="A93" s="79" t="s">
         <v>333</v>
       </c>
-      <c r="B93" s="76" t="s">
+      <c r="B93" s="80" t="s">
         <v>721</v>
       </c>
-      <c r="C93" s="77" t="s">
+      <c r="C93" s="81" t="s">
         <v>718</v>
       </c>
-      <c r="D93" s="83" t="n">
+      <c r="D93" s="87" t="n">
         <v>0.35</v>
       </c>
-      <c r="E93" s="76" t="s">
+      <c r="E93" s="80" t="s">
         <v>722</v>
       </c>
-      <c r="F93" s="76" t="s">
+      <c r="F93" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="G93" s="76" t="s">
+      <c r="G93" s="80" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="75" t="s">
+      <c r="A94" s="79" t="s">
         <v>333</v>
       </c>
-      <c r="B94" s="76" t="s">
+      <c r="B94" s="80" t="s">
         <v>724</v>
       </c>
-      <c r="C94" s="77" t="s">
+      <c r="C94" s="81" t="s">
         <v>725</v>
       </c>
-      <c r="D94" s="83" t="n">
+      <c r="D94" s="87" t="n">
         <v>0.6</v>
       </c>
-      <c r="E94" s="76" t="s">
+      <c r="E94" s="80" t="s">
         <v>726</v>
       </c>
-      <c r="F94" s="74" t="s">
+      <c r="F94" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G94" s="76" t="s">
+      <c r="G94" s="80" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="75" t="s">
+      <c r="A95" s="79" t="s">
         <v>346</v>
       </c>
-      <c r="B95" s="76" t="s">
+      <c r="B95" s="80" t="s">
         <v>728</v>
       </c>
-      <c r="C95" s="77" t="s">
+      <c r="C95" s="81" t="s">
         <v>729</v>
       </c>
-      <c r="D95" s="83" t="n">
+      <c r="D95" s="87" t="n">
         <v>0.25</v>
       </c>
-      <c r="E95" s="76" t="s">
+      <c r="E95" s="80" t="s">
         <v>730</v>
       </c>
-      <c r="F95" s="74" t="s">
+      <c r="F95" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G95" s="76" t="s">
+      <c r="G95" s="80" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="75" t="s">
+      <c r="A96" s="79" t="s">
         <v>346</v>
       </c>
-      <c r="B96" s="76" t="s">
+      <c r="B96" s="80" t="s">
         <v>732</v>
       </c>
-      <c r="C96" s="77" t="s">
+      <c r="C96" s="81" t="s">
         <v>718</v>
       </c>
-      <c r="D96" s="83" t="n">
+      <c r="D96" s="87" t="n">
         <v>0.5</v>
       </c>
-      <c r="E96" s="76" t="s">
+      <c r="E96" s="80" t="s">
         <v>733</v>
       </c>
-      <c r="F96" s="76" t="s">
+      <c r="F96" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="G96" s="76" t="s">
+      <c r="G96" s="80" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="75" t="s">
+      <c r="A97" s="79" t="s">
         <v>735</v>
       </c>
-      <c r="B97" s="76" t="s">
+      <c r="B97" s="80" t="s">
         <v>736</v>
       </c>
-      <c r="C97" s="77" t="s">
+      <c r="C97" s="81" t="s">
         <v>737</v>
       </c>
-      <c r="D97" s="83" t="n">
+      <c r="D97" s="87" t="n">
         <v>0.3</v>
       </c>
-      <c r="E97" s="76" t="s">
+      <c r="E97" s="80" t="s">
         <v>738</v>
       </c>
-      <c r="F97" s="74" t="s">
+      <c r="F97" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G97" s="76" t="s">
+      <c r="G97" s="80" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="75" t="s">
+      <c r="A98" s="79" t="s">
         <v>740</v>
       </c>
-      <c r="B98" s="76" t="s">
+      <c r="B98" s="80" t="s">
         <v>741</v>
       </c>
-      <c r="C98" s="77" t="s">
+      <c r="C98" s="81" t="s">
         <v>742</v>
       </c>
-      <c r="D98" s="83" t="n">
+      <c r="D98" s="87" t="n">
         <v>0.55</v>
       </c>
-      <c r="E98" s="76" t="s">
+      <c r="E98" s="80" t="s">
         <v>743</v>
       </c>
-      <c r="F98" s="74" t="s">
+      <c r="F98" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G98" s="76" t="s">
+      <c r="G98" s="80" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="75" t="s">
+      <c r="A99" s="79" t="s">
         <v>745</v>
       </c>
-      <c r="B99" s="76" t="s">
+      <c r="B99" s="80" t="s">
         <v>746</v>
       </c>
-      <c r="C99" s="77" t="s">
+      <c r="C99" s="81" t="s">
         <v>742</v>
       </c>
-      <c r="D99" s="83" t="n">
+      <c r="D99" s="87" t="n">
         <v>0.4</v>
       </c>
-      <c r="E99" s="76" t="s">
+      <c r="E99" s="80" t="s">
         <v>747</v>
       </c>
-      <c r="F99" s="76" t="s">
+      <c r="F99" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="G99" s="76" t="s">
+      <c r="G99" s="80" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="75" t="s">
+      <c r="A100" s="79" t="s">
         <v>749</v>
       </c>
-      <c r="B100" s="76" t="s">
+      <c r="B100" s="80" t="s">
         <v>750</v>
       </c>
-      <c r="C100" s="77" t="s">
+      <c r="C100" s="81" t="s">
         <v>751</v>
       </c>
-      <c r="D100" s="83" t="n">
+      <c r="D100" s="87" t="n">
         <v>0.35</v>
       </c>
-      <c r="E100" s="76" t="s">
+      <c r="E100" s="80" t="s">
         <v>752</v>
       </c>
-      <c r="F100" s="74" t="s">
+      <c r="F100" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G100" s="76" t="s">
+      <c r="G100" s="80" t="s">
         <v>753</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="75" t="s">
+      <c r="A101" s="79" t="s">
         <v>754</v>
       </c>
-      <c r="B101" s="76" t="s">
+      <c r="B101" s="80" t="s">
         <v>755</v>
       </c>
-      <c r="C101" s="102" t="s">
+      <c r="C101" s="106" t="s">
         <v>754</v>
       </c>
-      <c r="D101" s="83" t="n">
+      <c r="D101" s="87" t="n">
         <v>0.15</v>
       </c>
-      <c r="E101" s="76" t="s">
+      <c r="E101" s="80" t="s">
         <v>756</v>
       </c>
-      <c r="F101" s="74" t="s">
+      <c r="F101" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G101" s="76" t="s">
+      <c r="G101" s="80" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="75" t="s">
+      <c r="A102" s="79" t="s">
         <v>754</v>
       </c>
-      <c r="B102" s="76" t="s">
+      <c r="B102" s="80" t="s">
         <v>758</v>
       </c>
-      <c r="C102" s="77" t="s">
+      <c r="C102" s="81" t="s">
         <v>759</v>
       </c>
-      <c r="D102" s="83" t="n">
+      <c r="D102" s="87" t="n">
         <v>0.1</v>
       </c>
-      <c r="E102" s="76" t="s">
+      <c r="E102" s="80" t="s">
         <v>760</v>
       </c>
-      <c r="F102" s="74" t="s">
+      <c r="F102" s="78" t="s">
         <v>387</v>
       </c>
-      <c r="G102" s="76" t="s">
+      <c r="G102" s="80" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="75" t="s">
+      <c r="A103" s="79" t="s">
         <v>754</v>
       </c>
-      <c r="B103" s="76" t="s">
+      <c r="B103" s="80" t="s">
         <v>762</v>
       </c>
-      <c r="C103" s="77" t="s">
+      <c r="C103" s="81" t="s">
         <v>763</v>
       </c>
-      <c r="D103" s="83" t="n">
+      <c r="D103" s="87" t="n">
         <v>0.2</v>
       </c>
-      <c r="E103" s="76" t="s">
+      <c r="E103" s="80" t="s">
         <v>764</v>
       </c>
-      <c r="F103" s="76" t="s">
+      <c r="F103" s="80" t="s">
         <v>442</v>
       </c>
-      <c r="G103" s="76" t="s">
+      <c r="G103" s="80" t="s">
         <v>765</v>
       </c>
     </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="103" t="s">
+      <c r="A106" s="107" t="s">
         <v>766</v>
       </c>
-      <c r="B106" s="103"/>
-      <c r="C106" s="103"/>
-      <c r="D106" s="103"/>
-      <c r="E106" s="103"/>
-      <c r="F106" s="103"/>
-      <c r="G106" s="103"/>
-      <c r="H106" s="103"/>
-      <c r="I106" s="103"/>
+      <c r="B106" s="107"/>
+      <c r="C106" s="107"/>
+      <c r="D106" s="107"/>
+      <c r="E106" s="107"/>
+      <c r="F106" s="107"/>
+      <c r="G106" s="107"/>
+      <c r="H106" s="107"/>
+      <c r="I106" s="107"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="104" t="s">
+      <c r="A107" s="108" t="s">
         <v>767</v>
       </c>
-      <c r="B107" s="104"/>
-      <c r="C107" s="104"/>
-      <c r="D107" s="104"/>
-      <c r="E107" s="104"/>
-      <c r="F107" s="104"/>
-      <c r="G107" s="104"/>
-      <c r="H107" s="104"/>
-      <c r="I107" s="104"/>
+      <c r="B107" s="108"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="108"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="108"/>
+      <c r="H107" s="108"/>
+      <c r="I107" s="108"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="104" t="s">
+      <c r="A108" s="108" t="s">
         <v>768</v>
       </c>
-      <c r="B108" s="104"/>
-      <c r="C108" s="104"/>
-      <c r="D108" s="104"/>
-      <c r="E108" s="104"/>
-      <c r="F108" s="104"/>
-      <c r="G108" s="104"/>
-      <c r="H108" s="104"/>
-      <c r="I108" s="104"/>
+      <c r="B108" s="108"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="108"/>
+      <c r="E108" s="108"/>
+      <c r="F108" s="108"/>
+      <c r="G108" s="108"/>
+      <c r="H108" s="108"/>
+      <c r="I108" s="108"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="104" t="s">
+      <c r="A109" s="108" t="s">
         <v>769</v>
       </c>
-      <c r="B109" s="104"/>
-      <c r="C109" s="104"/>
-      <c r="D109" s="104"/>
-      <c r="E109" s="104"/>
-      <c r="F109" s="104"/>
-      <c r="G109" s="104"/>
-      <c r="H109" s="104"/>
-      <c r="I109" s="104"/>
+      <c r="B109" s="108"/>
+      <c r="C109" s="108"/>
+      <c r="D109" s="108"/>
+      <c r="E109" s="108"/>
+      <c r="F109" s="108"/>
+      <c r="G109" s="108"/>
+      <c r="H109" s="108"/>
+      <c r="I109" s="108"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="104" t="s">
+      <c r="A110" s="108" t="s">
         <v>770</v>
       </c>
-      <c r="B110" s="104"/>
-      <c r="C110" s="104"/>
-      <c r="D110" s="104"/>
-      <c r="E110" s="104"/>
-      <c r="F110" s="104"/>
-      <c r="G110" s="104"/>
-      <c r="H110" s="104"/>
-      <c r="I110" s="104"/>
+      <c r="B110" s="108"/>
+      <c r="C110" s="108"/>
+      <c r="D110" s="108"/>
+      <c r="E110" s="108"/>
+      <c r="F110" s="108"/>
+      <c r="G110" s="108"/>
+      <c r="H110" s="108"/>
+      <c r="I110" s="108"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="104" t="s">
+      <c r="A111" s="108" t="s">
         <v>771</v>
       </c>
-      <c r="B111" s="104"/>
-      <c r="C111" s="104"/>
-      <c r="D111" s="104"/>
-      <c r="E111" s="104"/>
-      <c r="F111" s="104"/>
-      <c r="G111" s="104"/>
-      <c r="H111" s="104"/>
-      <c r="I111" s="104"/>
+      <c r="B111" s="108"/>
+      <c r="C111" s="108"/>
+      <c r="D111" s="108"/>
+      <c r="E111" s="108"/>
+      <c r="F111" s="108"/>
+      <c r="G111" s="108"/>
+      <c r="H111" s="108"/>
+      <c r="I111" s="108"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="104" t="s">
+      <c r="A112" s="108" t="s">
         <v>772</v>
       </c>
-      <c r="B112" s="104"/>
-      <c r="C112" s="104"/>
-      <c r="D112" s="104"/>
-      <c r="E112" s="104"/>
-      <c r="F112" s="104"/>
-      <c r="G112" s="104"/>
-      <c r="H112" s="104"/>
-      <c r="I112" s="104"/>
+      <c r="B112" s="108"/>
+      <c r="C112" s="108"/>
+      <c r="D112" s="108"/>
+      <c r="E112" s="108"/>
+      <c r="F112" s="108"/>
+      <c r="G112" s="108"/>
+      <c r="H112" s="108"/>
+      <c r="I112" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -7191,9 +7252,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35"/>
@@ -7210,6 +7272,7 @@
         <v>50</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>51</v>
@@ -7442,6 +7505,7 @@
         <v>31190</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>68</v>
@@ -7648,6 +7712,8 @@
         <v>0.18</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
         <v>75</v>
@@ -7762,6 +7828,9 @@
       <c r="A26" s="6" t="s">
         <v>79</v>
       </c>
+      <c r="B26" s="20" t="n">
+        <v>0.043</v>
+      </c>
       <c r="E26" s="15" t="n">
         <v>0.042</v>
       </c>
@@ -7785,6 +7854,9 @@
       <c r="A27" s="6" t="s">
         <v>80</v>
       </c>
+      <c r="B27" s="20" t="n">
+        <v>0.055</v>
+      </c>
       <c r="E27" s="15" t="n">
         <v>0.055</v>
       </c>
@@ -7808,22 +7880,25 @@
       <c r="A28" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="20" t="n">
+      <c r="B28" s="21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E28" s="22" t="n">
         <v>1.8</v>
       </c>
-      <c r="F28" s="20" t="n">
+      <c r="F28" s="22" t="n">
         <v>1.8</v>
       </c>
-      <c r="G28" s="20" t="n">
+      <c r="G28" s="22" t="n">
         <v>1.8</v>
       </c>
-      <c r="H28" s="20" t="n">
+      <c r="H28" s="22" t="n">
         <v>1.8</v>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="I28" s="22" t="n">
         <v>1.8</v>
       </c>
-      <c r="J28" s="20" t="n">
+      <c r="J28" s="22" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -7831,6 +7906,9 @@
       <c r="A29" s="6" t="s">
         <v>82</v>
       </c>
+      <c r="B29" s="20" t="n">
+        <v>0.03</v>
+      </c>
       <c r="E29" s="15" t="n">
         <v>0.03</v>
       </c>
@@ -7854,10 +7932,22 @@
       <c r="A30" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="21" t="n">
+      <c r="B30" s="23" t="n">
         <v>401</v>
       </c>
-    </row>
+      <c r="E30" s="24" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7872,6 +7962,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J34"/>
@@ -7891,6 +7982,7 @@
         <v>85</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>86</v>
@@ -7941,39 +8033,39 @@
       <c r="A6" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="25" t="n">
         <f aca="false">Assumptions!B9</f>
         <v>71462</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">Assumptions!C9</f>
         <v>82419</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">Assumptions!D9</f>
         <v>83205</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">Assumptions!E9</f>
         <v>93190</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">Assumptions!F9</f>
         <v>109964</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">Assumptions!G9</f>
         <v>131957</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="25" t="n">
         <f aca="false">Assumptions!H9</f>
         <v>155710</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="25" t="n">
         <f aca="false">Assumptions!I9</f>
         <v>179067</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="25" t="n">
         <f aca="false">Assumptions!J9</f>
         <v>200555</v>
       </c>
@@ -7982,39 +8074,39 @@
       <c r="A7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="25" t="n">
         <f aca="false">Assumptions!B10</f>
         <v>3909</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="25" t="n">
         <f aca="false">Assumptions!C10</f>
         <v>6035</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="25" t="n">
         <f aca="false">Assumptions!D10</f>
         <v>10382</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">Assumptions!E10</f>
         <v>18791</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">Assumptions!F10</f>
         <v>30066</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <f aca="false">Assumptions!G10</f>
         <v>45099</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="25" t="n">
         <f aca="false">Assumptions!H10</f>
         <v>65393</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="25" t="n">
         <f aca="false">Assumptions!I10</f>
         <v>91550</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="25" t="n">
         <f aca="false">Assumptions!J10</f>
         <v>123593</v>
       </c>
@@ -8023,39 +8115,39 @@
       <c r="A8" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="25" t="n">
         <f aca="false">Assumptions!B11</f>
         <v>6091</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="25" t="n">
         <f aca="false">Assumptions!C11</f>
         <v>8319</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="25" t="n">
         <f aca="false">Assumptions!D11</f>
         <v>10467</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="25" t="n">
         <f aca="false">Assumptions!E11</f>
         <v>12560</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <f aca="false">Assumptions!F11</f>
         <v>15700</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="25" t="n">
         <f aca="false">Assumptions!G11</f>
         <v>19154</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="25" t="n">
         <f aca="false">Assumptions!H11</f>
         <v>22985</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="25" t="n">
         <f aca="false">Assumptions!I11</f>
         <v>27122</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="25" t="n">
         <f aca="false">Assumptions!J11</f>
         <v>31190</v>
       </c>
@@ -8064,39 +8156,39 @@
       <c r="A9" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B9" s="23" t="n">
+      <c r="B9" s="26" t="n">
         <f aca="false">SUM(B6:B8)</f>
         <v>81462</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">SUM(C6:C8)</f>
         <v>96773</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">SUM(D6:D8)</f>
         <v>104054</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">SUM(E6:E8)</f>
         <v>124541</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">SUM(F6:F8)</f>
         <v>155730</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="26" t="n">
         <f aca="false">SUM(G6:G8)</f>
         <v>196210</v>
       </c>
-      <c r="H9" s="23" t="n">
+      <c r="H9" s="26" t="n">
         <f aca="false">SUM(H6:H8)</f>
         <v>244088</v>
       </c>
-      <c r="I9" s="23" t="n">
+      <c r="I9" s="26" t="n">
         <f aca="false">SUM(I6:I8)</f>
         <v>297739</v>
       </c>
-      <c r="J9" s="23" t="n">
+      <c r="J9" s="26" t="n">
         <f aca="false">SUM(J6:J8)</f>
         <v>355338</v>
       </c>
@@ -8105,39 +8197,40 @@
       <c r="A10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="24" t="n">
-        <f aca="false">(C9-B9)/B9</f>
+      <c r="C10" s="27" t="n">
+        <f aca="false">IFERROR((C9-B9)/B9,0)</f>
         <v>0.187952665046279</v>
       </c>
-      <c r="D10" s="24" t="n">
-        <f aca="false">(D9-C9)/C9</f>
+      <c r="D10" s="27" t="n">
+        <f aca="false">IFERROR((D9-C9)/C9,0)</f>
         <v>0.0752379279344445</v>
       </c>
-      <c r="E10" s="24" t="n">
-        <f aca="false">(E9-D9)/D9</f>
+      <c r="E10" s="27" t="n">
+        <f aca="false">IFERROR((E9-D9)/D9,0)</f>
         <v>0.196888154227613</v>
       </c>
-      <c r="F10" s="24" t="n">
-        <f aca="false">(F9-E9)/E9</f>
+      <c r="F10" s="27" t="n">
+        <f aca="false">IFERROR((F9-E9)/E9,0)</f>
         <v>0.25043158477931</v>
       </c>
-      <c r="G10" s="24" t="n">
-        <f aca="false">(G9-F9)/F9</f>
+      <c r="G10" s="27" t="n">
+        <f aca="false">IFERROR((G9-F9)/F9,0)</f>
         <v>0.25993707057086</v>
       </c>
-      <c r="H10" s="24" t="n">
-        <f aca="false">(H9-G9)/G9</f>
+      <c r="H10" s="27" t="n">
+        <f aca="false">IFERROR((H9-G9)/G9,0)</f>
         <v>0.244014066561337</v>
       </c>
-      <c r="I10" s="24" t="n">
-        <f aca="false">(I9-H9)/H9</f>
+      <c r="I10" s="27" t="n">
+        <f aca="false">IFERROR((I9-H9)/H9,0)</f>
         <v>0.219801874733703</v>
       </c>
-      <c r="J10" s="24" t="n">
-        <f aca="false">(J9-I9)/I9</f>
+      <c r="J10" s="27" t="n">
+        <f aca="false">IFERROR((J9-I9)/I9,0)</f>
         <v>0.193454670029791</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>93</v>
@@ -8197,39 +8290,39 @@
       <c r="A14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="28" t="n">
         <f aca="false">B9+B13</f>
         <v>20854.272</v>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="28" t="n">
         <f aca="false">C9+C13</f>
         <v>17709.459</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="28" t="n">
         <f aca="false">D9+D13</f>
         <v>18521.612</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">E9+E13</f>
         <v>22666.462</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="28" t="n">
         <f aca="false">F9+F13</f>
         <v>30367.35</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="28" t="n">
         <f aca="false">G9+G13</f>
         <v>41204.1</v>
       </c>
-      <c r="H14" s="25" t="n">
+      <c r="H14" s="28" t="n">
         <f aca="false">H9+H13</f>
         <v>54919.8</v>
       </c>
-      <c r="I14" s="25" t="n">
+      <c r="I14" s="28" t="n">
         <f aca="false">I9+I13</f>
         <v>69968.665</v>
       </c>
-      <c r="J14" s="25" t="n">
+      <c r="J14" s="28" t="n">
         <f aca="false">J9+J13</f>
         <v>87057.81</v>
       </c>
@@ -8238,43 +8331,44 @@
       <c r="A15" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="24" t="n">
-        <f aca="false">B14/B9</f>
+      <c r="B15" s="27" t="n">
+        <f aca="false">IFERROR(B14/B9,0)</f>
         <v>0.256</v>
       </c>
-      <c r="C15" s="24" t="n">
-        <f aca="false">C14/C9</f>
+      <c r="C15" s="27" t="n">
+        <f aca="false">IFERROR(C14/C9,0)</f>
         <v>0.183</v>
       </c>
-      <c r="D15" s="24" t="n">
-        <f aca="false">D14/D9</f>
+      <c r="D15" s="27" t="n">
+        <f aca="false">IFERROR(D14/D9,0)</f>
         <v>0.178</v>
       </c>
-      <c r="E15" s="24" t="n">
-        <f aca="false">E14/E9</f>
+      <c r="E15" s="27" t="n">
+        <f aca="false">IFERROR(E14/E9,0)</f>
         <v>0.182</v>
       </c>
-      <c r="F15" s="24" t="n">
-        <f aca="false">F14/F9</f>
+      <c r="F15" s="27" t="n">
+        <f aca="false">IFERROR(F14/F9,0)</f>
         <v>0.195</v>
       </c>
-      <c r="G15" s="24" t="n">
-        <f aca="false">G14/G9</f>
+      <c r="G15" s="27" t="n">
+        <f aca="false">IFERROR(G14/G9,0)</f>
         <v>0.21</v>
       </c>
-      <c r="H15" s="24" t="n">
-        <f aca="false">H14/H9</f>
+      <c r="H15" s="27" t="n">
+        <f aca="false">IFERROR(H14/H9,0)</f>
         <v>0.225</v>
       </c>
-      <c r="I15" s="24" t="n">
-        <f aca="false">I14/I9</f>
+      <c r="I15" s="27" t="n">
+        <f aca="false">IFERROR(I14/I9,0)</f>
         <v>0.235</v>
       </c>
-      <c r="J15" s="24" t="n">
-        <f aca="false">J14/J9</f>
+      <c r="J15" s="27" t="n">
+        <f aca="false">IFERROR(J14/J9,0)</f>
         <v>0.245</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
         <v>97</v>
@@ -8416,80 +8510,81 @@
       <c r="A21" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="28" t="n">
         <f aca="false">SUM(B18:B20)</f>
         <v>-10997.37</v>
       </c>
-      <c r="C21" s="25" t="n">
+      <c r="C21" s="28" t="n">
         <f aca="false">SUM(C18:C20)</f>
         <v>-12967.582</v>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="28" t="n">
         <f aca="false">SUM(D18:D20)</f>
         <v>-13735.128</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">SUM(E18:E20)</f>
         <v>-15692.166</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="28" t="n">
         <f aca="false">SUM(F18:F20)</f>
         <v>-18687.6</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="28" t="n">
         <f aca="false">SUM(G18:G20)</f>
         <v>-22367.94</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="28" t="n">
         <f aca="false">SUM(H18:H20)</f>
         <v>-26361.504</v>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I21" s="28" t="n">
         <f aca="false">SUM(I18:I20)</f>
         <v>-30369.378</v>
       </c>
-      <c r="J21" s="25" t="n">
+      <c r="J21" s="28" t="n">
         <f aca="false">SUM(J18:J20)</f>
         <v>-34823.124</v>
       </c>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="23" t="n">
+      <c r="B23" s="26" t="n">
         <f aca="false">B14+B21</f>
         <v>9856.902</v>
       </c>
-      <c r="C23" s="23" t="n">
+      <c r="C23" s="26" t="n">
         <f aca="false">C14+C21</f>
         <v>4741.877</v>
       </c>
-      <c r="D23" s="23" t="n">
+      <c r="D23" s="26" t="n">
         <f aca="false">D14+D21</f>
         <v>4786.48399999999</v>
       </c>
-      <c r="E23" s="23" t="n">
+      <c r="E23" s="26" t="n">
         <f aca="false">E14+E21</f>
         <v>6974.296</v>
       </c>
-      <c r="F23" s="23" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">F14+F21</f>
         <v>11679.75</v>
       </c>
-      <c r="G23" s="23" t="n">
+      <c r="G23" s="26" t="n">
         <f aca="false">G14+G21</f>
         <v>18836.16</v>
       </c>
-      <c r="H23" s="23" t="n">
+      <c r="H23" s="26" t="n">
         <f aca="false">H14+H21</f>
         <v>28558.296</v>
       </c>
-      <c r="I23" s="23" t="n">
+      <c r="I23" s="26" t="n">
         <f aca="false">I14+I21</f>
         <v>39599.287</v>
       </c>
-      <c r="J23" s="23" t="n">
+      <c r="J23" s="26" t="n">
         <f aca="false">J14+J21</f>
         <v>52234.686</v>
       </c>
@@ -8498,43 +8593,44 @@
       <c r="A24" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="24" t="n">
-        <f aca="false">B23/B9</f>
+      <c r="B24" s="27" t="n">
+        <f aca="false">IFERROR(B23/B9,0)</f>
         <v>0.121</v>
       </c>
-      <c r="C24" s="24" t="n">
-        <f aca="false">C23/C9</f>
+      <c r="C24" s="27" t="n">
+        <f aca="false">IFERROR(C23/C9,0)</f>
         <v>0.049</v>
       </c>
-      <c r="D24" s="24" t="n">
-        <f aca="false">D23/D9</f>
+      <c r="D24" s="27" t="n">
+        <f aca="false">IFERROR(D23/D9,0)</f>
         <v>0.0459999999999999</v>
       </c>
-      <c r="E24" s="24" t="n">
-        <f aca="false">E23/E9</f>
+      <c r="E24" s="27" t="n">
+        <f aca="false">IFERROR(E23/E9,0)</f>
         <v>0.056</v>
       </c>
-      <c r="F24" s="24" t="n">
-        <f aca="false">F23/F9</f>
+      <c r="F24" s="27" t="n">
+        <f aca="false">IFERROR(F23/F9,0)</f>
         <v>0.0750000000000001</v>
       </c>
-      <c r="G24" s="24" t="n">
-        <f aca="false">G23/G9</f>
+      <c r="G24" s="27" t="n">
+        <f aca="false">IFERROR(G23/G9,0)</f>
         <v>0.096</v>
       </c>
-      <c r="H24" s="24" t="n">
-        <f aca="false">H23/H9</f>
+      <c r="H24" s="27" t="n">
+        <f aca="false">IFERROR(H23/H9,0)</f>
         <v>0.117</v>
       </c>
-      <c r="I24" s="24" t="n">
-        <f aca="false">I23/I9</f>
+      <c r="I24" s="27" t="n">
+        <f aca="false">IFERROR(I23/I9,0)</f>
         <v>0.133</v>
       </c>
-      <c r="J24" s="24" t="n">
-        <f aca="false">J23/J9</f>
+      <c r="J24" s="27" t="n">
+        <f aca="false">IFERROR(J23/J9,0)</f>
         <v>0.147</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>104</v>
@@ -8571,39 +8667,39 @@
       <c r="A27" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="26" t="n">
+      <c r="B27" s="29" t="n">
         <f aca="false">B23+B26</f>
         <v>9556.902</v>
       </c>
-      <c r="C27" s="26" t="n">
+      <c r="C27" s="29" t="n">
         <f aca="false">C23+C26</f>
         <v>4441.877</v>
       </c>
-      <c r="D27" s="26" t="n">
+      <c r="D27" s="29" t="n">
         <f aca="false">D23+D26</f>
         <v>4486.48399999999</v>
       </c>
-      <c r="E27" s="26" t="n">
+      <c r="E27" s="29" t="n">
         <f aca="false">E23+E26</f>
         <v>6674.296</v>
       </c>
-      <c r="F27" s="26" t="n">
+      <c r="F27" s="29" t="n">
         <f aca="false">F23+F26</f>
         <v>11379.75</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="29" t="n">
         <f aca="false">G23+G26</f>
         <v>18536.16</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="29" t="n">
         <f aca="false">H23+H26</f>
         <v>28258.296</v>
       </c>
-      <c r="I27" s="26" t="n">
+      <c r="I27" s="29" t="n">
         <f aca="false">I23+I26</f>
         <v>39299.287</v>
       </c>
-      <c r="J27" s="26" t="n">
+      <c r="J27" s="29" t="n">
         <f aca="false">J23+J26</f>
         <v>51934.686</v>
       </c>
@@ -8649,43 +8745,44 @@
         <v>-9348.24348</v>
       </c>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="B30" s="28" t="n">
+      <c r="B30" s="31" t="n">
         <f aca="false">B27+B28</f>
         <v>8792.34984</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="31" t="n">
         <f aca="false">C27+C28</f>
         <v>3997.6893</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="31" t="n">
         <f aca="false">D27+D28</f>
         <v>3948.10591999999</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E30" s="31" t="n">
         <f aca="false">E27+E28</f>
         <v>5739.89456</v>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="31" t="n">
         <f aca="false">F27+F28</f>
         <v>9672.78750000001</v>
       </c>
-      <c r="G30" s="28" t="n">
+      <c r="G30" s="31" t="n">
         <f aca="false">G27+G28</f>
         <v>15570.3744</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="31" t="n">
         <f aca="false">H27+H28</f>
         <v>23454.38568</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="31" t="n">
         <f aca="false">I27+I28</f>
         <v>32225.41534</v>
       </c>
-      <c r="J30" s="28" t="n">
+      <c r="J30" s="31" t="n">
         <f aca="false">J27+J28</f>
         <v>42586.44252</v>
       </c>
@@ -8694,80 +8791,81 @@
       <c r="A31" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="32" t="n">
         <f aca="false">IFERROR(B30/Assumptions!B25,0)</f>
         <v>2.53017261582734</v>
       </c>
-      <c r="C31" s="29" t="n">
-        <f aca="false">C30/Assumptions!C24</f>
+      <c r="C31" s="32" t="n">
+        <f aca="false">IFERROR(C30/Assumptions!C24,0)</f>
         <v>133256.31</v>
       </c>
-      <c r="D31" s="29" t="n">
-        <f aca="false">D30/Assumptions!D24</f>
+      <c r="D31" s="32" t="n">
+        <f aca="false">IFERROR(D30/Assumptions!D24,0)</f>
         <v>131603.530666666</v>
       </c>
-      <c r="E31" s="29" t="n">
-        <f aca="false">E30/Assumptions!E24</f>
+      <c r="E31" s="32" t="n">
+        <f aca="false">IFERROR(E30/Assumptions!E24,0)</f>
         <v>191329.818666667</v>
       </c>
-      <c r="F31" s="29" t="n">
-        <f aca="false">F30/Assumptions!F24</f>
+      <c r="F31" s="32" t="n">
+        <f aca="false">IFERROR(F30/Assumptions!F24,0)</f>
         <v>322426.25</v>
       </c>
-      <c r="G31" s="29" t="n">
-        <f aca="false">G30/Assumptions!G24</f>
+      <c r="G31" s="32" t="n">
+        <f aca="false">IFERROR(G30/Assumptions!G24,0)</f>
         <v>519012.48</v>
       </c>
-      <c r="H31" s="29" t="n">
-        <f aca="false">H30/Assumptions!H24</f>
+      <c r="H31" s="32" t="n">
+        <f aca="false">IFERROR(H30/Assumptions!H24,0)</f>
         <v>781812.856</v>
       </c>
-      <c r="I31" s="29" t="n">
-        <f aca="false">I30/Assumptions!I24</f>
+      <c r="I31" s="32" t="n">
+        <f aca="false">IFERROR(I30/Assumptions!I24,0)</f>
         <v>1074180.51133333</v>
       </c>
-      <c r="J31" s="29" t="n">
-        <f aca="false">J30/Assumptions!J24</f>
+      <c r="J31" s="32" t="n">
+        <f aca="false">IFERROR(J30/Assumptions!J24,0)</f>
         <v>1419548.084</v>
       </c>
     </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="26" t="n">
         <f aca="false">B23-B20</f>
         <v>13522.692</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="26" t="n">
         <f aca="false">C23-C20</f>
         <v>9386.981</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="26" t="n">
         <f aca="false">D23-D20</f>
         <v>9989.18399999999</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="26" t="n">
         <f aca="false">E23-E20</f>
         <v>12952.264</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="26" t="n">
         <f aca="false">F23-F20</f>
         <v>18843.33</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="26" t="n">
         <f aca="false">G23-G20</f>
         <v>27469.4</v>
       </c>
-      <c r="H33" s="23" t="n">
+      <c r="H33" s="26" t="n">
         <f aca="false">H23-H20</f>
         <v>38809.992</v>
       </c>
-      <c r="I33" s="23" t="n">
+      <c r="I33" s="26" t="n">
         <f aca="false">I23-I20</f>
         <v>51508.847</v>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="J33" s="26" t="n">
         <f aca="false">J23-J20</f>
         <v>65737.53</v>
       </c>
@@ -8776,40 +8874,40 @@
       <c r="A34" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="24" t="n">
-        <f aca="false">B33/B9</f>
+      <c r="B34" s="27" t="n">
+        <f aca="false">IFERROR(B33/B9,0)</f>
         <v>0.166</v>
       </c>
-      <c r="C34" s="24" t="n">
-        <f aca="false">C33/C9</f>
+      <c r="C34" s="27" t="n">
+        <f aca="false">IFERROR(C33/C9,0)</f>
         <v>0.097</v>
       </c>
-      <c r="D34" s="24" t="n">
-        <f aca="false">D33/D9</f>
+      <c r="D34" s="27" t="n">
+        <f aca="false">IFERROR(D33/D9,0)</f>
         <v>0.096</v>
       </c>
-      <c r="E34" s="24" t="n">
-        <f aca="false">E33/E9</f>
+      <c r="E34" s="27" t="n">
+        <f aca="false">IFERROR(E33/E9,0)</f>
         <v>0.104</v>
       </c>
-      <c r="F34" s="24" t="n">
-        <f aca="false">F33/F9</f>
+      <c r="F34" s="27" t="n">
+        <f aca="false">IFERROR(F33/F9,0)</f>
         <v>0.121</v>
       </c>
-      <c r="G34" s="24" t="n">
-        <f aca="false">G33/G9</f>
+      <c r="G34" s="27" t="n">
+        <f aca="false">IFERROR(G33/G9,0)</f>
         <v>0.14</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <f aca="false">H33/H9</f>
+      <c r="H34" s="27" t="n">
+        <f aca="false">IFERROR(H33/H9,0)</f>
         <v>0.159</v>
       </c>
-      <c r="I34" s="24" t="n">
-        <f aca="false">I33/I9</f>
+      <c r="I34" s="27" t="n">
+        <f aca="false">IFERROR(I33/I9,0)</f>
         <v>0.173</v>
       </c>
-      <c r="J34" s="24" t="n">
-        <f aca="false">J33/J9</f>
+      <c r="J34" s="27" t="n">
+        <f aca="false">IFERROR(J33/J9,0)</f>
         <v>0.185</v>
       </c>
     </row>
@@ -8827,6 +8925,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
@@ -8846,6 +8945,7 @@
         <v>112</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>113</v>
@@ -8905,22 +9005,22 @@
       <c r="D6" s="16" t="n">
         <v>33648</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="33" t="n">
         <v>36600</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="33" t="n">
         <v>42000</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="33" t="n">
         <v>50000</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="33" t="n">
         <v>60000</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="33" t="n">
         <v>72000</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="33" t="n">
         <v>86000</v>
       </c>
     </row>
@@ -8937,22 +9037,22 @@
       <c r="D7" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="30" t="n">
+      <c r="G7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="30" t="n">
+      <c r="H7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="30" t="n">
+      <c r="I7" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="30" t="n">
+      <c r="J7" s="33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8969,22 +9069,22 @@
       <c r="D8" s="16" t="n">
         <v>4140</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="33" t="n">
         <v>4700</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="33" t="n">
         <v>5500</v>
       </c>
-      <c r="G8" s="30" t="n">
+      <c r="G8" s="33" t="n">
         <v>6500</v>
       </c>
-      <c r="H8" s="30" t="n">
+      <c r="H8" s="33" t="n">
         <v>7600</v>
       </c>
-      <c r="I8" s="30" t="n">
+      <c r="I8" s="33" t="n">
         <v>8800</v>
       </c>
-      <c r="J8" s="30" t="n">
+      <c r="J8" s="33" t="n">
         <v>10000</v>
       </c>
     </row>
@@ -9001,22 +9101,22 @@
       <c r="D9" s="16" t="n">
         <v>14000</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="33" t="n">
         <v>15200</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="33" t="n">
         <v>17500</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="33" t="n">
         <v>20000</v>
       </c>
-      <c r="H9" s="30" t="n">
+      <c r="H9" s="33" t="n">
         <v>23000</v>
       </c>
-      <c r="I9" s="30" t="n">
+      <c r="I9" s="33" t="n">
         <v>26000</v>
       </c>
-      <c r="J9" s="30" t="n">
+      <c r="J9" s="33" t="n">
         <v>29000</v>
       </c>
     </row>
@@ -9033,22 +9133,22 @@
       <c r="D10" s="16" t="n">
         <v>3800</v>
       </c>
-      <c r="E10" s="30" t="n">
+      <c r="E10" s="33" t="n">
         <v>4200</v>
       </c>
-      <c r="F10" s="30" t="n">
+      <c r="F10" s="33" t="n">
         <v>4800</v>
       </c>
-      <c r="G10" s="30" t="n">
+      <c r="G10" s="33" t="n">
         <v>5500</v>
       </c>
-      <c r="H10" s="30" t="n">
+      <c r="H10" s="33" t="n">
         <v>6200</v>
       </c>
-      <c r="I10" s="30" t="n">
+      <c r="I10" s="33" t="n">
         <v>7000</v>
       </c>
-      <c r="J10" s="30" t="n">
+      <c r="J10" s="33" t="n">
         <v>7800</v>
       </c>
     </row>
@@ -9056,43 +9156,44 @@
       <c r="A11" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="28" t="n">
         <f aca="false">SUM(B6:B10)</f>
         <v>40917</v>
       </c>
-      <c r="C11" s="25" t="n">
+      <c r="C11" s="28" t="n">
         <f aca="false">SUM(C6:C10)</f>
         <v>49616</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="28" t="n">
         <f aca="false">SUM(D6:D10)</f>
         <v>55588</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="28" t="n">
         <f aca="false">SUM(E6:E10)</f>
         <v>60700</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="28" t="n">
         <f aca="false">SUM(F6:F10)</f>
         <v>69800</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="28" t="n">
         <f aca="false">SUM(G6:G10)</f>
         <v>82000</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="28" t="n">
         <f aca="false">SUM(H6:H10)</f>
         <v>96800</v>
       </c>
-      <c r="I11" s="25" t="n">
+      <c r="I11" s="28" t="n">
         <f aca="false">SUM(I6:I10)</f>
         <v>113800</v>
       </c>
-      <c r="J11" s="25" t="n">
+      <c r="J11" s="28" t="n">
         <f aca="false">SUM(J6:J10)</f>
         <v>132800</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>121</v>
@@ -9120,22 +9221,22 @@
       <c r="D14" s="16" t="n">
         <v>32000</v>
       </c>
-      <c r="E14" s="30" t="n">
+      <c r="E14" s="33" t="n">
         <v>35000</v>
       </c>
-      <c r="F14" s="30" t="n">
+      <c r="F14" s="33" t="n">
         <v>39000</v>
       </c>
-      <c r="G14" s="30" t="n">
+      <c r="G14" s="33" t="n">
         <v>43000</v>
       </c>
-      <c r="H14" s="30" t="n">
+      <c r="H14" s="33" t="n">
         <v>47000</v>
       </c>
-      <c r="I14" s="30" t="n">
+      <c r="I14" s="33" t="n">
         <v>51000</v>
       </c>
-      <c r="J14" s="30" t="n">
+      <c r="J14" s="33" t="n">
         <v>55000</v>
       </c>
     </row>
@@ -9152,22 +9253,22 @@
       <c r="D15" s="16" t="n">
         <v>400</v>
       </c>
-      <c r="E15" s="30" t="n">
+      <c r="E15" s="33" t="n">
         <v>400</v>
       </c>
-      <c r="F15" s="30" t="n">
+      <c r="F15" s="33" t="n">
         <v>400</v>
       </c>
-      <c r="G15" s="30" t="n">
+      <c r="G15" s="33" t="n">
         <v>400</v>
       </c>
-      <c r="H15" s="30" t="n">
+      <c r="H15" s="33" t="n">
         <v>400</v>
       </c>
-      <c r="I15" s="30" t="n">
+      <c r="I15" s="33" t="n">
         <v>400</v>
       </c>
-      <c r="J15" s="30" t="n">
+      <c r="J15" s="33" t="n">
         <v>400</v>
       </c>
     </row>
@@ -9184,66 +9285,68 @@
       <c r="D16" s="16" t="n">
         <v>7000</v>
       </c>
-      <c r="E16" s="30" t="n">
+      <c r="E16" s="33" t="n">
         <v>7500</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F16" s="33" t="n">
         <v>8000</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G16" s="33" t="n">
         <v>8500</v>
       </c>
-      <c r="H16" s="30" t="n">
+      <c r="H16" s="33" t="n">
         <v>9000</v>
       </c>
-      <c r="I16" s="30" t="n">
+      <c r="I16" s="33" t="n">
         <v>9500</v>
       </c>
-      <c r="J16" s="30" t="n">
+      <c r="J16" s="33" t="n">
         <v>10000</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="31" t="n">
         <f aca="false">B11+SUM(B14:B16)</f>
         <v>84412</v>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="31" t="n">
         <f aca="false">C11+SUM(C14:C16)</f>
         <v>85935</v>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="31" t="n">
         <f aca="false">D11+SUM(D14:D16)</f>
         <v>94988</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="31" t="n">
         <f aca="false">E11+SUM(E14:E16)</f>
         <v>103600</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="31" t="n">
         <f aca="false">F11+SUM(F14:F16)</f>
         <v>117200</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="31" t="n">
         <f aca="false">G11+SUM(G14:G16)</f>
         <v>133900</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="31" t="n">
         <f aca="false">H11+SUM(H14:H16)</f>
         <v>153200</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="31" t="n">
         <f aca="false">I11+SUM(I14:I16)</f>
         <v>174700</v>
       </c>
-      <c r="J18" s="28" t="n">
+      <c r="J18" s="31" t="n">
         <f aca="false">J11+SUM(J14:J16)</f>
         <v>198200</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>126</v>
@@ -9358,43 +9461,44 @@
       <c r="A24" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="25" t="n">
+      <c r="B24" s="28" t="n">
         <f aca="false">SUM(B21:B23)</f>
         <v>23899</v>
       </c>
-      <c r="C24" s="25" t="n">
+      <c r="C24" s="28" t="n">
         <f aca="false">SUM(C21:C23)</f>
         <v>25884</v>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="28" t="n">
         <f aca="false">SUM(D21:D23)</f>
         <v>27000</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="28" t="n">
         <f aca="false">SUM(E21:E23)</f>
         <v>29500</v>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="28" t="n">
         <f aca="false">SUM(F21:F23)</f>
         <v>33500</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="28" t="n">
         <f aca="false">SUM(G21:G23)</f>
         <v>38500</v>
       </c>
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="28" t="n">
         <f aca="false">SUM(H21:H23)</f>
         <v>43500</v>
       </c>
-      <c r="I24" s="25" t="n">
+      <c r="I24" s="28" t="n">
         <f aca="false">SUM(I21:I23)</f>
         <v>48500</v>
       </c>
-      <c r="J24" s="25" t="n">
+      <c r="J24" s="28" t="n">
         <f aca="false">SUM(J21:J23)</f>
         <v>53500</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>131</v>
@@ -9473,47 +9577,49 @@
         <v>8000</v>
       </c>
     </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="27" t="s">
+      <c r="A30" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="28" t="n">
+      <c r="B30" s="31" t="n">
         <f aca="false">B24+B27+B28</f>
         <v>35199</v>
       </c>
-      <c r="C30" s="28" t="n">
+      <c r="C30" s="31" t="n">
         <f aca="false">C24+C27+C28</f>
         <v>37184</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="31" t="n">
         <f aca="false">D24+D27+D28</f>
         <v>38300</v>
       </c>
-      <c r="E30" s="28" t="n">
+      <c r="E30" s="31" t="n">
         <f aca="false">E24+E27+E28</f>
         <v>40800</v>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="F30" s="31" t="n">
         <f aca="false">F24+F27+F28</f>
         <v>44800</v>
       </c>
-      <c r="G30" s="28" t="n">
+      <c r="G30" s="31" t="n">
         <f aca="false">G24+G27+G28</f>
         <v>49800</v>
       </c>
-      <c r="H30" s="28" t="n">
+      <c r="H30" s="31" t="n">
         <f aca="false">H24+H27+H28</f>
         <v>54800</v>
       </c>
-      <c r="I30" s="28" t="n">
+      <c r="I30" s="31" t="n">
         <f aca="false">I24+I27+I28</f>
         <v>59800</v>
       </c>
-      <c r="J30" s="28" t="n">
+      <c r="J30" s="31" t="n">
         <f aca="false">J24+J27+J28</f>
         <v>64800</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
         <v>135</v>
@@ -9532,80 +9638,81 @@
       <c r="A33" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B33" s="23" t="n">
+      <c r="B33" s="26" t="n">
         <f aca="false">B18-B30</f>
         <v>49213</v>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="26" t="n">
         <f aca="false">C18-C30</f>
         <v>48751</v>
       </c>
-      <c r="D33" s="23" t="n">
+      <c r="D33" s="26" t="n">
         <f aca="false">D18-D30</f>
         <v>56688</v>
       </c>
-      <c r="E33" s="23" t="n">
+      <c r="E33" s="26" t="n">
         <f aca="false">E18-E30</f>
         <v>62800</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="26" t="n">
         <f aca="false">F18-F30</f>
         <v>72400</v>
       </c>
-      <c r="G33" s="23" t="n">
+      <c r="G33" s="26" t="n">
         <f aca="false">G18-G30</f>
         <v>84100</v>
       </c>
-      <c r="H33" s="23" t="n">
+      <c r="H33" s="26" t="n">
         <f aca="false">H18-H30</f>
         <v>98400</v>
       </c>
-      <c r="I33" s="23" t="n">
+      <c r="I33" s="26" t="n">
         <f aca="false">I18-I30</f>
         <v>114900</v>
       </c>
-      <c r="J33" s="23" t="n">
+      <c r="J33" s="26" t="n">
         <f aca="false">J18-J30</f>
         <v>133400</v>
       </c>
     </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="35" t="n">
         <f aca="false">B18-B30-B33</f>
         <v>0</v>
       </c>
-      <c r="C35" s="32" t="n">
+      <c r="C35" s="35" t="n">
         <f aca="false">C18-C30-C33</f>
         <v>0</v>
       </c>
-      <c r="D35" s="32" t="n">
+      <c r="D35" s="35" t="n">
         <f aca="false">D18-D30-D33</f>
         <v>0</v>
       </c>
-      <c r="E35" s="32" t="n">
+      <c r="E35" s="35" t="n">
         <f aca="false">E18-E30-E33</f>
         <v>0</v>
       </c>
-      <c r="F35" s="32" t="n">
+      <c r="F35" s="35" t="n">
         <f aca="false">F18-F30-F33</f>
         <v>0</v>
       </c>
-      <c r="G35" s="32" t="n">
+      <c r="G35" s="35" t="n">
         <f aca="false">G18-G30-G33</f>
         <v>0</v>
       </c>
-      <c r="H35" s="32" t="n">
+      <c r="H35" s="35" t="n">
         <f aca="false">H18-H30-H33</f>
         <v>0</v>
       </c>
-      <c r="I35" s="32" t="n">
+      <c r="I35" s="35" t="n">
         <f aca="false">I18-I30-I33</f>
         <v>0</v>
       </c>
-      <c r="J35" s="32" t="n">
+      <c r="J35" s="35" t="n">
         <f aca="false">J18-J30-J33</f>
         <v>0</v>
       </c>
@@ -9624,6 +9731,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF4472C4"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J21"/>
@@ -9643,6 +9751,7 @@
         <v>112</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>139</v>
@@ -9693,39 +9802,39 @@
       <c r="A6" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B6" s="22" t="n">
+      <c r="B6" s="25" t="n">
         <f aca="false">'Income Statement'!B30</f>
         <v>8792.34984</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="25" t="n">
         <f aca="false">'Income Statement'!C30</f>
         <v>3997.6893</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">'Income Statement'!D30</f>
         <v>3948.10591999999</v>
       </c>
-      <c r="E6" s="22" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">'Income Statement'!E30</f>
         <v>5739.89456</v>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">'Income Statement'!F30</f>
         <v>9672.78750000001</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">'Income Statement'!G30</f>
         <v>15570.3744</v>
       </c>
-      <c r="H6" s="22" t="n">
+      <c r="H6" s="25" t="n">
         <f aca="false">'Income Statement'!H30</f>
         <v>23454.38568</v>
       </c>
-      <c r="I6" s="22" t="n">
+      <c r="I6" s="25" t="n">
         <f aca="false">'Income Statement'!I30</f>
         <v>32225.41534</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="25" t="n">
         <f aca="false">'Income Statement'!J30</f>
         <v>42586.44252</v>
       </c>
@@ -9734,39 +9843,39 @@
       <c r="A7" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B7" s="22" t="n">
+      <c r="B7" s="25" t="n">
         <f aca="false">-'Income Statement'!B20</f>
         <v>3665.79</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="25" t="n">
         <f aca="false">-'Income Statement'!C20</f>
         <v>4645.104</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="25" t="n">
         <f aca="false">-'Income Statement'!D20</f>
         <v>5202.7</v>
       </c>
-      <c r="E7" s="22" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">-'Income Statement'!E20</f>
         <v>5977.968</v>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">-'Income Statement'!F20</f>
         <v>7163.58</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <f aca="false">-'Income Statement'!G20</f>
         <v>8633.24</v>
       </c>
-      <c r="H7" s="22" t="n">
+      <c r="H7" s="25" t="n">
         <f aca="false">-'Income Statement'!H20</f>
         <v>10251.696</v>
       </c>
-      <c r="I7" s="22" t="n">
+      <c r="I7" s="25" t="n">
         <f aca="false">-'Income Statement'!I20</f>
         <v>11909.56</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="25" t="n">
         <f aca="false">-'Income Statement'!J20</f>
         <v>13502.844</v>
       </c>
@@ -9840,47 +9949,49 @@
         <v>-3167.945</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B11" s="23" t="n">
+      <c r="B11" s="26" t="n">
         <f aca="false">SUM(B6:B9)</f>
         <v>14018.13984</v>
       </c>
-      <c r="C11" s="23" t="n">
+      <c r="C11" s="26" t="n">
         <f aca="false">SUM(C6:C9)</f>
         <v>9288.4683</v>
       </c>
-      <c r="D11" s="23" t="n">
+      <c r="D11" s="26" t="n">
         <f aca="false">SUM(D6:D9)</f>
         <v>10531.92092</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="26" t="n">
         <f aca="false">SUM(E6:E9)</f>
         <v>12278.90256</v>
       </c>
-      <c r="F11" s="23" t="n">
+      <c r="F11" s="26" t="n">
         <f aca="false">SUM(F6:F9)</f>
         <v>16997.1925</v>
       </c>
-      <c r="G11" s="23" t="n">
+      <c r="G11" s="26" t="n">
         <f aca="false">SUM(G6:G9)</f>
         <v>24170.0144</v>
       </c>
-      <c r="H11" s="23" t="n">
+      <c r="H11" s="26" t="n">
         <f aca="false">SUM(H6:H9)</f>
         <v>33694.01168</v>
       </c>
-      <c r="I11" s="23" t="n">
+      <c r="I11" s="26" t="n">
         <f aca="false">SUM(I6:I9)</f>
         <v>44315.91534</v>
       </c>
-      <c r="J11" s="23" t="n">
+      <c r="J11" s="26" t="n">
         <f aca="false">SUM(J6:J9)</f>
         <v>56621.34152</v>
       </c>
     </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>146</v>
@@ -9968,84 +10079,86 @@
         <v>-500</v>
       </c>
     </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="23" t="n">
+      <c r="B17" s="26" t="n">
         <f aca="false">B14+B15</f>
         <v>-500</v>
       </c>
-      <c r="C17" s="23" t="n">
+      <c r="C17" s="26" t="n">
         <f aca="false">C14+C15</f>
         <v>-500</v>
       </c>
-      <c r="D17" s="23" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">D14+D15</f>
         <v>-500</v>
       </c>
-      <c r="E17" s="23" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">E14+E15</f>
         <v>-500</v>
       </c>
-      <c r="F17" s="23" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">F14+F15</f>
         <v>-500</v>
       </c>
-      <c r="G17" s="23" t="n">
+      <c r="G17" s="26" t="n">
         <f aca="false">G14+G15</f>
         <v>-500</v>
       </c>
-      <c r="H17" s="23" t="n">
+      <c r="H17" s="26" t="n">
         <f aca="false">H14+H15</f>
         <v>-500</v>
       </c>
-      <c r="I17" s="23" t="n">
+      <c r="I17" s="26" t="n">
         <f aca="false">I14+I15</f>
         <v>-500</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="26" t="n">
         <f aca="false">J14+J15</f>
         <v>-500</v>
       </c>
     </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="B19" s="28" t="n">
+      <c r="B19" s="31" t="n">
         <f aca="false">B11+B14</f>
         <v>14018.13984</v>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="31" t="n">
         <f aca="false">C11+C14</f>
         <v>9288.4683</v>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="31" t="n">
         <f aca="false">D11+D14</f>
         <v>10531.92092</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="31" t="n">
         <f aca="false">E11+E14</f>
         <v>12278.90256</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="31" t="n">
         <f aca="false">F11+F14</f>
         <v>16997.1925</v>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="31" t="n">
         <f aca="false">G11+G14</f>
         <v>24170.0144</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="31" t="n">
         <f aca="false">H11+H14</f>
         <v>33694.01168</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="31" t="n">
         <f aca="false">I11+I14</f>
         <v>44315.91534</v>
       </c>
-      <c r="J19" s="28" t="n">
+      <c r="J19" s="31" t="n">
         <f aca="false">J11+J14</f>
         <v>56621.34152</v>
       </c>
@@ -10054,40 +10167,40 @@
       <c r="A20" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B20" s="24" t="n">
-        <f aca="false">B19/'Income Statement'!B9</f>
+      <c r="B20" s="27" t="n">
+        <f aca="false">IFERROR(B19/'Income Statement'!B9,0)</f>
         <v>0.172081950357222</v>
       </c>
-      <c r="C20" s="24" t="n">
-        <f aca="false">C19/'Income Statement'!C9</f>
+      <c r="C20" s="27" t="n">
+        <f aca="false">IFERROR(C19/'Income Statement'!C9,0)</f>
         <v>0.0959820228782822</v>
       </c>
-      <c r="D20" s="24" t="n">
-        <f aca="false">D19/'Income Statement'!D9</f>
+      <c r="D20" s="27" t="n">
+        <f aca="false">IFERROR(D19/'Income Statement'!D9,0)</f>
         <v>0.10121591596671</v>
       </c>
-      <c r="E20" s="24" t="n">
-        <f aca="false">E19/'Income Statement'!E9</f>
+      <c r="E20" s="27" t="n">
+        <f aca="false">IFERROR(E19/'Income Statement'!E9,0)</f>
         <v>0.098593254912037</v>
       </c>
-      <c r="F20" s="24" t="n">
-        <f aca="false">F19/'Income Statement'!F9</f>
+      <c r="F20" s="27" t="n">
+        <f aca="false">IFERROR(F19/'Income Statement'!F9,0)</f>
         <v>0.109145267450074</v>
       </c>
-      <c r="G20" s="24" t="n">
-        <f aca="false">G19/'Income Statement'!G9</f>
+      <c r="G20" s="27" t="n">
+        <f aca="false">IFERROR(G19/'Income Statement'!G9,0)</f>
         <v>0.123184416696397</v>
       </c>
-      <c r="H20" s="24" t="n">
-        <f aca="false">H19/'Income Statement'!H9</f>
+      <c r="H20" s="27" t="n">
+        <f aca="false">IFERROR(H19/'Income Statement'!H9,0)</f>
         <v>0.138040426731343</v>
       </c>
-      <c r="I20" s="24" t="n">
-        <f aca="false">I19/'Income Statement'!I9</f>
+      <c r="I20" s="27" t="n">
+        <f aca="false">IFERROR(I19/'Income Statement'!I9,0)</f>
         <v>0.148841486469693</v>
       </c>
-      <c r="J20" s="24" t="n">
-        <f aca="false">J19/'Income Statement'!J9</f>
+      <c r="J20" s="27" t="n">
+        <f aca="false">IFERROR(J19/'Income Statement'!J9,0)</f>
         <v>0.159345022260496</v>
       </c>
     </row>
@@ -10095,40 +10208,40 @@
       <c r="A21" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="36" t="n">
         <f aca="false">IFERROR(B19/Assumptions!B25,0)</f>
         <v>4.03399707625899</v>
       </c>
-      <c r="C21" s="33" t="n">
-        <f aca="false">C19/Assumptions!C24</f>
+      <c r="C21" s="36" t="n">
+        <f aca="false">IFERROR(C19/Assumptions!C24,0)</f>
         <v>309615.61</v>
       </c>
-      <c r="D21" s="33" t="n">
-        <f aca="false">D19/Assumptions!D24</f>
+      <c r="D21" s="36" t="n">
+        <f aca="false">IFERROR(D19/Assumptions!D24,0)</f>
         <v>351064.030666667</v>
       </c>
-      <c r="E21" s="33" t="n">
-        <f aca="false">E19/Assumptions!E24</f>
+      <c r="E21" s="36" t="n">
+        <f aca="false">IFERROR(E19/Assumptions!E24,0)</f>
         <v>409296.752</v>
       </c>
-      <c r="F21" s="33" t="n">
-        <f aca="false">F19/Assumptions!F24</f>
+      <c r="F21" s="36" t="n">
+        <f aca="false">IFERROR(F19/Assumptions!F24,0)</f>
         <v>566573.083333334</v>
       </c>
-      <c r="G21" s="33" t="n">
-        <f aca="false">G19/Assumptions!G24</f>
+      <c r="G21" s="36" t="n">
+        <f aca="false">IFERROR(G19/Assumptions!G24,0)</f>
         <v>805667.146666667</v>
       </c>
-      <c r="H21" s="33" t="n">
-        <f aca="false">H19/Assumptions!H24</f>
+      <c r="H21" s="36" t="n">
+        <f aca="false">IFERROR(H19/Assumptions!H24,0)</f>
         <v>1123133.72266667</v>
       </c>
-      <c r="I21" s="33" t="n">
-        <f aca="false">I19/Assumptions!I24</f>
+      <c r="I21" s="36" t="n">
+        <f aca="false">IFERROR(I19/Assumptions!I24,0)</f>
         <v>1477197.178</v>
       </c>
-      <c r="J21" s="33" t="n">
-        <f aca="false">J19/Assumptions!J24</f>
+      <c r="J21" s="36" t="n">
+        <f aca="false">IFERROR(J19/Assumptions!J24,0)</f>
         <v>1887378.05066667</v>
       </c>
     </row>
@@ -10146,6 +10259,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FF5B9BD5"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
@@ -10165,6 +10279,7 @@
         <v>112</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>154</v>
@@ -10215,31 +10330,31 @@
       <c r="A6" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="37" t="n">
         <v>1314</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="37" t="n">
         <v>1809</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="37" t="n">
         <v>1950</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="37" t="n">
         <v>2200</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="37" t="n">
         <v>2600</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="37" t="n">
         <v>3100</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="37" t="n">
         <v>3600</v>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="37" t="n">
         <v>4100</v>
       </c>
-      <c r="J6" s="34" t="n">
+      <c r="J6" s="37" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -10247,31 +10362,31 @@
       <c r="A7" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="38" t="n">
         <v>52</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="38" t="n">
         <v>44</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="38" t="n">
         <v>43</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="38" t="n">
         <v>42</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="38" t="n">
         <v>41.5</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="38" t="n">
         <v>41</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="38" t="n">
         <v>41</v>
       </c>
-      <c r="I7" s="35" t="n">
+      <c r="I7" s="38" t="n">
         <v>41.5</v>
       </c>
-      <c r="J7" s="35" t="n">
+      <c r="J7" s="38" t="n">
         <v>42</v>
       </c>
     </row>
@@ -10353,38 +10468,39 @@
         <v>62</v>
       </c>
       <c r="C10" s="18" t="n">
-        <f aca="false">(Assumptions!C9-Assumptions!B9)/Assumptions!B9</f>
+        <f aca="false">IFERROR((Assumptions!C9-Assumptions!B9)/Assumptions!B9,0)</f>
         <v>0.153326243318127</v>
       </c>
       <c r="D10" s="18" t="n">
-        <f aca="false">(Assumptions!D9-Assumptions!C9)/Assumptions!C9</f>
+        <f aca="false">IFERROR((Assumptions!D9-Assumptions!C9)/Assumptions!C9,0)</f>
         <v>0.00953663596986132</v>
       </c>
       <c r="E10" s="18" t="n">
-        <f aca="false">(Assumptions!E9-Assumptions!D9)/Assumptions!D9</f>
+        <f aca="false">IFERROR((Assumptions!E9-Assumptions!D9)/Assumptions!D9,0)</f>
         <v>0.120004807403401</v>
       </c>
       <c r="F10" s="18" t="n">
-        <f aca="false">(Assumptions!F9-Assumptions!E9)/Assumptions!E9</f>
+        <f aca="false">IFERROR((Assumptions!F9-Assumptions!E9)/Assumptions!E9,0)</f>
         <v>0.179997853846979</v>
       </c>
       <c r="G10" s="18" t="n">
-        <f aca="false">(Assumptions!G9-Assumptions!F9)/Assumptions!F9</f>
+        <f aca="false">IFERROR((Assumptions!G9-Assumptions!F9)/Assumptions!F9,0)</f>
         <v>0.200001818777054</v>
       </c>
       <c r="H10" s="18" t="n">
-        <f aca="false">(Assumptions!H9-Assumptions!G9)/Assumptions!G9</f>
+        <f aca="false">IFERROR((Assumptions!H9-Assumptions!G9)/Assumptions!G9,0)</f>
         <v>0.180005607887418</v>
       </c>
       <c r="I10" s="18" t="n">
-        <f aca="false">(Assumptions!I9-Assumptions!H9)/Assumptions!H9</f>
+        <f aca="false">IFERROR((Assumptions!I9-Assumptions!H9)/Assumptions!H9,0)</f>
         <v>0.150003211097553</v>
       </c>
       <c r="J10" s="18" t="n">
-        <f aca="false">(Assumptions!J9-Assumptions!I9)/Assumptions!I9</f>
+        <f aca="false">IFERROR((Assumptions!J9-Assumptions!I9)/Assumptions!I9,0)</f>
         <v>0.119999776619924</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>160</v>
@@ -10403,31 +10519,31 @@
       <c r="A13" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="39" t="n">
         <v>6.5</v>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="39" t="n">
         <v>14.7</v>
       </c>
-      <c r="D13" s="36" t="n">
+      <c r="D13" s="39" t="n">
         <v>22</v>
       </c>
-      <c r="E13" s="36" t="n">
+      <c r="E13" s="39" t="n">
         <v>35</v>
       </c>
-      <c r="F13" s="36" t="n">
+      <c r="F13" s="39" t="n">
         <v>52</v>
       </c>
-      <c r="G13" s="36" t="n">
+      <c r="G13" s="39" t="n">
         <v>72</v>
       </c>
-      <c r="H13" s="36" t="n">
+      <c r="H13" s="39" t="n">
         <v>98</v>
       </c>
-      <c r="I13" s="36" t="n">
+      <c r="I13" s="39" t="n">
         <v>130</v>
       </c>
-      <c r="J13" s="36" t="n">
+      <c r="J13" s="39" t="n">
         <v>168</v>
       </c>
     </row>
@@ -10550,6 +10666,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G34"/>
@@ -10569,6 +10686,7 @@
         <v>165</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>166</v>
@@ -10599,7 +10717,7 @@
       <c r="A7" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="40" t="n">
         <f aca="false">Assumptions!E27</f>
         <v>0.055</v>
       </c>
@@ -10642,11 +10760,13 @@
       <c r="A12" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B12" s="38" t="n">
+      <c r="B12" s="41" t="n">
         <f aca="false">B8*B11+B9*B10</f>
         <v>3334.5039445</v>
       </c>
     </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>174</v>
@@ -10674,27 +10794,27 @@
       <c r="A16" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="22" t="n">
+      <c r="B16" s="25" t="n">
         <f aca="false">'Cash Flow'!E19</f>
         <v>12278.90256</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="25" t="n">
         <f aca="false">'Cash Flow'!F19</f>
         <v>16997.1925</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="25" t="n">
         <f aca="false">'Cash Flow'!G19</f>
         <v>24170.0144</v>
       </c>
-      <c r="E16" s="22" t="n">
+      <c r="E16" s="25" t="n">
         <f aca="false">'Cash Flow'!H19</f>
         <v>33694.01168</v>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="25" t="n">
         <f aca="false">'Cash Flow'!I19</f>
         <v>44315.91534</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="25" t="n">
         <f aca="false">'Cash Flow'!J19</f>
         <v>56621.34152</v>
       </c>
@@ -10703,28 +10823,28 @@
       <c r="A17" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^1</f>
+      <c r="B17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^1,0)</f>
         <v>0.000299804772124142</v>
       </c>
-      <c r="C17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^2</f>
+      <c r="C17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^2,0)</f>
         <v>8.98829013884089E-008</v>
       </c>
-      <c r="D17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^3</f>
+      <c r="D17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^3,0)</f>
         <v>2.69473227686087E-011</v>
       </c>
-      <c r="E17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^4</f>
+      <c r="E17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^4,0)</f>
         <v>8.07893596199843E-015</v>
       </c>
-      <c r="F17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^5</f>
+      <c r="F17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^5,0)</f>
         <v>2.42210355509248E-018</v>
       </c>
-      <c r="G17" s="39" t="n">
-        <f aca="false">1/(1+$B$12)^6</f>
+      <c r="G17" s="42" t="n">
+        <f aca="false">IFERROR(1/(1+$B$12)^6,0)</f>
         <v>7.26158204395575E-022</v>
       </c>
     </row>
@@ -10732,31 +10852,32 @@
       <c r="A18" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="B18" s="26" t="n">
+      <c r="B18" s="29" t="n">
         <f aca="false">B16*B17</f>
         <v>3.68127358393535</v>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="29" t="n">
         <f aca="false">C16*C17</f>
         <v>0.0015277569773573</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="29" t="n">
         <f aca="false">D16*D17</f>
         <v>6.51317179358719E-007</v>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="29" t="n">
         <f aca="false">E16*E17</f>
         <v>2.72211762665547E-010</v>
       </c>
-      <c r="F18" s="26" t="n">
+      <c r="F18" s="29" t="n">
         <f aca="false">F16*F17</f>
         <v>1.07337736092191E-013</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="29" t="n">
         <f aca="false">G16*G17</f>
         <v>4.11160516886318E-017</v>
       </c>
     </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>178</v>
@@ -10788,7 +10909,7 @@
         <v>181</v>
       </c>
       <c r="B23" s="16" t="n">
-        <f aca="false">B21*(1+B22)/(B12-B22)</f>
+        <f aca="false">IFERROR(B21*(1+B22)/(B12-B22),0)</f>
         <v>47.5709090564855</v>
       </c>
     </row>
@@ -10797,10 +10918,11 @@
         <v>182</v>
       </c>
       <c r="B24" s="16" t="n">
-        <f aca="false">B23/(1+$B$12)^6</f>
+        <f aca="false">IFERROR(B23/(1+$B$12)^6,0)</f>
         <v>3.45440059019227E-020</v>
       </c>
     </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>183</v>
@@ -10832,7 +10954,7 @@
       <c r="A29" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="30" t="n">
+      <c r="B29" s="33" t="n">
         <v>-27800</v>
       </c>
     </row>
@@ -10849,7 +10971,7 @@
       <c r="A31" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B31" s="40" t="n">
+      <c r="B31" s="43" t="n">
         <f aca="false">Assumptions!E24</f>
         <v>0.03</v>
       </c>
@@ -10858,8 +10980,8 @@
       <c r="A32" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="B32" s="41" t="n">
-        <f aca="false">B30/B31</f>
+      <c r="B32" s="44" t="n">
+        <f aca="false">IFERROR(B30/B31,0)</f>
         <v>926789.426733083</v>
       </c>
     </row>
@@ -10867,7 +10989,7 @@
       <c r="A33" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="29" t="n">
+      <c r="B33" s="32" t="n">
         <f aca="false">Assumptions!E29</f>
         <v>0.03</v>
       </c>
@@ -10876,8 +10998,8 @@
       <c r="A34" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B34" s="42" t="n">
-        <f aca="false">(B32-B33)/B33</f>
+      <c r="B34" s="45" t="n">
+        <f aca="false">IFERROR((B32-B33)/B33,0)</f>
         <v>30892979.8911028</v>
       </c>
     </row>
@@ -10895,6 +11017,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
@@ -10917,6 +11040,7 @@
         <v>191</v>
       </c>
     </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>192</v>
@@ -10941,13 +11065,13 @@
       <c r="A5" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="24" t="n">
         <v>100</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0.9</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="32" t="n">
         <f aca="false">B5*C5</f>
         <v>90</v>
       </c>
@@ -10962,13 +11086,13 @@
       <c r="A6" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="24" t="n">
         <v>100</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="32" t="n">
         <f aca="false">B6*C6</f>
         <v>80</v>
       </c>
@@ -10983,13 +11107,13 @@
       <c r="A7" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="24" t="n">
         <v>75</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>0.6</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">B7*C7</f>
         <v>45</v>
       </c>
@@ -11004,13 +11128,13 @@
       <c r="A8" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="24" t="n">
         <v>225</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>0.25</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="32" t="n">
         <f aca="false">B8*C8</f>
         <v>56.25</v>
       </c>
@@ -11025,13 +11149,13 @@
       <c r="A9" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="24" t="n">
         <v>40</v>
       </c>
       <c r="C9" s="15" t="n">
         <v>0.8</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="32" t="n">
         <f aca="false">B9*C9</f>
         <v>32</v>
       </c>
@@ -11046,13 +11170,13 @@
       <c r="A10" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="24" t="n">
         <v>125</v>
       </c>
       <c r="C10" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="32" t="n">
         <f aca="false">B10*C10</f>
         <v>12.5</v>
       </c>
@@ -11063,11 +11187,12 @@
         <v>214</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="46" t="n">
         <f aca="false">SUM(D5:D10)</f>
         <v>315.75</v>
       </c>
@@ -11076,16 +11201,17 @@
       <c r="A13" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="32" t="n">
         <f aca="false">SUM(B5:B10)</f>
         <v>665</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B15" s="44" t="n">
+      <c r="B15" s="47" t="n">
         <f aca="false">Assumptions!E29</f>
         <v>0.03</v>
       </c>
@@ -11094,8 +11220,8 @@
       <c r="A16" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B16" s="42" t="n">
-        <f aca="false">(D12-B15)/B15</f>
+      <c r="B16" s="45" t="n">
+        <f aca="false">IFERROR((D12-B15)/B15,0)</f>
         <v>10524</v>
       </c>
     </row>
@@ -11113,9 +11239,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
+    <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -11130,6 +11257,7 @@
         <v>218</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>219</v>
@@ -11154,18 +11282,18 @@
       <c r="A4" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="B4" s="21" t="n">
+      <c r="B4" s="24" t="n">
         <v>800</v>
       </c>
       <c r="C4" s="15" t="n">
         <v>0.1</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="32" t="n">
         <f aca="false">B4*C4</f>
         <v>80</v>
       </c>
       <c r="E4" s="18" t="n">
-        <f aca="false">(B4-Assumptions!E29)/Assumptions!E29</f>
+        <f aca="false">IFERROR((B4-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>26665.6666666667</v>
       </c>
       <c r="F4" s="11" t="s">
@@ -11176,18 +11304,18 @@
       <c r="A5" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="21" t="n">
+      <c r="B5" s="24" t="n">
         <v>600</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>0.3</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="32" t="n">
         <f aca="false">B5*C5</f>
         <v>180</v>
       </c>
       <c r="E5" s="18" t="n">
-        <f aca="false">(B5-Assumptions!E29)/Assumptions!E29</f>
+        <f aca="false">IFERROR((B5-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>19999</v>
       </c>
       <c r="F5" s="11" t="s">
@@ -11198,18 +11326,18 @@
       <c r="A6" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="24" t="n">
         <v>435</v>
       </c>
       <c r="C6" s="15" t="n">
         <v>0.35</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="32" t="n">
         <f aca="false">B6*C6</f>
         <v>152.25</v>
       </c>
       <c r="E6" s="18" t="n">
-        <f aca="false">(B6-Assumptions!E29)/Assumptions!E29</f>
+        <f aca="false">IFERROR((B6-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>14499</v>
       </c>
       <c r="F6" s="11" t="s">
@@ -11220,18 +11348,18 @@
       <c r="A7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="24" t="n">
         <v>320</v>
       </c>
       <c r="C7" s="15" t="n">
         <v>0.2</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">B7*C7</f>
         <v>64</v>
       </c>
       <c r="E7" s="18" t="n">
-        <f aca="false">(B7-Assumptions!E29)/Assumptions!E29</f>
+        <f aca="false">IFERROR((B7-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>10665.6666666667</v>
       </c>
       <c r="F7" s="11" t="s">
@@ -11242,41 +11370,50 @@
       <c r="A8" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="24" t="n">
         <v>170</v>
       </c>
       <c r="C8" s="15" t="n">
         <v>0.05</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="32" t="n">
         <f aca="false">B8*C8</f>
         <v>8.5</v>
       </c>
       <c r="E8" s="18" t="n">
-        <f aca="false">(B8-Assumptions!E29)/Assumptions!E29</f>
+        <f aca="false">IFERROR((B8-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>5665.66666666667</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>233</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="30" t="s">
         <v>234</v>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="B10" s="48" t="n">
+        <f aca="false">SUMPRODUCT(B4:B8,C4:C8)</f>
+        <v>484.75</v>
+      </c>
+      <c r="C10" s="49" t="n">
         <f aca="false">SUM(C4:C8)</f>
         <v>1</v>
       </c>
-      <c r="D10" s="46" t="n">
+      <c r="D10" s="50" t="n">
         <f aca="false">SUM(D4:D8)</f>
         <v>484.75</v>
       </c>
-      <c r="E10" s="42" t="n">
-        <f aca="false">(D10-Assumptions!E29)/Assumptions!E29</f>
+      <c r="E10" s="45" t="n">
+        <f aca="false">IFERROR((D10-Assumptions!E29)/Assumptions!E29,0)</f>
         <v>16157.3333333333</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/samples/TSLA-2026-03-10/TSLA-financial-model.xlsx
+++ b/samples/TSLA-2026-03-10/TSLA-financial-model.xlsx
@@ -22,6 +22,9 @@
     <sheet name="Catalyst Calendar" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Position Sizing" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="Delta Intelligence" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Developer Ecosystem" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Early Warning Dashboard" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="Tech Stack &amp; Roadmap" sheetId="17" state="visible" r:id="rId19"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="961">
   <si>
     <t xml:space="preserve">Hedge Fund-Grade Equity Analysis</t>
   </si>
@@ -986,7 +989,31 @@
     <t xml:space="preserve">Consensus-aligned, asymmetric upside</t>
   </si>
   <si>
-    <t xml:space="preserve">WEIGHTED AVERAGE</t>
+    <t xml:space="preserve">Developer Ecosystem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &gt; SDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACS 10+ OEMs, Fleet API paid, no FSD SDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early Warning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Bearish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9 bearish vs 3 bullish signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Deep-Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moat Bifurcated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5B FSD mi, 4680 &gt;95%, AI5 delayed</t>
   </si>
   <si>
     <t xml:space="preserve">CATALYST CALENDAR (2026)</t>
@@ -2352,13 +2379,553 @@
   </si>
   <si>
     <t xml:space="preserve">6. DISCLAIMER: Alternative data signals have lower reliability than financial statement data. Confidence levels are provided for each signal. Use in conjunction with fundamental analysis, not as standalone indicators.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1: Platform Lock-In Scorecard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock-In Score (1-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Risk Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charging (NACS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10+ OEMs adopted; 450K+ stalls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet API functional; docs uneven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energy Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Powerwall API new; not exclusive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOW-MEDIUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD Data/Training</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5B miles; no external access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance Telematics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proprietary fleet data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 2: Competitive Ecosystem Comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waymo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comma.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GitHub Repos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Third-Party Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD SDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waymax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACS Adoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10+ OEMs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adopted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lock-In Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Early Warning Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1: Signal Summary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bearish Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong headwinds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bullish Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modest support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral Signals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NET DIRECTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 2: Detailed Signal Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bloomberg?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BYD vs Tesla (2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BYD 2.254M / Tesla 1.636M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesla -9% YoY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARKET SHARE LOSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China Delivery Times</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-3 weeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collapsed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immediate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMAND CLIFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider Net Selling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-$26.8M (90d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accelerating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED FLAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NHTSA FSD Violations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80+ documented</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+60% in 4mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REGULATORY RISK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithium Prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138K CNY/T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rising</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-9 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COST PRESSURE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto Loan Rejection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+8.5pp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMAND DESTRUCTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassdoor Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5/5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable weak</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TALENT RISK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Musk Attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5+ major roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SpaceX IPO focus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-12 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXECUTION RISK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin Layoffs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,700 jobs cut</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contracting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORGANIZATIONAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">China Sales Recovery</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+35% MoM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Improving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-6 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Q Launch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H2 2026 target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9-12 mo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD v14.2 Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-L4 (per Xpeng)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Stack &amp; Roadmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 1: Technology Stack Moat Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proprietary (1-10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replication (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap Trend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD UX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Widening</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesla App</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrowing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleet Learning Loop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intelligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">End-to-end FSD NN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery Prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HW4 Chip (50 TOPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Competitive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI5 (500 TOPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strong (delayed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4680 Cells (dry cathode)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gigacasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD Training (8.5B mi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supercharger Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer Behavior (6M+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 2: Product Roadmap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model Q ($25K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giga Berlin tooling, LFP confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$3B annual ramp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybercab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First unit built Texas, Unboxed mfg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2M units/yr design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimus Gen 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shanghai expo, production Q2 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MED-HIGH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$200B TAM potential</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD Unsupervised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5B miles, 10B threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q2-Q3 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$12K→$20K/vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tesla Semi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nevada factory, 50K/yr capacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2-3B incremental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Megapack 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houston fab, 50 GWh/yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue doubling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Section 3: Competitive Battlefield Matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobileye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyundai/Kia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass-Market EVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium EVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autonomous Driving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/Robotics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\);\-"/>
@@ -2370,12 +2937,11 @@
     <numFmt numFmtId="172" formatCode="\$#,##0.0"/>
     <numFmt numFmtId="173" formatCode="0.0"/>
     <numFmt numFmtId="174" formatCode="0.0000"/>
-    <numFmt numFmtId="175" formatCode="\$#,##0"/>
-    <numFmt numFmtId="176" formatCode="\$#,##0.0;&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="177" formatCode="0%"/>
-    <numFmt numFmtId="178" formatCode="0"/>
+    <numFmt numFmtId="175" formatCode="\$#,##0.0;&quot;($&quot;#,##0.0\);\-"/>
+    <numFmt numFmtId="176" formatCode="0%"/>
+    <numFmt numFmtId="177" formatCode="0"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2644,8 +3210,62 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2661,7 +3281,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
@@ -2716,6 +3336,60 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4EC"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B0000"/>
+        <bgColor rgb="FF9C0006"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF003366"/>
+        <bgColor rgb="FF1F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFE8D5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD966"/>
+        <bgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor rgb="FF008080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3D3D3"/>
+        <bgColor rgb="FFE8D5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
+        <bgColor rgb="FFED7D31"/>
       </patternFill>
     </fill>
   </fills>
@@ -2782,7 +3456,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="109">
+  <cellXfs count="128">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2863,11 +3537,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2875,7 +3549,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2975,7 +3649,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2996,10 +3670,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3035,8 +3705,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="173" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -3055,11 +3737,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3127,15 +3809,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="175" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="176" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3147,7 +3829,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3171,19 +3853,19 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="30" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="12" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3191,7 +3873,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="7" fillId="10" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3219,6 +3901,74 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="16" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="42" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="38" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3238,7 +3988,7 @@
       <rgbColor rgb="FFFFFF00"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF9C0006"/>
+      <rgbColor rgb="FF8B0000"/>
       <rgbColor rgb="FF008000"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF9C6500"/>
@@ -3249,40 +3999,40 @@
       <rgbColor rgb="FFA5A5A5"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFD6E4F0"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FF4A1A6B"/>
-      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FFFF6B6B"/>
       <rgbColor rgb="FF2E75B6"/>
-      <rgbColor rgb="FFE8D5F5"/>
+      <rgbColor rgb="FFD3D3D3"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFFD966"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FFCC0000"/>
+      <rgbColor rgb="FF9C0006"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFD6E4F0"/>
+      <rgbColor rgb="FFC6EFCE"/>
+      <rgbColor rgb="FFFFEB9C"/>
+      <rgbColor rgb="FFE8D5F5"/>
+      <rgbColor rgb="FFFCE4EC"/>
       <rgbColor rgb="FFF2F2F2"/>
-      <rgbColor rgb="FFE2EFDA"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4EC"/>
+      <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF4472C4"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FFFFC000"/>
       <rgbColor rgb="FFCC6600"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF6A3D9A"/>
       <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF70AD47"/>
+      <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF006100"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFCC0000"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FF333333"/>
@@ -3472,7 +4222,7 @@
     <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:C36"/>
+  <dimension ref="B3:C36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -3480,23 +4230,18 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3545,8 +4290,6 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
         <v>14</v>
@@ -3656,8 +4399,6 @@
         <v>40</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
         <v>41</v>
@@ -3726,7 +4467,6 @@
         <v>235</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>236</v>
@@ -3804,13 +4544,13 @@
       <c r="F5" s="53" t="n">
         <v>22</v>
       </c>
-      <c r="G5" s="54" t="n">
+      <c r="G5" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="H5" s="54" t="n">
+      <c r="H5" s="20" t="n">
         <v>0.2</v>
       </c>
-      <c r="I5" s="54" t="n">
+      <c r="I5" s="20" t="n">
         <v>0.04</v>
       </c>
     </row>
@@ -3833,13 +4573,13 @@
       <c r="F6" s="53" t="n">
         <v>-10</v>
       </c>
-      <c r="G6" s="54" t="n">
+      <c r="G6" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="54" t="n">
+      <c r="H6" s="20" t="n">
         <v>-0.3</v>
       </c>
-      <c r="I6" s="54" t="n">
+      <c r="I6" s="20" t="n">
         <v>-0.2</v>
       </c>
     </row>
@@ -3862,13 +4602,13 @@
       <c r="F7" s="53" t="n">
         <v>-8</v>
       </c>
-      <c r="G7" s="54" t="n">
+      <c r="G7" s="20" t="n">
         <v>0.25</v>
       </c>
-      <c r="H7" s="54" t="n">
+      <c r="H7" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="I7" s="54" t="n">
+      <c r="I7" s="20" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -3891,13 +4631,13 @@
       <c r="F8" s="53" t="n">
         <v>10</v>
       </c>
-      <c r="G8" s="54" t="n">
+      <c r="G8" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="H8" s="54" t="n">
+      <c r="H8" s="20" t="n">
         <v>0.185</v>
       </c>
-      <c r="I8" s="54" t="n">
+      <c r="I8" s="20" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -3920,13 +4660,13 @@
       <c r="F9" s="53" t="n">
         <v>4.5</v>
       </c>
-      <c r="G9" s="54" t="n">
+      <c r="G9" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="H9" s="54" t="n">
+      <c r="H9" s="20" t="n">
         <v>0.17</v>
       </c>
-      <c r="I9" s="54" t="n">
+      <c r="I9" s="20" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -3949,13 +4689,13 @@
       <c r="F10" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="54" t="n">
+      <c r="G10" s="20" t="n">
         <v>0.02</v>
       </c>
-      <c r="H10" s="54" t="n">
+      <c r="H10" s="20" t="n">
         <v>0.155</v>
       </c>
-      <c r="I10" s="54" t="n">
+      <c r="I10" s="20" t="n">
         <v>0.07</v>
       </c>
     </row>
@@ -3978,34 +4718,33 @@
       <c r="F11" s="53" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="54" t="n">
+      <c r="G11" s="20" t="n">
         <v>0.01</v>
       </c>
-      <c r="H11" s="54" t="n">
+      <c r="H11" s="20" t="n">
         <v>0.12</v>
       </c>
-      <c r="I11" s="54" t="n">
+      <c r="I11" s="20" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C13" s="55" t="n">
+      <c r="C13" s="54" t="n">
         <f aca="false">MEDIAN(C5:C11)</f>
         <v>55</v>
       </c>
-      <c r="D13" s="56" t="n">
+      <c r="D13" s="55" t="n">
         <f aca="false">MEDIAN(D5:D11)</f>
         <v>0.9</v>
       </c>
-      <c r="E13" s="56" t="n">
+      <c r="E13" s="55" t="n">
         <f aca="false">MEDIAN(E5:E11)</f>
         <v>5</v>
       </c>
-      <c r="F13" s="56" t="n">
+      <c r="F13" s="55" t="n">
         <f aca="false">MEDIAN(F5:F11)</f>
         <v>6</v>
       </c>
@@ -4026,31 +4765,31 @@
       <c r="A14" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C14" s="57" t="n">
+      <c r="C14" s="56" t="n">
         <f aca="false">IFERROR((C4-C13)/C13,0)</f>
         <v>22.2727272727273</v>
       </c>
-      <c r="D14" s="57" t="n">
+      <c r="D14" s="56" t="n">
         <f aca="false">IFERROR((D4-D13)/D13,0)</f>
         <v>12.3333333333333</v>
       </c>
-      <c r="E14" s="57" t="n">
+      <c r="E14" s="56" t="n">
         <f aca="false">IFERROR((E4-E13)/E13,0)</f>
         <v>12</v>
       </c>
-      <c r="F14" s="57" t="n">
+      <c r="F14" s="56" t="n">
         <f aca="false">IFERROR((F4-F13)/F13,0)</f>
         <v>26.6666666666667</v>
       </c>
-      <c r="G14" s="57" t="n">
+      <c r="G14" s="56" t="n">
         <f aca="false">IFERROR((G4-G13)/G13,0)</f>
         <v>2</v>
       </c>
-      <c r="H14" s="57" t="n">
+      <c r="H14" s="56" t="n">
         <f aca="false">IFERROR((H4-H13)/H13,0)</f>
         <v>0.174193548387097</v>
       </c>
-      <c r="I14" s="57" t="n">
+      <c r="I14" s="56" t="n">
         <f aca="false">IFERROR((I4-I13)/I13,0)</f>
         <v>-0.925</v>
       </c>
@@ -4072,7 +4811,7 @@
     <tabColor rgb="FF70AD47"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -4089,7 +4828,6 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>261</v>
@@ -4117,10 +4855,10 @@
       <c r="B4" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="C4" s="58" t="n">
+      <c r="C4" s="57" t="n">
         <v>6.5</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -4137,10 +4875,10 @@
       <c r="B5" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="58" t="n">
+      <c r="C5" s="57" t="n">
         <v>6.5</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -4157,10 +4895,10 @@
       <c r="B6" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="C6" s="58" t="n">
+      <c r="C6" s="57" t="n">
         <v>6.5</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -4177,10 +4915,10 @@
       <c r="B7" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="C7" s="60" t="n">
+      <c r="C7" s="59" t="n">
         <v>7.5</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E7" s="6" t="s">
@@ -4197,10 +4935,10 @@
       <c r="B8" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="C8" s="58" t="n">
+      <c r="C8" s="57" t="n">
         <v>6.5</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E8" s="6" t="s">
@@ -4217,10 +4955,10 @@
       <c r="B9" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C9" s="60" t="n">
+      <c r="C9" s="59" t="n">
         <v>8</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -4237,10 +4975,10 @@
       <c r="B10" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C10" s="60" t="n">
+      <c r="C10" s="59" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="61" t="s">
         <v>288</v>
       </c>
       <c r="E10" s="6" t="s">
@@ -4257,10 +4995,10 @@
       <c r="B11" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="58" t="n">
+      <c r="C11" s="57" t="n">
         <v>6.8</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E11" s="6" t="s">
@@ -4277,10 +5015,10 @@
       <c r="B12" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="C12" s="60" t="n">
+      <c r="C12" s="59" t="n">
         <v>7.8</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E12" s="6" t="s">
@@ -4297,10 +5035,10 @@
       <c r="B13" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="58" t="n">
+      <c r="C13" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="61" t="s">
+      <c r="D13" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E13" s="6" t="s">
@@ -4317,10 +5055,10 @@
       <c r="B14" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="C14" s="58" t="n">
+      <c r="C14" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="D14" s="61" t="s">
+      <c r="D14" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -4337,10 +5075,10 @@
       <c r="B15" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="C15" s="58" t="n">
+      <c r="C15" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E15" s="6" t="s">
@@ -4357,10 +5095,10 @@
       <c r="B16" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="C16" s="58" t="n">
+      <c r="C16" s="57" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="61" t="s">
+      <c r="D16" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E16" s="6" t="s">
@@ -4377,10 +5115,10 @@
       <c r="B17" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C17" s="58" t="n">
+      <c r="C17" s="57" t="n">
         <v>6</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -4397,10 +5135,10 @@
       <c r="B18" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="C18" s="58" t="n">
+      <c r="C18" s="57" t="n">
         <v>6.5</v>
       </c>
-      <c r="D18" s="61" t="s">
+      <c r="D18" s="60" t="s">
         <v>278</v>
       </c>
       <c r="E18" s="6" t="s">
@@ -4417,10 +5155,10 @@
       <c r="B19" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="58" t="n">
+      <c r="C19" s="57" t="n">
         <v>6.8</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="58" t="s">
         <v>268</v>
       </c>
       <c r="E19" s="6" t="s">
@@ -4430,19 +5168,66 @@
         <v>316</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="62" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="62" t="s">
+        <v>317</v>
+      </c>
+      <c r="C20" s="63" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>278</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>319</v>
+      </c>
+    </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C21" s="63" t="n">
-        <f aca="false">AVERAGE(C4:C20)</f>
-        <v>6.5875</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A21" s="62" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="64" t="s">
+        <v>320</v>
+      </c>
+      <c r="C21" s="65" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>278</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="62" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="62" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>268</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="F22" s="63" t="s">
+        <v>325</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4471,22 +5256,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>326</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>221</v>
@@ -4497,162 +5281,162 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="C4" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D4" s="64" t="s">
+        <v>332</v>
+      </c>
+      <c r="C4" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="D4" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="E4" s="54" t="n">
+      <c r="E4" s="20" t="n">
         <v>0.6</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" s="61" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="D5" s="64" t="s">
+      <c r="D5" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="E5" s="54" t="n">
+      <c r="E5" s="20" t="n">
         <v>0.95</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D6" s="64" t="s">
+        <v>339</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="E6" s="54" t="n">
+      <c r="E6" s="20" t="n">
         <v>0.65</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="58" t="s">
         <v>333</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="C7" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D7" s="65" t="s">
-        <v>335</v>
-      </c>
-      <c r="E7" s="54" t="n">
+      <c r="D7" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="20" t="n">
         <v>0.42</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="65" t="s">
-        <v>335</v>
-      </c>
-      <c r="E8" s="54" t="n">
+        <v>346</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="D8" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="E8" s="20" t="n">
         <v>0.35</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D9" s="64" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="D9" s="66" t="s">
         <v>268</v>
       </c>
-      <c r="E9" s="54" t="n">
+      <c r="E9" s="20" t="n">
         <v>0.5</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="C10" s="61" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="D10" s="66" t="s">
-        <v>344</v>
-      </c>
-      <c r="E10" s="54" t="n">
+      <c r="D10" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="E10" s="20" t="n">
         <v>0.4</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="C11" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="D11" s="66" t="s">
-        <v>344</v>
-      </c>
-      <c r="E11" s="54" t="n">
+        <v>355</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>352</v>
+      </c>
+      <c r="E11" s="20" t="n">
         <v>0.7</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4682,19 +5466,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>357</v>
+      </c>
+    </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>197</v>
@@ -4702,19 +5485,19 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B4" s="15" t="n">
         <v>0.65</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B5" s="18" t="n">
         <f aca="false">1-B4</f>
@@ -4725,19 +5508,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="B6" s="67" t="n">
+        <v>364</v>
+      </c>
+      <c r="B6" s="69" t="n">
         <v>2.8</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B7" s="18" t="n">
         <f aca="false">IFERROR((B4*B6-B5)/B6,0)</f>
@@ -4745,12 +5528,12 @@
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B8" s="18" t="n">
         <f aca="false">IFERROR(B7/2,0)</f>
@@ -4758,38 +5541,37 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>369</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="68" t="n">
+        <v>370</v>
+      </c>
+      <c r="B10" s="70" t="n">
         <v>1000000</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="B11" s="69" t="n">
+        <v>372</v>
+      </c>
+      <c r="B11" s="71" t="n">
         <f aca="false">B10*B8</f>
         <v>262500</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B12" s="43" t="n">
         <f aca="false">IFERROR(B11/Assumptions!E29,0)</f>
@@ -4797,20 +5579,19 @@
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>375</v>
+      </c>
+    </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B14" s="15" t="n">
         <v>-0.495</v>
       </c>
       <c r="C14" s="11"/>
       <c r="D14" s="11" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4844,2382 +5625,2371 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="70" t="s">
-        <v>370</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
-      <c r="E1" s="70"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="70"/>
-      <c r="H1" s="70"/>
-      <c r="I1" s="70"/>
+      <c r="A1" s="72" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="71" t="s">
-        <v>371</v>
-      </c>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
+      <c r="A2" s="73" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="72" t="s">
-        <v>372</v>
-      </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="A3" s="74" t="s">
+        <v>380</v>
+      </c>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
+      <c r="I3" s="74"/>
+    </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="73" t="s">
-        <v>373</v>
-      </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="73"/>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
+      <c r="A5" s="75" t="s">
+        <v>381</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="74" t="s">
-        <v>374</v>
-      </c>
-      <c r="B6" s="74" t="s">
-        <v>375</v>
-      </c>
-      <c r="C6" s="74" t="s">
-        <v>376</v>
-      </c>
-      <c r="D6" s="74" t="s">
-        <v>377</v>
-      </c>
-      <c r="E6" s="74" t="s">
-        <v>378</v>
-      </c>
-      <c r="F6" s="74" t="s">
+      <c r="A6" s="76" t="s">
+        <v>382</v>
+      </c>
+      <c r="B6" s="76" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="76" t="s">
+        <v>384</v>
+      </c>
+      <c r="D6" s="76" t="s">
+        <v>385</v>
+      </c>
+      <c r="E6" s="76" t="s">
+        <v>386</v>
+      </c>
+      <c r="F6" s="76" t="s">
         <v>264</v>
       </c>
-      <c r="G6" s="74" t="s">
-        <v>379</v>
-      </c>
-      <c r="H6" s="74" t="s">
-        <v>380</v>
-      </c>
-      <c r="I6" s="74" t="s">
-        <v>381</v>
+      <c r="G6" s="76" t="s">
+        <v>387</v>
+      </c>
+      <c r="H6" s="76" t="s">
+        <v>388</v>
+      </c>
+      <c r="I6" s="76" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="75" t="s">
-        <v>382</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" s="76" t="s">
-        <v>384</v>
-      </c>
-      <c r="D7" s="76" t="s">
-        <v>385</v>
-      </c>
-      <c r="E7" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F7" s="76" t="s">
+      <c r="A7" s="77" t="s">
+        <v>390</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>391</v>
+      </c>
+      <c r="C7" s="78" t="s">
+        <v>392</v>
+      </c>
+      <c r="D7" s="78" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F7" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G7" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H7" s="76" t="s">
-        <v>388</v>
-      </c>
-      <c r="I7" s="76" t="s">
-        <v>389</v>
+      <c r="G7" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H7" s="78" t="s">
+        <v>396</v>
+      </c>
+      <c r="I7" s="78" t="s">
+        <v>397</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="79" t="s">
-        <v>382</v>
-      </c>
-      <c r="B8" s="80" t="s">
+      <c r="A8" s="81" t="s">
         <v>390</v>
       </c>
-      <c r="C8" s="80" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="80" t="s">
-        <v>392</v>
-      </c>
-      <c r="E8" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F8" s="80" t="s">
+      <c r="B8" s="82" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" s="82" t="s">
+        <v>399</v>
+      </c>
+      <c r="D8" s="82" t="s">
+        <v>400</v>
+      </c>
+      <c r="E8" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="82" t="s">
         <v>278</v>
       </c>
-      <c r="G8" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H8" s="80" t="s">
-        <v>393</v>
-      </c>
-      <c r="I8" s="80" t="s">
+      <c r="G8" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H8" s="82" t="s">
+        <v>401</v>
+      </c>
+      <c r="I8" s="82" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="77" t="s">
+        <v>390</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>403</v>
+      </c>
+      <c r="C9" s="78" t="s">
+        <v>404</v>
+      </c>
+      <c r="D9" s="78" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="79" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="75" t="s">
-        <v>382</v>
-      </c>
-      <c r="B9" s="76" t="s">
+      <c r="F9" s="78" t="s">
+        <v>268</v>
+      </c>
+      <c r="G9" s="80" t="s">
         <v>395</v>
       </c>
-      <c r="C9" s="76" t="s">
-        <v>396</v>
-      </c>
-      <c r="D9" s="76" t="s">
-        <v>397</v>
-      </c>
-      <c r="E9" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F9" s="76" t="s">
+      <c r="H9" s="78" t="s">
+        <v>406</v>
+      </c>
+      <c r="I9" s="78" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="81" t="s">
+        <v>408</v>
+      </c>
+      <c r="B10" s="82" t="s">
+        <v>409</v>
+      </c>
+      <c r="C10" s="82" t="s">
+        <v>410</v>
+      </c>
+      <c r="D10" s="82" t="s">
+        <v>411</v>
+      </c>
+      <c r="E10" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F10" s="82" t="s">
         <v>268</v>
       </c>
-      <c r="G9" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>398</v>
-      </c>
-      <c r="I9" s="76" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="79" t="s">
-        <v>400</v>
-      </c>
-      <c r="B10" s="80" t="s">
-        <v>401</v>
-      </c>
-      <c r="C10" s="80" t="s">
-        <v>402</v>
-      </c>
-      <c r="D10" s="80" t="s">
-        <v>403</v>
-      </c>
-      <c r="E10" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F10" s="80" t="s">
+      <c r="G10" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H10" s="82" t="s">
+        <v>412</v>
+      </c>
+      <c r="I10" s="82" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="77" t="s">
+        <v>408</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>414</v>
+      </c>
+      <c r="C11" s="78" t="s">
+        <v>415</v>
+      </c>
+      <c r="D11" s="78" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F11" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G10" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H10" s="80" t="s">
-        <v>404</v>
-      </c>
-      <c r="I10" s="80" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="75" t="s">
-        <v>400</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>406</v>
-      </c>
-      <c r="C11" s="76" t="s">
-        <v>407</v>
-      </c>
-      <c r="D11" s="76" t="s">
+      <c r="G11" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H11" s="78" t="s">
+        <v>417</v>
+      </c>
+      <c r="I11" s="78" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="81" t="s">
         <v>408</v>
       </c>
-      <c r="E11" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F11" s="76" t="s">
+      <c r="B12" s="82" t="s">
+        <v>419</v>
+      </c>
+      <c r="C12" s="82" t="s">
+        <v>420</v>
+      </c>
+      <c r="D12" s="82" t="s">
+        <v>421</v>
+      </c>
+      <c r="E12" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F12" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G12" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H12" s="82" t="s">
+        <v>422</v>
+      </c>
+      <c r="I12" s="82" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="77" t="s">
+        <v>424</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>425</v>
+      </c>
+      <c r="C13" s="78" t="s">
+        <v>426</v>
+      </c>
+      <c r="D13" s="78" t="s">
+        <v>427</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F13" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G11" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>409</v>
-      </c>
-      <c r="I11" s="76" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="79" t="s">
-        <v>400</v>
-      </c>
-      <c r="B12" s="80" t="s">
-        <v>411</v>
-      </c>
-      <c r="C12" s="80" t="s">
-        <v>412</v>
-      </c>
-      <c r="D12" s="80" t="s">
-        <v>413</v>
-      </c>
-      <c r="E12" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F12" s="80" t="s">
+      <c r="G13" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>428</v>
+      </c>
+      <c r="I13" s="78" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="81" t="s">
+        <v>424</v>
+      </c>
+      <c r="B14" s="82" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="82" t="s">
+        <v>431</v>
+      </c>
+      <c r="D14" s="82" t="s">
+        <v>432</v>
+      </c>
+      <c r="E14" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F14" s="82" t="s">
         <v>278</v>
       </c>
-      <c r="G12" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H12" s="80" t="s">
-        <v>414</v>
-      </c>
-      <c r="I12" s="80" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="75" t="s">
-        <v>416</v>
-      </c>
-      <c r="B13" s="76" t="s">
-        <v>417</v>
-      </c>
-      <c r="C13" s="76" t="s">
-        <v>418</v>
-      </c>
-      <c r="D13" s="76" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F13" s="76" t="s">
+      <c r="G14" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>433</v>
+      </c>
+      <c r="I14" s="82" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="77" t="s">
+        <v>424</v>
+      </c>
+      <c r="B15" s="78" t="s">
+        <v>435</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" s="78" t="s">
+        <v>437</v>
+      </c>
+      <c r="E15" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F15" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G13" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>420</v>
-      </c>
-      <c r="I13" s="76" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="79" t="s">
-        <v>416</v>
-      </c>
-      <c r="B14" s="80" t="s">
-        <v>422</v>
-      </c>
-      <c r="C14" s="80" t="s">
-        <v>423</v>
-      </c>
-      <c r="D14" s="80" t="s">
-        <v>424</v>
-      </c>
-      <c r="E14" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F14" s="80" t="s">
+      <c r="G15" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H15" s="78" t="s">
+        <v>438</v>
+      </c>
+      <c r="I15" s="78" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="81" t="s">
+        <v>440</v>
+      </c>
+      <c r="B16" s="82" t="s">
+        <v>441</v>
+      </c>
+      <c r="C16" s="82" t="s">
+        <v>442</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F16" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="G16" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H16" s="82" t="s">
+        <v>444</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="77" t="s">
+        <v>440</v>
+      </c>
+      <c r="B17" s="78" t="s">
+        <v>446</v>
+      </c>
+      <c r="C17" s="78" t="s">
+        <v>447</v>
+      </c>
+      <c r="D17" s="78" t="s">
+        <v>448</v>
+      </c>
+      <c r="E17" s="84" t="s">
+        <v>449</v>
+      </c>
+      <c r="F17" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="G14" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H14" s="80" t="s">
-        <v>425</v>
-      </c>
-      <c r="I14" s="80" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="75" t="s">
-        <v>416</v>
-      </c>
-      <c r="B15" s="76" t="s">
-        <v>427</v>
-      </c>
-      <c r="C15" s="76" t="s">
-        <v>428</v>
-      </c>
-      <c r="D15" s="76" t="s">
-        <v>429</v>
-      </c>
-      <c r="E15" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F15" s="76" t="s">
+      <c r="G17" s="78" t="s">
+        <v>450</v>
+      </c>
+      <c r="H17" s="78" t="s">
+        <v>451</v>
+      </c>
+      <c r="I17" s="78" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="81" t="s">
+        <v>440</v>
+      </c>
+      <c r="B18" s="82" t="s">
+        <v>453</v>
+      </c>
+      <c r="C18" s="82" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" s="82" t="s">
+        <v>455</v>
+      </c>
+      <c r="E18" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F18" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H18" s="82" t="s">
+        <v>456</v>
+      </c>
+      <c r="I18" s="82" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="77" t="s">
+        <v>440</v>
+      </c>
+      <c r="B19" s="78" t="s">
+        <v>458</v>
+      </c>
+      <c r="C19" s="78" t="s">
+        <v>459</v>
+      </c>
+      <c r="D19" s="78" t="s">
+        <v>460</v>
+      </c>
+      <c r="E19" s="84" t="s">
+        <v>449</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>288</v>
+      </c>
+      <c r="G19" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H19" s="78" t="s">
+        <v>461</v>
+      </c>
+      <c r="I19" s="78" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="81" t="s">
+        <v>463</v>
+      </c>
+      <c r="B20" s="82" t="s">
+        <v>464</v>
+      </c>
+      <c r="C20" s="82" t="s">
+        <v>465</v>
+      </c>
+      <c r="D20" s="82" t="s">
+        <v>466</v>
+      </c>
+      <c r="E20" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F20" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="H20" s="82" t="s">
+        <v>467</v>
+      </c>
+      <c r="I20" s="82" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="77" t="s">
+        <v>463</v>
+      </c>
+      <c r="B21" s="78" t="s">
+        <v>469</v>
+      </c>
+      <c r="C21" s="78" t="s">
+        <v>470</v>
+      </c>
+      <c r="D21" s="78" t="s">
+        <v>471</v>
+      </c>
+      <c r="E21" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F21" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G15" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H15" s="76" t="s">
-        <v>430</v>
-      </c>
-      <c r="I15" s="76" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="79" t="s">
+      <c r="G21" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H21" s="78" t="s">
+        <v>472</v>
+      </c>
+      <c r="I21" s="78" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="81" t="s">
+        <v>463</v>
+      </c>
+      <c r="B22" s="82" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" s="82" t="s">
+        <v>475</v>
+      </c>
+      <c r="D22" s="82" t="s">
+        <v>476</v>
+      </c>
+      <c r="E22" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F22" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G22" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H22" s="82" t="s">
+        <v>477</v>
+      </c>
+      <c r="I22" s="82" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="B23" s="78" t="s">
+        <v>480</v>
+      </c>
+      <c r="C23" s="78" t="s">
+        <v>481</v>
+      </c>
+      <c r="D23" s="78" t="s">
+        <v>482</v>
+      </c>
+      <c r="E23" s="85" t="s">
+        <v>483</v>
+      </c>
+      <c r="F23" s="78" t="s">
+        <v>288</v>
+      </c>
+      <c r="G23" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H23" s="78" t="s">
+        <v>484</v>
+      </c>
+      <c r="I23" s="78" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="81" t="s">
+        <v>479</v>
+      </c>
+      <c r="B24" s="82" t="s">
+        <v>486</v>
+      </c>
+      <c r="C24" s="82" t="s">
+        <v>487</v>
+      </c>
+      <c r="D24" s="82" t="s">
+        <v>488</v>
+      </c>
+      <c r="E24" s="86" t="s">
+        <v>483</v>
+      </c>
+      <c r="F24" s="82" t="s">
+        <v>288</v>
+      </c>
+      <c r="G24" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H24" s="82" t="s">
+        <v>489</v>
+      </c>
+      <c r="I24" s="82" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="77" t="s">
+        <v>479</v>
+      </c>
+      <c r="B25" s="78" t="s">
+        <v>491</v>
+      </c>
+      <c r="C25" s="78" t="s">
+        <v>492</v>
+      </c>
+      <c r="D25" s="78" t="s">
+        <v>493</v>
+      </c>
+      <c r="E25" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F25" s="78" t="s">
+        <v>278</v>
+      </c>
+      <c r="G25" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H25" s="78" t="s">
+        <v>494</v>
+      </c>
+      <c r="I25" s="78" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="81" t="s">
+        <v>496</v>
+      </c>
+      <c r="B26" s="82" t="s">
+        <v>497</v>
+      </c>
+      <c r="C26" s="82" t="s">
+        <v>498</v>
+      </c>
+      <c r="D26" s="82" t="s">
+        <v>499</v>
+      </c>
+      <c r="E26" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F26" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G26" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H26" s="82" t="s">
+        <v>500</v>
+      </c>
+      <c r="I26" s="82" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="77" t="s">
+        <v>496</v>
+      </c>
+      <c r="B27" s="78" t="s">
+        <v>502</v>
+      </c>
+      <c r="C27" s="78" t="s">
+        <v>503</v>
+      </c>
+      <c r="D27" s="78" t="s">
+        <v>504</v>
+      </c>
+      <c r="E27" s="84" t="s">
+        <v>449</v>
+      </c>
+      <c r="F27" s="78" t="s">
+        <v>278</v>
+      </c>
+      <c r="G27" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H27" s="78" t="s">
+        <v>505</v>
+      </c>
+      <c r="I27" s="78" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="81" t="s">
+        <v>507</v>
+      </c>
+      <c r="B28" s="82" t="s">
+        <v>508</v>
+      </c>
+      <c r="C28" s="82" t="s">
+        <v>509</v>
+      </c>
+      <c r="D28" s="82" t="s">
+        <v>488</v>
+      </c>
+      <c r="E28" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F28" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G28" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H28" s="82" t="s">
+        <v>510</v>
+      </c>
+      <c r="I28" s="82" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="77" t="s">
+        <v>507</v>
+      </c>
+      <c r="B29" s="78" t="s">
+        <v>512</v>
+      </c>
+      <c r="C29" s="78" t="s">
+        <v>513</v>
+      </c>
+      <c r="D29" s="78" t="s">
+        <v>514</v>
+      </c>
+      <c r="E29" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F29" s="78" t="s">
+        <v>278</v>
+      </c>
+      <c r="G29" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H29" s="78" t="s">
+        <v>515</v>
+      </c>
+      <c r="I29" s="78" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="81" t="s">
+        <v>507</v>
+      </c>
+      <c r="B30" s="82" t="s">
+        <v>517</v>
+      </c>
+      <c r="C30" s="82" t="s">
+        <v>518</v>
+      </c>
+      <c r="D30" s="82" t="s">
+        <v>518</v>
+      </c>
+      <c r="E30" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F30" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="G30" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="H30" s="82" t="s">
+        <v>519</v>
+      </c>
+      <c r="I30" s="82" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="77" t="s">
+        <v>521</v>
+      </c>
+      <c r="B31" s="78" t="s">
+        <v>522</v>
+      </c>
+      <c r="C31" s="78" t="s">
+        <v>523</v>
+      </c>
+      <c r="D31" s="78" t="s">
+        <v>524</v>
+      </c>
+      <c r="E31" s="84" t="s">
+        <v>449</v>
+      </c>
+      <c r="F31" s="78" t="s">
+        <v>268</v>
+      </c>
+      <c r="G31" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H31" s="78" t="s">
+        <v>525</v>
+      </c>
+      <c r="I31" s="78" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="81" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="82" t="s">
+        <v>527</v>
+      </c>
+      <c r="C32" s="82" t="s">
+        <v>528</v>
+      </c>
+      <c r="D32" s="82" t="s">
         <v>432</v>
       </c>
-      <c r="B16" s="80" t="s">
-        <v>433</v>
-      </c>
-      <c r="C16" s="80" t="s">
-        <v>434</v>
-      </c>
-      <c r="D16" s="80" t="s">
-        <v>435</v>
-      </c>
-      <c r="E16" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F16" s="80" t="s">
+      <c r="E32" s="87" t="s">
+        <v>449</v>
+      </c>
+      <c r="F32" s="82" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H32" s="82" t="s">
+        <v>529</v>
+      </c>
+      <c r="I32" s="82" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="77" t="s">
+        <v>521</v>
+      </c>
+      <c r="B33" s="78" t="s">
+        <v>531</v>
+      </c>
+      <c r="C33" s="78" t="s">
+        <v>532</v>
+      </c>
+      <c r="D33" s="78" t="s">
+        <v>533</v>
+      </c>
+      <c r="E33" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F33" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="G16" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H16" s="80" t="s">
-        <v>436</v>
-      </c>
-      <c r="I16" s="80" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="75" t="s">
-        <v>432</v>
-      </c>
-      <c r="B17" s="76" t="s">
-        <v>438</v>
-      </c>
-      <c r="C17" s="76" t="s">
-        <v>439</v>
-      </c>
-      <c r="D17" s="76" t="s">
-        <v>440</v>
-      </c>
-      <c r="E17" s="82" t="s">
-        <v>441</v>
-      </c>
-      <c r="F17" s="76" t="s">
+      <c r="G33" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H33" s="78" t="s">
+        <v>534</v>
+      </c>
+      <c r="I33" s="78" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="81" t="s">
+        <v>536</v>
+      </c>
+      <c r="B34" s="82" t="s">
+        <v>537</v>
+      </c>
+      <c r="C34" s="82" t="s">
+        <v>538</v>
+      </c>
+      <c r="D34" s="82" t="s">
+        <v>539</v>
+      </c>
+      <c r="E34" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F34" s="82" t="s">
         <v>278</v>
       </c>
-      <c r="G17" s="76" t="s">
-        <v>442</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>443</v>
-      </c>
-      <c r="I17" s="76" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="79" t="s">
-        <v>432</v>
-      </c>
-      <c r="B18" s="80" t="s">
-        <v>445</v>
-      </c>
-      <c r="C18" s="80" t="s">
-        <v>446</v>
-      </c>
-      <c r="D18" s="80" t="s">
-        <v>447</v>
-      </c>
-      <c r="E18" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F18" s="80" t="s">
+      <c r="G34" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H34" s="82" t="s">
+        <v>540</v>
+      </c>
+      <c r="I34" s="82" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="77" t="s">
+        <v>536</v>
+      </c>
+      <c r="B35" s="78" t="s">
+        <v>542</v>
+      </c>
+      <c r="C35" s="78" t="s">
+        <v>543</v>
+      </c>
+      <c r="D35" s="78" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F35" s="78" t="s">
+        <v>268</v>
+      </c>
+      <c r="G35" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H35" s="78" t="s">
+        <v>545</v>
+      </c>
+      <c r="I35" s="78" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="81" t="s">
+        <v>536</v>
+      </c>
+      <c r="B36" s="82" t="s">
+        <v>547</v>
+      </c>
+      <c r="C36" s="82" t="s">
+        <v>548</v>
+      </c>
+      <c r="D36" s="82" t="s">
+        <v>549</v>
+      </c>
+      <c r="E36" s="83" t="s">
+        <v>394</v>
+      </c>
+      <c r="F36" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="G36" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H36" s="82" t="s">
+        <v>550</v>
+      </c>
+      <c r="I36" s="82" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="77" t="s">
+        <v>552</v>
+      </c>
+      <c r="B37" s="78" t="s">
+        <v>553</v>
+      </c>
+      <c r="C37" s="78" t="s">
+        <v>554</v>
+      </c>
+      <c r="D37" s="78" t="s">
+        <v>555</v>
+      </c>
+      <c r="E37" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F37" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="G18" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H18" s="80" t="s">
-        <v>448</v>
-      </c>
-      <c r="I18" s="80" t="s">
+      <c r="G37" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H37" s="78" t="s">
+        <v>556</v>
+      </c>
+      <c r="I37" s="78" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="81" t="s">
+        <v>552</v>
+      </c>
+      <c r="B38" s="82" t="s">
+        <v>558</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>559</v>
+      </c>
+      <c r="D38" s="82" t="s">
+        <v>560</v>
+      </c>
+      <c r="E38" s="87" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="75" t="s">
-        <v>432</v>
-      </c>
-      <c r="B19" s="76" t="s">
-        <v>450</v>
-      </c>
-      <c r="C19" s="76" t="s">
-        <v>451</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>452</v>
-      </c>
-      <c r="E19" s="82" t="s">
-        <v>441</v>
-      </c>
-      <c r="F19" s="76" t="s">
-        <v>288</v>
-      </c>
-      <c r="G19" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H19" s="76" t="s">
-        <v>453</v>
-      </c>
-      <c r="I19" s="76" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="79" t="s">
-        <v>455</v>
-      </c>
-      <c r="B20" s="80" t="s">
-        <v>456</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>457</v>
-      </c>
-      <c r="D20" s="80" t="s">
-        <v>458</v>
-      </c>
-      <c r="E20" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F20" s="80" t="s">
+      <c r="F38" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="G38" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H38" s="82" t="s">
+        <v>561</v>
+      </c>
+      <c r="I38" s="82" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="77" t="s">
+        <v>552</v>
+      </c>
+      <c r="B39" s="78" t="s">
+        <v>563</v>
+      </c>
+      <c r="C39" s="78" t="s">
+        <v>564</v>
+      </c>
+      <c r="D39" s="78" t="s">
+        <v>565</v>
+      </c>
+      <c r="E39" s="79" t="s">
+        <v>394</v>
+      </c>
+      <c r="F39" s="78" t="s">
         <v>278</v>
       </c>
-      <c r="G20" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="H20" s="80" t="s">
-        <v>459</v>
-      </c>
-      <c r="I20" s="80" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="75" t="s">
-        <v>455</v>
-      </c>
-      <c r="B21" s="76" t="s">
-        <v>461</v>
-      </c>
-      <c r="C21" s="76" t="s">
-        <v>462</v>
-      </c>
-      <c r="D21" s="76" t="s">
-        <v>463</v>
-      </c>
-      <c r="E21" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F21" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="G21" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>464</v>
-      </c>
-      <c r="I21" s="76" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="79" t="s">
-        <v>455</v>
-      </c>
-      <c r="B22" s="80" t="s">
-        <v>466</v>
-      </c>
-      <c r="C22" s="80" t="s">
-        <v>467</v>
-      </c>
-      <c r="D22" s="80" t="s">
-        <v>468</v>
-      </c>
-      <c r="E22" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F22" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G22" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H22" s="80" t="s">
-        <v>469</v>
-      </c>
-      <c r="I22" s="80" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="75" t="s">
-        <v>471</v>
-      </c>
-      <c r="B23" s="76" t="s">
-        <v>472</v>
-      </c>
-      <c r="C23" s="76" t="s">
-        <v>473</v>
-      </c>
-      <c r="D23" s="76" t="s">
-        <v>474</v>
-      </c>
-      <c r="E23" s="83" t="s">
-        <v>475</v>
-      </c>
-      <c r="F23" s="76" t="s">
-        <v>288</v>
-      </c>
-      <c r="G23" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>476</v>
-      </c>
-      <c r="I23" s="76" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="79" t="s">
-        <v>471</v>
-      </c>
-      <c r="B24" s="80" t="s">
-        <v>478</v>
-      </c>
-      <c r="C24" s="80" t="s">
-        <v>479</v>
-      </c>
-      <c r="D24" s="80" t="s">
-        <v>480</v>
-      </c>
-      <c r="E24" s="84" t="s">
-        <v>475</v>
-      </c>
-      <c r="F24" s="80" t="s">
-        <v>288</v>
-      </c>
-      <c r="G24" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H24" s="80" t="s">
-        <v>481</v>
-      </c>
-      <c r="I24" s="80" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="75" t="s">
-        <v>471</v>
-      </c>
-      <c r="B25" s="76" t="s">
-        <v>483</v>
-      </c>
-      <c r="C25" s="76" t="s">
-        <v>484</v>
-      </c>
-      <c r="D25" s="76" t="s">
-        <v>485</v>
-      </c>
-      <c r="E25" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F25" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>486</v>
-      </c>
-      <c r="I25" s="76" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="79" t="s">
-        <v>488</v>
-      </c>
-      <c r="B26" s="80" t="s">
-        <v>489</v>
-      </c>
-      <c r="C26" s="80" t="s">
-        <v>490</v>
-      </c>
-      <c r="D26" s="80" t="s">
-        <v>491</v>
-      </c>
-      <c r="E26" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F26" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G26" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H26" s="80" t="s">
-        <v>492</v>
-      </c>
-      <c r="I26" s="80" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="75" t="s">
-        <v>488</v>
-      </c>
-      <c r="B27" s="76" t="s">
-        <v>494</v>
-      </c>
-      <c r="C27" s="76" t="s">
-        <v>495</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>496</v>
-      </c>
-      <c r="E27" s="82" t="s">
-        <v>441</v>
-      </c>
-      <c r="F27" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="G27" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H27" s="76" t="s">
-        <v>497</v>
-      </c>
-      <c r="I27" s="76" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="79" t="s">
-        <v>499</v>
-      </c>
-      <c r="B28" s="80" t="s">
-        <v>500</v>
-      </c>
-      <c r="C28" s="80" t="s">
-        <v>501</v>
-      </c>
-      <c r="D28" s="80" t="s">
-        <v>480</v>
-      </c>
-      <c r="E28" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F28" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G28" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H28" s="80" t="s">
-        <v>502</v>
-      </c>
-      <c r="I28" s="80" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="75" t="s">
-        <v>499</v>
-      </c>
-      <c r="B29" s="76" t="s">
-        <v>504</v>
-      </c>
-      <c r="C29" s="76" t="s">
-        <v>505</v>
-      </c>
-      <c r="D29" s="76" t="s">
-        <v>506</v>
-      </c>
-      <c r="E29" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F29" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="G29" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>507</v>
-      </c>
-      <c r="I29" s="76" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="79" t="s">
-        <v>499</v>
-      </c>
-      <c r="B30" s="80" t="s">
-        <v>509</v>
-      </c>
-      <c r="C30" s="80" t="s">
-        <v>510</v>
-      </c>
-      <c r="D30" s="80" t="s">
-        <v>510</v>
-      </c>
-      <c r="E30" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F30" s="80" t="s">
-        <v>268</v>
-      </c>
-      <c r="G30" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="H30" s="80" t="s">
-        <v>511</v>
-      </c>
-      <c r="I30" s="80" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="75" t="s">
-        <v>513</v>
-      </c>
-      <c r="B31" s="76" t="s">
-        <v>514</v>
-      </c>
-      <c r="C31" s="76" t="s">
-        <v>515</v>
-      </c>
-      <c r="D31" s="76" t="s">
-        <v>516</v>
-      </c>
-      <c r="E31" s="82" t="s">
-        <v>441</v>
-      </c>
-      <c r="F31" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="G31" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H31" s="76" t="s">
-        <v>517</v>
-      </c>
-      <c r="I31" s="76" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="79" t="s">
-        <v>513</v>
-      </c>
-      <c r="B32" s="80" t="s">
-        <v>519</v>
-      </c>
-      <c r="C32" s="80" t="s">
-        <v>520</v>
-      </c>
-      <c r="D32" s="80" t="s">
-        <v>424</v>
-      </c>
-      <c r="E32" s="85" t="s">
-        <v>441</v>
-      </c>
-      <c r="F32" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G32" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H32" s="80" t="s">
-        <v>521</v>
-      </c>
-      <c r="I32" s="80" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="75" t="s">
-        <v>513</v>
-      </c>
-      <c r="B33" s="76" t="s">
-        <v>523</v>
-      </c>
-      <c r="C33" s="76" t="s">
-        <v>524</v>
-      </c>
-      <c r="D33" s="76" t="s">
-        <v>525</v>
-      </c>
-      <c r="E33" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F33" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="G33" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H33" s="76" t="s">
-        <v>526</v>
-      </c>
-      <c r="I33" s="76" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="79" t="s">
-        <v>528</v>
-      </c>
-      <c r="B34" s="80" t="s">
-        <v>529</v>
-      </c>
-      <c r="C34" s="80" t="s">
-        <v>530</v>
-      </c>
-      <c r="D34" s="80" t="s">
-        <v>531</v>
-      </c>
-      <c r="E34" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F34" s="80" t="s">
-        <v>278</v>
-      </c>
-      <c r="G34" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H34" s="80" t="s">
-        <v>532</v>
-      </c>
-      <c r="I34" s="80" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="75" t="s">
-        <v>528</v>
-      </c>
-      <c r="B35" s="76" t="s">
-        <v>534</v>
-      </c>
-      <c r="C35" s="76" t="s">
-        <v>535</v>
-      </c>
-      <c r="D35" s="76" t="s">
-        <v>536</v>
-      </c>
-      <c r="E35" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F35" s="76" t="s">
-        <v>268</v>
-      </c>
-      <c r="G35" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H35" s="76" t="s">
-        <v>537</v>
-      </c>
-      <c r="I35" s="76" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="79" t="s">
-        <v>528</v>
-      </c>
-      <c r="B36" s="80" t="s">
-        <v>539</v>
-      </c>
-      <c r="C36" s="80" t="s">
-        <v>540</v>
-      </c>
-      <c r="D36" s="80" t="s">
-        <v>541</v>
-      </c>
-      <c r="E36" s="81" t="s">
-        <v>386</v>
-      </c>
-      <c r="F36" s="80" t="s">
-        <v>268</v>
-      </c>
-      <c r="G36" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H36" s="80" t="s">
-        <v>542</v>
-      </c>
-      <c r="I36" s="80" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="75" t="s">
-        <v>544</v>
-      </c>
-      <c r="B37" s="76" t="s">
-        <v>545</v>
-      </c>
-      <c r="C37" s="76" t="s">
-        <v>546</v>
-      </c>
-      <c r="D37" s="76" t="s">
-        <v>547</v>
-      </c>
-      <c r="E37" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F37" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="G37" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H37" s="76" t="s">
-        <v>548</v>
-      </c>
-      <c r="I37" s="76" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="79" t="s">
-        <v>544</v>
-      </c>
-      <c r="B38" s="80" t="s">
-        <v>550</v>
-      </c>
-      <c r="C38" s="80" t="s">
-        <v>551</v>
-      </c>
-      <c r="D38" s="80" t="s">
-        <v>552</v>
-      </c>
-      <c r="E38" s="85" t="s">
-        <v>441</v>
-      </c>
-      <c r="F38" s="80" t="s">
-        <v>268</v>
-      </c>
-      <c r="G38" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H38" s="80" t="s">
-        <v>553</v>
-      </c>
-      <c r="I38" s="80" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="75" t="s">
-        <v>544</v>
-      </c>
-      <c r="B39" s="76" t="s">
-        <v>555</v>
-      </c>
-      <c r="C39" s="76" t="s">
-        <v>556</v>
-      </c>
-      <c r="D39" s="76" t="s">
-        <v>557</v>
-      </c>
-      <c r="E39" s="77" t="s">
-        <v>386</v>
-      </c>
-      <c r="F39" s="76" t="s">
-        <v>278</v>
-      </c>
-      <c r="G39" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="H39" s="76" t="s">
-        <v>558</v>
-      </c>
-      <c r="I39" s="76" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="G39" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="H39" s="78" t="s">
+        <v>566</v>
+      </c>
+      <c r="I39" s="78" t="s">
+        <v>567</v>
+      </c>
+    </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="73" t="s">
-        <v>560</v>
-      </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="73"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="A42" s="75" t="s">
+        <v>568</v>
+      </c>
+      <c r="B42" s="75"/>
+      <c r="C42" s="75"/>
+      <c r="D42" s="75"/>
+      <c r="E42" s="75"/>
+      <c r="F42" s="75"/>
+      <c r="G42" s="75"/>
+      <c r="H42" s="75"/>
+      <c r="I42" s="75"/>
     </row>
     <row r="43" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="74" t="s">
-        <v>561</v>
-      </c>
-      <c r="B43" s="74" t="s">
-        <v>562</v>
-      </c>
-      <c r="C43" s="74" t="s">
-        <v>563</v>
-      </c>
-      <c r="D43" s="74" t="s">
-        <v>564</v>
-      </c>
-      <c r="E43" s="74" t="s">
-        <v>565</v>
-      </c>
-      <c r="F43" s="74" t="s">
+      <c r="A43" s="76" t="s">
+        <v>569</v>
+      </c>
+      <c r="B43" s="76" t="s">
+        <v>570</v>
+      </c>
+      <c r="C43" s="76" t="s">
+        <v>571</v>
+      </c>
+      <c r="D43" s="76" t="s">
+        <v>572</v>
+      </c>
+      <c r="E43" s="76" t="s">
+        <v>573</v>
+      </c>
+      <c r="F43" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="G43" s="74" t="s">
-        <v>566</v>
-      </c>
-      <c r="H43" s="74" t="s">
-        <v>567</v>
-      </c>
-      <c r="I43" s="74" t="s">
-        <v>568</v>
+      <c r="G43" s="76" t="s">
+        <v>574</v>
+      </c>
+      <c r="H43" s="76" t="s">
+        <v>575</v>
+      </c>
+      <c r="I43" s="76" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="79" t="s">
-        <v>569</v>
-      </c>
-      <c r="B44" s="80" t="s">
-        <v>570</v>
-      </c>
-      <c r="C44" s="80" t="s">
-        <v>571</v>
-      </c>
-      <c r="D44" s="80" t="s">
-        <v>572</v>
-      </c>
-      <c r="E44" s="86" t="n">
+      <c r="A44" s="81" t="s">
+        <v>577</v>
+      </c>
+      <c r="B44" s="82" t="s">
+        <v>578</v>
+      </c>
+      <c r="C44" s="82" t="s">
+        <v>579</v>
+      </c>
+      <c r="D44" s="82" t="s">
+        <v>580</v>
+      </c>
+      <c r="E44" s="88" t="n">
         <v>8</v>
       </c>
-      <c r="F44" s="87" t="n">
+      <c r="F44" s="89" t="n">
         <v>0.3</v>
       </c>
-      <c r="G44" s="88" t="n">
+      <c r="G44" s="90" t="n">
         <f aca="false">E44*F44</f>
         <v>2.4</v>
       </c>
-      <c r="H44" s="80" t="s">
-        <v>573</v>
-      </c>
-      <c r="I44" s="81" t="s">
-        <v>574</v>
+      <c r="H44" s="82" t="s">
+        <v>581</v>
+      </c>
+      <c r="I44" s="83" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="79" t="s">
-        <v>575</v>
-      </c>
-      <c r="B45" s="80" t="s">
-        <v>576</v>
-      </c>
-      <c r="C45" s="80" t="s">
-        <v>577</v>
-      </c>
-      <c r="D45" s="80" t="s">
-        <v>578</v>
-      </c>
-      <c r="E45" s="86" t="n">
+      <c r="A45" s="81" t="s">
+        <v>583</v>
+      </c>
+      <c r="B45" s="82" t="s">
+        <v>584</v>
+      </c>
+      <c r="C45" s="82" t="s">
+        <v>585</v>
+      </c>
+      <c r="D45" s="82" t="s">
+        <v>586</v>
+      </c>
+      <c r="E45" s="88" t="n">
         <v>15</v>
       </c>
-      <c r="F45" s="87" t="n">
+      <c r="F45" s="89" t="n">
         <v>0.55</v>
       </c>
-      <c r="G45" s="88" t="n">
+      <c r="G45" s="90" t="n">
         <f aca="false">E45*F45</f>
         <v>8.25</v>
       </c>
-      <c r="H45" s="80" t="s">
-        <v>579</v>
-      </c>
-      <c r="I45" s="81" t="s">
-        <v>574</v>
+      <c r="H45" s="82" t="s">
+        <v>587</v>
+      </c>
+      <c r="I45" s="83" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="79" t="s">
-        <v>580</v>
-      </c>
-      <c r="B46" s="80" t="s">
-        <v>581</v>
-      </c>
-      <c r="C46" s="80" t="s">
-        <v>582</v>
-      </c>
-      <c r="D46" s="80" t="s">
-        <v>583</v>
-      </c>
-      <c r="E46" s="86" t="n">
+      <c r="A46" s="81" t="s">
+        <v>588</v>
+      </c>
+      <c r="B46" s="82" t="s">
+        <v>589</v>
+      </c>
+      <c r="C46" s="82" t="s">
+        <v>590</v>
+      </c>
+      <c r="D46" s="82" t="s">
+        <v>591</v>
+      </c>
+      <c r="E46" s="88" t="n">
         <v>4.2</v>
       </c>
-      <c r="F46" s="87" t="n">
+      <c r="F46" s="89" t="n">
         <v>0.65</v>
       </c>
-      <c r="G46" s="88" t="n">
+      <c r="G46" s="90" t="n">
         <f aca="false">E46*F46</f>
         <v>2.73</v>
       </c>
-      <c r="H46" s="80" t="s">
-        <v>584</v>
-      </c>
-      <c r="I46" s="81" t="s">
-        <v>585</v>
+      <c r="H46" s="82" t="s">
+        <v>592</v>
+      </c>
+      <c r="I46" s="83" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="79" t="s">
-        <v>586</v>
-      </c>
-      <c r="B47" s="80" t="s">
-        <v>587</v>
-      </c>
-      <c r="C47" s="80" t="s">
-        <v>588</v>
-      </c>
-      <c r="D47" s="80" t="s">
-        <v>589</v>
-      </c>
-      <c r="E47" s="86" t="n">
+      <c r="A47" s="81" t="s">
+        <v>594</v>
+      </c>
+      <c r="B47" s="82" t="s">
+        <v>595</v>
+      </c>
+      <c r="C47" s="82" t="s">
+        <v>596</v>
+      </c>
+      <c r="D47" s="82" t="s">
+        <v>597</v>
+      </c>
+      <c r="E47" s="88" t="n">
         <v>2.5</v>
       </c>
-      <c r="F47" s="87" t="n">
+      <c r="F47" s="89" t="n">
         <v>0.5</v>
       </c>
-      <c r="G47" s="88" t="n">
+      <c r="G47" s="90" t="n">
         <f aca="false">E47*F47</f>
         <v>1.25</v>
       </c>
-      <c r="H47" s="80" t="s">
-        <v>590</v>
-      </c>
-      <c r="I47" s="81" t="s">
-        <v>585</v>
+      <c r="H47" s="82" t="s">
+        <v>598</v>
+      </c>
+      <c r="I47" s="83" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="79" t="s">
-        <v>591</v>
-      </c>
-      <c r="B48" s="80" t="s">
-        <v>592</v>
-      </c>
-      <c r="C48" s="80" t="s">
-        <v>593</v>
-      </c>
-      <c r="D48" s="80" t="s">
-        <v>594</v>
-      </c>
-      <c r="E48" s="86" t="n">
+      <c r="A48" s="81" t="s">
+        <v>599</v>
+      </c>
+      <c r="B48" s="82" t="s">
+        <v>600</v>
+      </c>
+      <c r="C48" s="82" t="s">
+        <v>601</v>
+      </c>
+      <c r="D48" s="82" t="s">
+        <v>602</v>
+      </c>
+      <c r="E48" s="88" t="n">
         <v>-6</v>
       </c>
-      <c r="F48" s="87" t="n">
+      <c r="F48" s="89" t="n">
         <v>0.45</v>
       </c>
-      <c r="G48" s="88" t="n">
+      <c r="G48" s="90" t="n">
         <f aca="false">E48*F48</f>
         <v>-2.7</v>
       </c>
-      <c r="H48" s="80" t="s">
-        <v>595</v>
-      </c>
-      <c r="I48" s="85" t="s">
-        <v>596</v>
+      <c r="H48" s="82" t="s">
+        <v>603</v>
+      </c>
+      <c r="I48" s="87" t="s">
+        <v>604</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="79" t="s">
-        <v>597</v>
-      </c>
-      <c r="B49" s="80" t="s">
-        <v>598</v>
-      </c>
-      <c r="C49" s="80" t="s">
-        <v>599</v>
-      </c>
-      <c r="D49" s="80" t="s">
-        <v>600</v>
-      </c>
-      <c r="E49" s="86" t="n">
+      <c r="A49" s="81" t="s">
+        <v>605</v>
+      </c>
+      <c r="B49" s="82" t="s">
+        <v>606</v>
+      </c>
+      <c r="C49" s="82" t="s">
+        <v>607</v>
+      </c>
+      <c r="D49" s="82" t="s">
+        <v>608</v>
+      </c>
+      <c r="E49" s="88" t="n">
         <v>-5</v>
       </c>
-      <c r="F49" s="87" t="n">
+      <c r="F49" s="89" t="n">
         <v>0.6</v>
       </c>
-      <c r="G49" s="88" t="n">
+      <c r="G49" s="90" t="n">
         <f aca="false">E49*F49</f>
         <v>-3</v>
       </c>
-      <c r="H49" s="80" t="s">
-        <v>601</v>
-      </c>
-      <c r="I49" s="85" t="s">
-        <v>602</v>
+      <c r="H49" s="82" t="s">
+        <v>609</v>
+      </c>
+      <c r="I49" s="87" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="79" t="s">
-        <v>603</v>
-      </c>
-      <c r="B50" s="80" t="s">
-        <v>604</v>
-      </c>
-      <c r="C50" s="80" t="s">
-        <v>605</v>
-      </c>
-      <c r="D50" s="80" t="s">
-        <v>606</v>
-      </c>
-      <c r="E50" s="86" t="n">
+      <c r="A50" s="81" t="s">
+        <v>611</v>
+      </c>
+      <c r="B50" s="82" t="s">
+        <v>612</v>
+      </c>
+      <c r="C50" s="82" t="s">
+        <v>613</v>
+      </c>
+      <c r="D50" s="82" t="s">
+        <v>614</v>
+      </c>
+      <c r="E50" s="88" t="n">
         <v>12</v>
       </c>
-      <c r="F50" s="87" t="n">
+      <c r="F50" s="89" t="n">
         <v>0.15</v>
       </c>
-      <c r="G50" s="88" t="n">
+      <c r="G50" s="90" t="n">
         <f aca="false">E50*F50</f>
         <v>1.8</v>
       </c>
-      <c r="H50" s="80" t="s">
-        <v>607</v>
-      </c>
-      <c r="I50" s="81" t="s">
-        <v>608</v>
+      <c r="H50" s="82" t="s">
+        <v>615</v>
+      </c>
+      <c r="I50" s="83" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="79" t="s">
-        <v>609</v>
-      </c>
-      <c r="B51" s="80" t="s">
-        <v>610</v>
-      </c>
-      <c r="C51" s="80" t="s">
-        <v>611</v>
-      </c>
-      <c r="D51" s="80" t="s">
-        <v>612</v>
-      </c>
-      <c r="E51" s="86" t="n">
+      <c r="A51" s="81" t="s">
+        <v>617</v>
+      </c>
+      <c r="B51" s="82" t="s">
+        <v>618</v>
+      </c>
+      <c r="C51" s="82" t="s">
+        <v>619</v>
+      </c>
+      <c r="D51" s="82" t="s">
+        <v>620</v>
+      </c>
+      <c r="E51" s="88" t="n">
         <v>3.5</v>
       </c>
-      <c r="F51" s="87" t="n">
+      <c r="F51" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="G51" s="88" t="n">
+      <c r="G51" s="90" t="n">
         <f aca="false">E51*F51</f>
         <v>1.4</v>
       </c>
-      <c r="H51" s="80" t="s">
-        <v>595</v>
-      </c>
-      <c r="I51" s="81" t="s">
-        <v>585</v>
+      <c r="H51" s="82" t="s">
+        <v>603</v>
+      </c>
+      <c r="I51" s="83" t="s">
+        <v>593</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="79" t="s">
-        <v>613</v>
-      </c>
-      <c r="B52" s="80" t="s">
-        <v>614</v>
-      </c>
-      <c r="C52" s="80" t="s">
-        <v>615</v>
-      </c>
-      <c r="D52" s="80" t="s">
-        <v>616</v>
-      </c>
-      <c r="E52" s="86" t="n">
+      <c r="A52" s="81" t="s">
+        <v>621</v>
+      </c>
+      <c r="B52" s="82" t="s">
+        <v>622</v>
+      </c>
+      <c r="C52" s="82" t="s">
+        <v>623</v>
+      </c>
+      <c r="D52" s="82" t="s">
+        <v>624</v>
+      </c>
+      <c r="E52" s="88" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F52" s="87" t="n">
+      <c r="F52" s="89" t="n">
         <v>0.35</v>
       </c>
-      <c r="G52" s="88" t="n">
+      <c r="G52" s="90" t="n">
         <f aca="false">E52*F52</f>
         <v>-0.525</v>
       </c>
-      <c r="H52" s="80" t="s">
-        <v>617</v>
-      </c>
-      <c r="I52" s="85" t="s">
-        <v>602</v>
+      <c r="H52" s="82" t="s">
+        <v>625</v>
+      </c>
+      <c r="I52" s="87" t="s">
+        <v>610</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="79" t="s">
-        <v>618</v>
-      </c>
-      <c r="B53" s="80" t="s">
-        <v>619</v>
-      </c>
-      <c r="C53" s="80" t="s">
-        <v>620</v>
-      </c>
-      <c r="D53" s="80" t="s">
-        <v>621</v>
-      </c>
-      <c r="E53" s="86" t="n">
+      <c r="A53" s="81" t="s">
+        <v>626</v>
+      </c>
+      <c r="B53" s="82" t="s">
+        <v>627</v>
+      </c>
+      <c r="C53" s="82" t="s">
+        <v>628</v>
+      </c>
+      <c r="D53" s="82" t="s">
+        <v>629</v>
+      </c>
+      <c r="E53" s="88" t="n">
         <v>20</v>
       </c>
-      <c r="F53" s="87" t="n">
+      <c r="F53" s="89" t="n">
         <v>0.2</v>
       </c>
-      <c r="G53" s="88" t="n">
+      <c r="G53" s="90" t="n">
         <f aca="false">E53*F53</f>
         <v>4</v>
       </c>
-      <c r="H53" s="80" t="s">
-        <v>617</v>
-      </c>
-      <c r="I53" s="81" t="s">
-        <v>574</v>
+      <c r="H53" s="82" t="s">
+        <v>625</v>
+      </c>
+      <c r="I53" s="83" t="s">
+        <v>582</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="89" t="s">
-        <v>622</v>
-      </c>
-      <c r="B54" s="90"/>
-      <c r="C54" s="90"/>
-      <c r="D54" s="90"/>
-      <c r="E54" s="90"/>
-      <c r="F54" s="90"/>
-      <c r="G54" s="91" t="n">
+      <c r="A54" s="91" t="s">
+        <v>630</v>
+      </c>
+      <c r="B54" s="92"/>
+      <c r="C54" s="92"/>
+      <c r="D54" s="92"/>
+      <c r="E54" s="92"/>
+      <c r="F54" s="92"/>
+      <c r="G54" s="93" t="n">
         <f aca="false">SUM(G44:G53)</f>
         <v>15.605</v>
       </c>
-      <c r="H54" s="90"/>
-      <c r="I54" s="90"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="H54" s="92"/>
+      <c r="I54" s="92"/>
+    </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="73" t="s">
-        <v>623</v>
-      </c>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
+      <c r="A57" s="75" t="s">
+        <v>631</v>
+      </c>
+      <c r="B57" s="75"/>
+      <c r="C57" s="75"/>
+      <c r="D57" s="75"/>
+      <c r="E57" s="75"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="75"/>
+      <c r="H57" s="75"/>
+      <c r="I57" s="75"/>
     </row>
     <row r="58" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="74" t="s">
-        <v>624</v>
-      </c>
-      <c r="B58" s="74" t="s">
-        <v>625</v>
-      </c>
-      <c r="C58" s="74" t="s">
-        <v>626</v>
-      </c>
-      <c r="D58" s="74" t="s">
-        <v>627</v>
-      </c>
-      <c r="E58" s="74" t="s">
-        <v>628</v>
-      </c>
-      <c r="F58" s="74" t="s">
-        <v>629</v>
+      <c r="A58" s="76" t="s">
+        <v>632</v>
+      </c>
+      <c r="B58" s="76" t="s">
+        <v>633</v>
+      </c>
+      <c r="C58" s="76" t="s">
+        <v>634</v>
+      </c>
+      <c r="D58" s="76" t="s">
+        <v>635</v>
+      </c>
+      <c r="E58" s="76" t="s">
+        <v>636</v>
+      </c>
+      <c r="F58" s="76" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="92" t="s">
-        <v>630</v>
-      </c>
-      <c r="B59" s="93" t="s">
-        <v>631</v>
-      </c>
-      <c r="C59" s="93" t="s">
-        <v>632</v>
-      </c>
-      <c r="D59" s="94" t="s">
+      <c r="A59" s="94" t="s">
+        <v>638</v>
+      </c>
+      <c r="B59" s="95" t="s">
+        <v>639</v>
+      </c>
+      <c r="C59" s="95" t="s">
+        <v>640</v>
+      </c>
+      <c r="D59" s="96" t="s">
         <v>268</v>
       </c>
-      <c r="E59" s="93" t="s">
-        <v>633</v>
-      </c>
-      <c r="F59" s="93" t="s">
-        <v>634</v>
+      <c r="E59" s="95" t="s">
+        <v>641</v>
+      </c>
+      <c r="F59" s="95" t="s">
+        <v>642</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="95" t="s">
-        <v>635</v>
-      </c>
-      <c r="B60" s="80" t="s">
-        <v>636</v>
-      </c>
-      <c r="C60" s="80" t="s">
-        <v>637</v>
-      </c>
-      <c r="D60" s="81" t="s">
+      <c r="A60" s="97" t="s">
+        <v>643</v>
+      </c>
+      <c r="B60" s="82" t="s">
+        <v>644</v>
+      </c>
+      <c r="C60" s="82" t="s">
+        <v>645</v>
+      </c>
+      <c r="D60" s="83" t="s">
         <v>268</v>
       </c>
-      <c r="E60" s="80" t="s">
-        <v>638</v>
-      </c>
-      <c r="F60" s="80" t="s">
-        <v>639</v>
+      <c r="E60" s="82" t="s">
+        <v>646</v>
+      </c>
+      <c r="F60" s="82" t="s">
+        <v>647</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="92" t="s">
-        <v>640</v>
-      </c>
-      <c r="B61" s="93" t="s">
-        <v>641</v>
-      </c>
-      <c r="C61" s="93" t="s">
-        <v>642</v>
-      </c>
-      <c r="D61" s="96" t="s">
+      <c r="A61" s="94" t="s">
+        <v>648</v>
+      </c>
+      <c r="B61" s="95" t="s">
+        <v>649</v>
+      </c>
+      <c r="C61" s="95" t="s">
+        <v>650</v>
+      </c>
+      <c r="D61" s="98" t="s">
         <v>278</v>
       </c>
-      <c r="E61" s="93" t="s">
-        <v>643</v>
-      </c>
-      <c r="F61" s="93" t="s">
-        <v>644</v>
+      <c r="E61" s="95" t="s">
+        <v>651</v>
+      </c>
+      <c r="F61" s="95" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="95" t="s">
-        <v>645</v>
-      </c>
-      <c r="B62" s="80" t="s">
-        <v>646</v>
-      </c>
-      <c r="C62" s="80" t="s">
-        <v>647</v>
-      </c>
-      <c r="D62" s="84" t="s">
+      <c r="A62" s="97" t="s">
+        <v>653</v>
+      </c>
+      <c r="B62" s="82" t="s">
+        <v>654</v>
+      </c>
+      <c r="C62" s="82" t="s">
+        <v>655</v>
+      </c>
+      <c r="D62" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="E62" s="80" t="s">
-        <v>648</v>
-      </c>
-      <c r="F62" s="80" t="s">
-        <v>649</v>
+      <c r="E62" s="82" t="s">
+        <v>656</v>
+      </c>
+      <c r="F62" s="82" t="s">
+        <v>657</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="92" t="s">
-        <v>650</v>
-      </c>
-      <c r="B63" s="93" t="s">
-        <v>651</v>
-      </c>
-      <c r="C63" s="93" t="s">
-        <v>652</v>
-      </c>
-      <c r="D63" s="94" t="s">
+      <c r="A63" s="94" t="s">
+        <v>658</v>
+      </c>
+      <c r="B63" s="95" t="s">
+        <v>659</v>
+      </c>
+      <c r="C63" s="95" t="s">
+        <v>660</v>
+      </c>
+      <c r="D63" s="96" t="s">
         <v>268</v>
       </c>
-      <c r="E63" s="93" t="s">
-        <v>653</v>
-      </c>
-      <c r="F63" s="93" t="s">
-        <v>654</v>
+      <c r="E63" s="95" t="s">
+        <v>661</v>
+      </c>
+      <c r="F63" s="95" t="s">
+        <v>662</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="95" t="s">
-        <v>655</v>
-      </c>
-      <c r="B64" s="80" t="s">
-        <v>656</v>
-      </c>
-      <c r="C64" s="80" t="s">
-        <v>657</v>
-      </c>
-      <c r="D64" s="84" t="s">
+      <c r="A64" s="97" t="s">
+        <v>663</v>
+      </c>
+      <c r="B64" s="82" t="s">
+        <v>664</v>
+      </c>
+      <c r="C64" s="82" t="s">
+        <v>665</v>
+      </c>
+      <c r="D64" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="E64" s="80" t="s">
-        <v>658</v>
-      </c>
-      <c r="F64" s="80" t="s">
-        <v>659</v>
+      <c r="E64" s="82" t="s">
+        <v>666</v>
+      </c>
+      <c r="F64" s="82" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="92" t="s">
-        <v>660</v>
-      </c>
-      <c r="B65" s="93" t="s">
-        <v>661</v>
-      </c>
-      <c r="C65" s="93" t="s">
-        <v>662</v>
-      </c>
-      <c r="D65" s="94" t="s">
+      <c r="A65" s="94" t="s">
+        <v>668</v>
+      </c>
+      <c r="B65" s="95" t="s">
+        <v>669</v>
+      </c>
+      <c r="C65" s="95" t="s">
+        <v>670</v>
+      </c>
+      <c r="D65" s="96" t="s">
         <v>268</v>
       </c>
-      <c r="E65" s="93" t="s">
-        <v>663</v>
-      </c>
-      <c r="F65" s="93" t="s">
-        <v>664</v>
+      <c r="E65" s="95" t="s">
+        <v>671</v>
+      </c>
+      <c r="F65" s="95" t="s">
+        <v>672</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="95" t="s">
-        <v>665</v>
-      </c>
-      <c r="B66" s="80" t="s">
-        <v>666</v>
-      </c>
-      <c r="C66" s="80" t="s">
-        <v>667</v>
-      </c>
-      <c r="D66" s="84" t="s">
+      <c r="A66" s="97" t="s">
+        <v>673</v>
+      </c>
+      <c r="B66" s="82" t="s">
+        <v>674</v>
+      </c>
+      <c r="C66" s="82" t="s">
+        <v>675</v>
+      </c>
+      <c r="D66" s="86" t="s">
         <v>278</v>
       </c>
-      <c r="E66" s="80" t="s">
-        <v>668</v>
-      </c>
-      <c r="F66" s="80" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="E66" s="82" t="s">
+        <v>676</v>
+      </c>
+      <c r="F66" s="82" t="s">
+        <v>677</v>
+      </c>
+    </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="73" t="s">
-        <v>670</v>
-      </c>
-      <c r="B69" s="73"/>
-      <c r="C69" s="73"/>
-      <c r="D69" s="73"/>
-      <c r="E69" s="73"/>
-      <c r="F69" s="73"/>
-      <c r="G69" s="73"/>
-      <c r="H69" s="73"/>
-      <c r="I69" s="73"/>
+      <c r="A69" s="75" t="s">
+        <v>678</v>
+      </c>
+      <c r="B69" s="75"/>
+      <c r="C69" s="75"/>
+      <c r="D69" s="75"/>
+      <c r="E69" s="75"/>
+      <c r="F69" s="75"/>
+      <c r="G69" s="75"/>
+      <c r="H69" s="75"/>
+      <c r="I69" s="75"/>
     </row>
     <row r="70" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="74" t="s">
-        <v>671</v>
-      </c>
-      <c r="B70" s="74" t="s">
-        <v>672</v>
-      </c>
-      <c r="C70" s="74" t="s">
-        <v>673</v>
-      </c>
-      <c r="D70" s="74" t="s">
-        <v>674</v>
-      </c>
-      <c r="E70" s="74" t="s">
-        <v>675</v>
-      </c>
-      <c r="F70" s="74" t="s">
-        <v>676</v>
+      <c r="A70" s="76" t="s">
+        <v>679</v>
+      </c>
+      <c r="B70" s="76" t="s">
+        <v>680</v>
+      </c>
+      <c r="C70" s="76" t="s">
+        <v>681</v>
+      </c>
+      <c r="D70" s="76" t="s">
+        <v>682</v>
+      </c>
+      <c r="E70" s="76" t="s">
+        <v>683</v>
+      </c>
+      <c r="F70" s="76" t="s">
+        <v>684</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="75" t="s">
-        <v>677</v>
-      </c>
-      <c r="B71" s="97" t="n">
+      <c r="A71" s="77" t="s">
+        <v>685</v>
+      </c>
+      <c r="B71" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="C71" s="97" t="n">
+      <c r="C71" s="99" t="n">
         <v>9</v>
       </c>
-      <c r="D71" s="97" t="n">
+      <c r="D71" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="E71" s="98" t="n">
+      <c r="E71" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F71" s="83" t="s">
-        <v>678</v>
+      <c r="F71" s="85" t="s">
+        <v>686</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="79" t="s">
-        <v>679</v>
-      </c>
-      <c r="B72" s="99" t="n">
+      <c r="A72" s="81" t="s">
+        <v>687</v>
+      </c>
+      <c r="B72" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="C72" s="100" t="n">
+      <c r="C72" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="D72" s="100" t="n">
+      <c r="D72" s="102" t="n">
         <v>5</v>
       </c>
-      <c r="E72" s="98" t="n">
+      <c r="E72" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F72" s="101" t="s">
-        <v>680</v>
+      <c r="F72" s="103" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="75" t="s">
-        <v>681</v>
-      </c>
-      <c r="B73" s="99" t="n">
+      <c r="A73" s="77" t="s">
+        <v>689</v>
+      </c>
+      <c r="B73" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="C73" s="99" t="n">
+      <c r="C73" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="D73" s="102" t="n">
+      <c r="D73" s="104" t="n">
         <v>7</v>
       </c>
-      <c r="E73" s="98" t="n">
+      <c r="E73" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F73" s="101" t="s">
-        <v>682</v>
+      <c r="F73" s="103" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="79" t="s">
-        <v>683</v>
-      </c>
-      <c r="B74" s="100" t="n">
+      <c r="A74" s="81" t="s">
+        <v>691</v>
+      </c>
+      <c r="B74" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="C74" s="100" t="n">
+      <c r="C74" s="102" t="n">
         <v>5</v>
       </c>
-      <c r="D74" s="100" t="n">
+      <c r="D74" s="102" t="n">
         <v>6</v>
       </c>
-      <c r="E74" s="98" t="n">
+      <c r="E74" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F74" s="103" t="s">
-        <v>684</v>
+      <c r="F74" s="105" t="s">
+        <v>692</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="75" t="s">
-        <v>685</v>
-      </c>
-      <c r="B75" s="99" t="n">
+      <c r="A75" s="77" t="s">
+        <v>693</v>
+      </c>
+      <c r="B75" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="C75" s="99" t="n">
+      <c r="C75" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="D75" s="99" t="n">
+      <c r="D75" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="E75" s="98" t="n">
+      <c r="E75" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F75" s="92" t="s">
-        <v>686</v>
+      <c r="F75" s="94" t="s">
+        <v>694</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="79" t="s">
-        <v>687</v>
-      </c>
-      <c r="B76" s="99" t="n">
+      <c r="A76" s="81" t="s">
+        <v>695</v>
+      </c>
+      <c r="B76" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="C76" s="99" t="n">
+      <c r="C76" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="D76" s="100" t="n">
+      <c r="D76" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="E76" s="98" t="n">
+      <c r="E76" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F76" s="101" t="s">
-        <v>688</v>
+      <c r="F76" s="103" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="75" t="s">
-        <v>689</v>
-      </c>
-      <c r="B77" s="97" t="n">
+      <c r="A77" s="77" t="s">
+        <v>697</v>
+      </c>
+      <c r="B77" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="C77" s="102" t="n">
+      <c r="C77" s="104" t="n">
         <v>5</v>
       </c>
-      <c r="D77" s="102" t="n">
+      <c r="D77" s="104" t="n">
         <v>6</v>
       </c>
-      <c r="E77" s="98" t="n">
+      <c r="E77" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F77" s="83" t="s">
-        <v>690</v>
+      <c r="F77" s="85" t="s">
+        <v>698</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="79" t="s">
-        <v>691</v>
-      </c>
-      <c r="B78" s="99" t="n">
+      <c r="A78" s="81" t="s">
+        <v>699</v>
+      </c>
+      <c r="B78" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="99" t="n">
+      <c r="C78" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="D78" s="100" t="n">
+      <c r="D78" s="102" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="98" t="n">
+      <c r="E78" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F78" s="92" t="s">
-        <v>692</v>
+      <c r="F78" s="94" t="s">
+        <v>700</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="75" t="s">
-        <v>693</v>
-      </c>
-      <c r="B79" s="99" t="n">
+      <c r="A79" s="77" t="s">
+        <v>701</v>
+      </c>
+      <c r="B79" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="C79" s="99" t="n">
+      <c r="C79" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D79" s="99" t="n">
+      <c r="D79" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="98" t="n">
+      <c r="E79" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F79" s="92" t="s">
-        <v>694</v>
+      <c r="F79" s="94" t="s">
+        <v>702</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="79" t="s">
-        <v>695</v>
-      </c>
-      <c r="B80" s="99" t="n">
+      <c r="A80" s="81" t="s">
+        <v>703</v>
+      </c>
+      <c r="B80" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="99" t="n">
+      <c r="C80" s="101" t="n">
         <v>2</v>
       </c>
-      <c r="D80" s="100" t="n">
+      <c r="D80" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="98" t="n">
+      <c r="E80" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F80" s="92" t="s">
-        <v>696</v>
+      <c r="F80" s="94" t="s">
+        <v>704</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="75" t="s">
-        <v>697</v>
-      </c>
-      <c r="B81" s="99" t="n">
+      <c r="A81" s="77" t="s">
+        <v>705</v>
+      </c>
+      <c r="B81" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="C81" s="99" t="n">
+      <c r="C81" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D81" s="99" t="n">
+      <c r="D81" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="E81" s="98" t="n">
+      <c r="E81" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F81" s="92" t="s">
-        <v>698</v>
+      <c r="F81" s="94" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="79" t="s">
-        <v>699</v>
-      </c>
-      <c r="B82" s="99" t="n">
+      <c r="A82" s="81" t="s">
+        <v>707</v>
+      </c>
+      <c r="B82" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="C82" s="99" t="n">
+      <c r="C82" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D82" s="100" t="n">
+      <c r="D82" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="E82" s="98" t="n">
+      <c r="E82" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F82" s="92" t="s">
-        <v>700</v>
+      <c r="F82" s="94" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="75" t="s">
-        <v>701</v>
-      </c>
-      <c r="B83" s="99" t="n">
+      <c r="A83" s="77" t="s">
+        <v>709</v>
+      </c>
+      <c r="B83" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="C83" s="99" t="n">
+      <c r="C83" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D83" s="99" t="n">
+      <c r="D83" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="E83" s="98" t="n">
+      <c r="E83" s="100" t="n">
         <v>9</v>
       </c>
-      <c r="F83" s="92" t="s">
-        <v>702</v>
+      <c r="F83" s="94" t="s">
+        <v>710</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="79" t="s">
-        <v>703</v>
-      </c>
-      <c r="B84" s="99" t="n">
+      <c r="A84" s="81" t="s">
+        <v>711</v>
+      </c>
+      <c r="B84" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="C84" s="100" t="n">
+      <c r="C84" s="102" t="n">
         <v>4</v>
       </c>
-      <c r="D84" s="100" t="n">
+      <c r="D84" s="102" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="98" t="n">
+      <c r="E84" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F84" s="103" t="s">
-        <v>704</v>
+      <c r="F84" s="105" t="s">
+        <v>712</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="75" t="s">
-        <v>705</v>
-      </c>
-      <c r="B85" s="99" t="n">
+      <c r="A85" s="77" t="s">
+        <v>713</v>
+      </c>
+      <c r="B85" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="C85" s="99" t="n">
+      <c r="C85" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="D85" s="102" t="n">
+      <c r="D85" s="104" t="n">
         <v>6</v>
       </c>
-      <c r="E85" s="98" t="n">
+      <c r="E85" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F85" s="101" t="s">
-        <v>706</v>
+      <c r="F85" s="103" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="79" t="s">
-        <v>707</v>
-      </c>
-      <c r="B86" s="99" t="n">
+      <c r="A86" s="81" t="s">
+        <v>715</v>
+      </c>
+      <c r="B86" s="101" t="n">
         <v>1</v>
       </c>
-      <c r="C86" s="99" t="n">
+      <c r="C86" s="101" t="n">
         <v>0</v>
       </c>
-      <c r="D86" s="99" t="n">
+      <c r="D86" s="101" t="n">
         <v>3</v>
       </c>
-      <c r="E86" s="98" t="n">
+      <c r="E86" s="100" t="n">
         <v>8</v>
       </c>
-      <c r="F86" s="92" t="s">
-        <v>708</v>
+      <c r="F86" s="94" t="s">
+        <v>716</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="104" t="s">
-        <v>709</v>
-      </c>
-      <c r="B87" s="105" t="n">
+      <c r="A87" s="106" t="s">
+        <v>717</v>
+      </c>
+      <c r="B87" s="107" t="n">
         <f aca="false">AVERAGE(B71:B86)</f>
         <v>2.375</v>
       </c>
-      <c r="C87" s="105" t="n">
+      <c r="C87" s="107" t="n">
         <f aca="false">AVERAGE(C71:C86)</f>
         <v>2.3125</v>
       </c>
-      <c r="D87" s="105" t="n">
+      <c r="D87" s="107" t="n">
         <f aca="false">AVERAGE(D71:D86)</f>
         <v>4.625</v>
       </c>
-      <c r="E87" s="105" t="n">
+      <c r="E87" s="107" t="n">
         <f aca="false">AVERAGE(E71:E86)</f>
         <v>8.5625</v>
       </c>
-      <c r="F87" s="90"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="F87" s="92"/>
+    </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="73" t="s">
-        <v>710</v>
-      </c>
-      <c r="B90" s="73"/>
-      <c r="C90" s="73"/>
-      <c r="D90" s="73"/>
-      <c r="E90" s="73"/>
-      <c r="F90" s="73"/>
-      <c r="G90" s="73"/>
-      <c r="H90" s="73"/>
-      <c r="I90" s="73"/>
+      <c r="A90" s="75" t="s">
+        <v>718</v>
+      </c>
+      <c r="B90" s="75"/>
+      <c r="C90" s="75"/>
+      <c r="D90" s="75"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
     </row>
     <row r="91" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="74" t="s">
-        <v>711</v>
-      </c>
-      <c r="B91" s="74" t="s">
-        <v>712</v>
-      </c>
-      <c r="C91" s="74" t="s">
-        <v>713</v>
-      </c>
-      <c r="D91" s="74" t="s">
+      <c r="A91" s="76" t="s">
+        <v>719</v>
+      </c>
+      <c r="B91" s="76" t="s">
+        <v>720</v>
+      </c>
+      <c r="C91" s="76" t="s">
+        <v>721</v>
+      </c>
+      <c r="D91" s="76" t="s">
         <v>221</v>
       </c>
-      <c r="E91" s="74" t="s">
-        <v>714</v>
-      </c>
-      <c r="F91" s="74" t="s">
-        <v>715</v>
-      </c>
-      <c r="G91" s="74" t="s">
-        <v>716</v>
+      <c r="E91" s="76" t="s">
+        <v>722</v>
+      </c>
+      <c r="F91" s="76" t="s">
+        <v>723</v>
+      </c>
+      <c r="G91" s="76" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="79" t="s">
-        <v>330</v>
-      </c>
-      <c r="B92" s="80" t="s">
-        <v>717</v>
-      </c>
-      <c r="C92" s="81" t="s">
-        <v>718</v>
-      </c>
-      <c r="D92" s="87" t="n">
+      <c r="A92" s="81" t="s">
+        <v>338</v>
+      </c>
+      <c r="B92" s="82" t="s">
+        <v>725</v>
+      </c>
+      <c r="C92" s="83" t="s">
+        <v>726</v>
+      </c>
+      <c r="D92" s="89" t="n">
         <v>0.45</v>
       </c>
-      <c r="E92" s="80" t="s">
-        <v>719</v>
-      </c>
-      <c r="F92" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G92" s="80" t="s">
-        <v>720</v>
+      <c r="E92" s="82" t="s">
+        <v>727</v>
+      </c>
+      <c r="F92" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G92" s="82" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="79" t="s">
-        <v>333</v>
-      </c>
-      <c r="B93" s="80" t="s">
-        <v>721</v>
-      </c>
-      <c r="C93" s="81" t="s">
-        <v>718</v>
-      </c>
-      <c r="D93" s="87" t="n">
+      <c r="A93" s="81" t="s">
+        <v>341</v>
+      </c>
+      <c r="B93" s="82" t="s">
+        <v>729</v>
+      </c>
+      <c r="C93" s="83" t="s">
+        <v>726</v>
+      </c>
+      <c r="D93" s="89" t="n">
         <v>0.35</v>
       </c>
-      <c r="E93" s="80" t="s">
-        <v>722</v>
-      </c>
-      <c r="F93" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="G93" s="80" t="s">
-        <v>723</v>
+      <c r="E93" s="82" t="s">
+        <v>730</v>
+      </c>
+      <c r="F93" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="G93" s="82" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="79" t="s">
-        <v>333</v>
-      </c>
-      <c r="B94" s="80" t="s">
-        <v>724</v>
-      </c>
-      <c r="C94" s="81" t="s">
-        <v>725</v>
-      </c>
-      <c r="D94" s="87" t="n">
+      <c r="A94" s="81" t="s">
+        <v>341</v>
+      </c>
+      <c r="B94" s="82" t="s">
+        <v>732</v>
+      </c>
+      <c r="C94" s="83" t="s">
+        <v>733</v>
+      </c>
+      <c r="D94" s="89" t="n">
         <v>0.6</v>
       </c>
-      <c r="E94" s="80" t="s">
+      <c r="E94" s="82" t="s">
+        <v>734</v>
+      </c>
+      <c r="F94" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G94" s="82" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="81" t="s">
+        <v>354</v>
+      </c>
+      <c r="B95" s="82" t="s">
+        <v>736</v>
+      </c>
+      <c r="C95" s="83" t="s">
+        <v>737</v>
+      </c>
+      <c r="D95" s="89" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E95" s="82" t="s">
+        <v>738</v>
+      </c>
+      <c r="F95" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G95" s="82" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="81" t="s">
+        <v>354</v>
+      </c>
+      <c r="B96" s="82" t="s">
+        <v>740</v>
+      </c>
+      <c r="C96" s="83" t="s">
         <v>726</v>
       </c>
-      <c r="F94" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G94" s="80" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="79" t="s">
-        <v>346</v>
-      </c>
-      <c r="B95" s="80" t="s">
-        <v>728</v>
-      </c>
-      <c r="C95" s="81" t="s">
-        <v>729</v>
-      </c>
-      <c r="D95" s="87" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E95" s="80" t="s">
-        <v>730</v>
-      </c>
-      <c r="F95" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G95" s="80" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="79" t="s">
-        <v>346</v>
-      </c>
-      <c r="B96" s="80" t="s">
-        <v>732</v>
-      </c>
-      <c r="C96" s="81" t="s">
-        <v>718</v>
-      </c>
-      <c r="D96" s="87" t="n">
+      <c r="D96" s="89" t="n">
         <v>0.5</v>
       </c>
-      <c r="E96" s="80" t="s">
-        <v>733</v>
-      </c>
-      <c r="F96" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="G96" s="80" t="s">
-        <v>734</v>
+      <c r="E96" s="82" t="s">
+        <v>741</v>
+      </c>
+      <c r="F96" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="G96" s="82" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="79" t="s">
-        <v>735</v>
-      </c>
-      <c r="B97" s="80" t="s">
-        <v>736</v>
-      </c>
-      <c r="C97" s="81" t="s">
-        <v>737</v>
-      </c>
-      <c r="D97" s="87" t="n">
+      <c r="A97" s="81" t="s">
+        <v>743</v>
+      </c>
+      <c r="B97" s="82" t="s">
+        <v>744</v>
+      </c>
+      <c r="C97" s="83" t="s">
+        <v>745</v>
+      </c>
+      <c r="D97" s="89" t="n">
         <v>0.3</v>
       </c>
-      <c r="E97" s="80" t="s">
-        <v>738</v>
-      </c>
-      <c r="F97" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G97" s="80" t="s">
-        <v>739</v>
+      <c r="E97" s="82" t="s">
+        <v>746</v>
+      </c>
+      <c r="F97" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G97" s="82" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="79" t="s">
-        <v>740</v>
-      </c>
-      <c r="B98" s="80" t="s">
-        <v>741</v>
-      </c>
-      <c r="C98" s="81" t="s">
-        <v>742</v>
-      </c>
-      <c r="D98" s="87" t="n">
+      <c r="A98" s="81" t="s">
+        <v>748</v>
+      </c>
+      <c r="B98" s="82" t="s">
+        <v>749</v>
+      </c>
+      <c r="C98" s="83" t="s">
+        <v>750</v>
+      </c>
+      <c r="D98" s="89" t="n">
         <v>0.55</v>
       </c>
-      <c r="E98" s="80" t="s">
-        <v>743</v>
-      </c>
-      <c r="F98" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G98" s="80" t="s">
-        <v>744</v>
+      <c r="E98" s="82" t="s">
+        <v>751</v>
+      </c>
+      <c r="F98" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G98" s="82" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="79" t="s">
-        <v>745</v>
-      </c>
-      <c r="B99" s="80" t="s">
-        <v>746</v>
-      </c>
-      <c r="C99" s="81" t="s">
-        <v>742</v>
-      </c>
-      <c r="D99" s="87" t="n">
+      <c r="A99" s="81" t="s">
+        <v>753</v>
+      </c>
+      <c r="B99" s="82" t="s">
+        <v>754</v>
+      </c>
+      <c r="C99" s="83" t="s">
+        <v>750</v>
+      </c>
+      <c r="D99" s="89" t="n">
         <v>0.4</v>
       </c>
-      <c r="E99" s="80" t="s">
-        <v>747</v>
-      </c>
-      <c r="F99" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="G99" s="80" t="s">
-        <v>748</v>
+      <c r="E99" s="82" t="s">
+        <v>755</v>
+      </c>
+      <c r="F99" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="G99" s="82" t="s">
+        <v>756</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="79" t="s">
-        <v>749</v>
-      </c>
-      <c r="B100" s="80" t="s">
-        <v>750</v>
-      </c>
-      <c r="C100" s="81" t="s">
-        <v>751</v>
-      </c>
-      <c r="D100" s="87" t="n">
+      <c r="A100" s="81" t="s">
+        <v>757</v>
+      </c>
+      <c r="B100" s="82" t="s">
+        <v>758</v>
+      </c>
+      <c r="C100" s="83" t="s">
+        <v>759</v>
+      </c>
+      <c r="D100" s="89" t="n">
         <v>0.35</v>
       </c>
-      <c r="E100" s="80" t="s">
-        <v>752</v>
-      </c>
-      <c r="F100" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G100" s="80" t="s">
-        <v>753</v>
+      <c r="E100" s="82" t="s">
+        <v>760</v>
+      </c>
+      <c r="F100" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G100" s="82" t="s">
+        <v>761</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="79" t="s">
-        <v>754</v>
-      </c>
-      <c r="B101" s="80" t="s">
-        <v>755</v>
-      </c>
-      <c r="C101" s="106" t="s">
-        <v>754</v>
-      </c>
-      <c r="D101" s="87" t="n">
+      <c r="A101" s="81" t="s">
+        <v>762</v>
+      </c>
+      <c r="B101" s="82" t="s">
+        <v>763</v>
+      </c>
+      <c r="C101" s="108" t="s">
+        <v>762</v>
+      </c>
+      <c r="D101" s="89" t="n">
         <v>0.15</v>
       </c>
-      <c r="E101" s="80" t="s">
-        <v>756</v>
-      </c>
-      <c r="F101" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G101" s="80" t="s">
-        <v>757</v>
+      <c r="E101" s="82" t="s">
+        <v>764</v>
+      </c>
+      <c r="F101" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G101" s="82" t="s">
+        <v>765</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="79" t="s">
-        <v>754</v>
-      </c>
-      <c r="B102" s="80" t="s">
-        <v>758</v>
-      </c>
-      <c r="C102" s="81" t="s">
-        <v>759</v>
-      </c>
-      <c r="D102" s="87" t="n">
+      <c r="A102" s="81" t="s">
+        <v>762</v>
+      </c>
+      <c r="B102" s="82" t="s">
+        <v>766</v>
+      </c>
+      <c r="C102" s="83" t="s">
+        <v>767</v>
+      </c>
+      <c r="D102" s="89" t="n">
         <v>0.1</v>
       </c>
-      <c r="E102" s="80" t="s">
-        <v>760</v>
-      </c>
-      <c r="F102" s="78" t="s">
-        <v>387</v>
-      </c>
-      <c r="G102" s="80" t="s">
-        <v>761</v>
+      <c r="E102" s="82" t="s">
+        <v>768</v>
+      </c>
+      <c r="F102" s="80" t="s">
+        <v>395</v>
+      </c>
+      <c r="G102" s="82" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="79" t="s">
-        <v>754</v>
-      </c>
-      <c r="B103" s="80" t="s">
+      <c r="A103" s="81" t="s">
         <v>762</v>
       </c>
-      <c r="C103" s="81" t="s">
-        <v>763</v>
-      </c>
-      <c r="D103" s="87" t="n">
+      <c r="B103" s="82" t="s">
+        <v>770</v>
+      </c>
+      <c r="C103" s="83" t="s">
+        <v>771</v>
+      </c>
+      <c r="D103" s="89" t="n">
         <v>0.2</v>
       </c>
-      <c r="E103" s="80" t="s">
-        <v>764</v>
-      </c>
-      <c r="F103" s="80" t="s">
-        <v>442</v>
-      </c>
-      <c r="G103" s="80" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="E103" s="82" t="s">
+        <v>772</v>
+      </c>
+      <c r="F103" s="82" t="s">
+        <v>450</v>
+      </c>
+      <c r="G103" s="82" t="s">
+        <v>773</v>
+      </c>
+    </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="107" t="s">
-        <v>766</v>
-      </c>
-      <c r="B106" s="107"/>
-      <c r="C106" s="107"/>
-      <c r="D106" s="107"/>
-      <c r="E106" s="107"/>
-      <c r="F106" s="107"/>
-      <c r="G106" s="107"/>
-      <c r="H106" s="107"/>
-      <c r="I106" s="107"/>
+      <c r="A106" s="109" t="s">
+        <v>774</v>
+      </c>
+      <c r="B106" s="109"/>
+      <c r="C106" s="109"/>
+      <c r="D106" s="109"/>
+      <c r="E106" s="109"/>
+      <c r="F106" s="109"/>
+      <c r="G106" s="109"/>
+      <c r="H106" s="109"/>
+      <c r="I106" s="109"/>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="108" t="s">
-        <v>767</v>
-      </c>
-      <c r="B107" s="108"/>
-      <c r="C107" s="108"/>
-      <c r="D107" s="108"/>
-      <c r="E107" s="108"/>
-      <c r="F107" s="108"/>
-      <c r="G107" s="108"/>
-      <c r="H107" s="108"/>
-      <c r="I107" s="108"/>
+      <c r="A107" s="110" t="s">
+        <v>775</v>
+      </c>
+      <c r="B107" s="110"/>
+      <c r="C107" s="110"/>
+      <c r="D107" s="110"/>
+      <c r="E107" s="110"/>
+      <c r="F107" s="110"/>
+      <c r="G107" s="110"/>
+      <c r="H107" s="110"/>
+      <c r="I107" s="110"/>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="108" t="s">
-        <v>768</v>
-      </c>
-      <c r="B108" s="108"/>
-      <c r="C108" s="108"/>
-      <c r="D108" s="108"/>
-      <c r="E108" s="108"/>
-      <c r="F108" s="108"/>
-      <c r="G108" s="108"/>
-      <c r="H108" s="108"/>
-      <c r="I108" s="108"/>
+      <c r="A108" s="110" t="s">
+        <v>776</v>
+      </c>
+      <c r="B108" s="110"/>
+      <c r="C108" s="110"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="110"/>
+      <c r="F108" s="110"/>
+      <c r="G108" s="110"/>
+      <c r="H108" s="110"/>
+      <c r="I108" s="110"/>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="108" t="s">
-        <v>769</v>
-      </c>
-      <c r="B109" s="108"/>
-      <c r="C109" s="108"/>
-      <c r="D109" s="108"/>
-      <c r="E109" s="108"/>
-      <c r="F109" s="108"/>
-      <c r="G109" s="108"/>
-      <c r="H109" s="108"/>
-      <c r="I109" s="108"/>
+      <c r="A109" s="110" t="s">
+        <v>777</v>
+      </c>
+      <c r="B109" s="110"/>
+      <c r="C109" s="110"/>
+      <c r="D109" s="110"/>
+      <c r="E109" s="110"/>
+      <c r="F109" s="110"/>
+      <c r="G109" s="110"/>
+      <c r="H109" s="110"/>
+      <c r="I109" s="110"/>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="108" t="s">
-        <v>770</v>
-      </c>
-      <c r="B110" s="108"/>
-      <c r="C110" s="108"/>
-      <c r="D110" s="108"/>
-      <c r="E110" s="108"/>
-      <c r="F110" s="108"/>
-      <c r="G110" s="108"/>
-      <c r="H110" s="108"/>
-      <c r="I110" s="108"/>
+      <c r="A110" s="110" t="s">
+        <v>778</v>
+      </c>
+      <c r="B110" s="110"/>
+      <c r="C110" s="110"/>
+      <c r="D110" s="110"/>
+      <c r="E110" s="110"/>
+      <c r="F110" s="110"/>
+      <c r="G110" s="110"/>
+      <c r="H110" s="110"/>
+      <c r="I110" s="110"/>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="108" t="s">
-        <v>771</v>
-      </c>
-      <c r="B111" s="108"/>
-      <c r="C111" s="108"/>
-      <c r="D111" s="108"/>
-      <c r="E111" s="108"/>
-      <c r="F111" s="108"/>
-      <c r="G111" s="108"/>
-      <c r="H111" s="108"/>
-      <c r="I111" s="108"/>
+      <c r="A111" s="110" t="s">
+        <v>779</v>
+      </c>
+      <c r="B111" s="110"/>
+      <c r="C111" s="110"/>
+      <c r="D111" s="110"/>
+      <c r="E111" s="110"/>
+      <c r="F111" s="110"/>
+      <c r="G111" s="110"/>
+      <c r="H111" s="110"/>
+      <c r="I111" s="110"/>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="108" t="s">
-        <v>772</v>
-      </c>
-      <c r="B112" s="108"/>
-      <c r="C112" s="108"/>
-      <c r="D112" s="108"/>
-      <c r="E112" s="108"/>
-      <c r="F112" s="108"/>
-      <c r="G112" s="108"/>
-      <c r="H112" s="108"/>
-      <c r="I112" s="108"/>
+      <c r="A112" s="110" t="s">
+        <v>780</v>
+      </c>
+      <c r="B112" s="110"/>
+      <c r="C112" s="110"/>
+      <c r="D112" s="110"/>
+      <c r="E112" s="110"/>
+      <c r="F112" s="110"/>
+      <c r="G112" s="110"/>
+      <c r="H112" s="110"/>
+      <c r="I112" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -7249,13 +8019,1255 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF6A3D9A"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="111" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="112" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="113" t="s">
+        <v>782</v>
+      </c>
+      <c r="B4" s="113" t="s">
+        <v>783</v>
+      </c>
+      <c r="C4" s="113" t="s">
+        <v>784</v>
+      </c>
+      <c r="D4" s="113" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="63" t="s">
+        <v>786</v>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>787</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63" t="s">
+        <v>789</v>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>790</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="63" t="s">
+        <v>791</v>
+      </c>
+      <c r="B7" s="63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>792</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="63" t="s">
+        <v>794</v>
+      </c>
+      <c r="B8" s="63" t="n">
+        <v>8</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>795</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="63" t="s">
+        <v>796</v>
+      </c>
+      <c r="B9" s="63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" s="63" t="s">
+        <v>797</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="63" t="s">
+        <v>798</v>
+      </c>
+      <c r="B10" s="63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C10" s="63" t="s">
+        <v>318</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="112" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="113" t="s">
+        <v>679</v>
+      </c>
+      <c r="B13" s="113" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="113" t="s">
+        <v>800</v>
+      </c>
+      <c r="D13" s="113" t="s">
+        <v>801</v>
+      </c>
+      <c r="E13" s="113" t="s">
+        <v>246</v>
+      </c>
+      <c r="F13" s="113" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="63" t="s">
+        <v>802</v>
+      </c>
+      <c r="B14" s="63" t="s">
+        <v>803</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>804</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>805</v>
+      </c>
+      <c r="E14" s="63" t="s">
+        <v>804</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="63" t="s">
+        <v>806</v>
+      </c>
+      <c r="B15" s="63" t="n">
+        <v>64</v>
+      </c>
+      <c r="C15" s="63" t="s">
+        <v>807</v>
+      </c>
+      <c r="D15" s="63" t="n">
+        <v>154</v>
+      </c>
+      <c r="E15" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="63" t="s">
+        <v>808</v>
+      </c>
+      <c r="B16" s="63" t="s">
+        <v>809</v>
+      </c>
+      <c r="C16" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>810</v>
+      </c>
+      <c r="E16" s="63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="63" t="s">
+        <v>811</v>
+      </c>
+      <c r="B17" s="63" t="s">
+        <v>804</v>
+      </c>
+      <c r="C17" s="63" t="s">
+        <v>812</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>813</v>
+      </c>
+      <c r="E17" s="63" t="s">
+        <v>804</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="63" t="s">
+        <v>814</v>
+      </c>
+      <c r="B18" s="63" t="s">
+        <v>815</v>
+      </c>
+      <c r="C18" s="63" t="s">
+        <v>816</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>816</v>
+      </c>
+      <c r="E18" s="63" t="s">
+        <v>816</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="63" t="s">
+        <v>818</v>
+      </c>
+      <c r="B19" s="63" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C19" s="63" t="s">
+        <v>816</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>819</v>
+      </c>
+      <c r="E19" s="63" t="s">
+        <v>820</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>820</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FFCC0000"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="111" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="112" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="114" t="s">
+        <v>823</v>
+      </c>
+      <c r="B4" s="114" t="s">
+        <v>824</v>
+      </c>
+      <c r="C4" s="114" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="63" t="s">
+        <v>825</v>
+      </c>
+      <c r="B5" s="63" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" s="63" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="63" t="s">
+        <v>827</v>
+      </c>
+      <c r="B6" s="63" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="63" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="63" t="s">
+        <v>829</v>
+      </c>
+      <c r="B7" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="63" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="63" t="s">
+        <v>830</v>
+      </c>
+      <c r="B8" s="63" t="s">
+        <v>831</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="112" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="115" t="s">
+        <v>833</v>
+      </c>
+      <c r="B11" s="115" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="115" t="s">
+        <v>834</v>
+      </c>
+      <c r="D11" s="115" t="s">
+        <v>835</v>
+      </c>
+      <c r="E11" s="115" t="s">
+        <v>836</v>
+      </c>
+      <c r="F11" s="115" t="s">
+        <v>264</v>
+      </c>
+      <c r="G11" s="115" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="116" t="s">
+        <v>838</v>
+      </c>
+      <c r="B12" s="116" t="s">
+        <v>839</v>
+      </c>
+      <c r="C12" s="116" t="s">
+        <v>840</v>
+      </c>
+      <c r="D12" s="116" t="s">
+        <v>841</v>
+      </c>
+      <c r="E12" s="117" t="s">
+        <v>842</v>
+      </c>
+      <c r="F12" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G12" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="116" t="s">
+        <v>844</v>
+      </c>
+      <c r="B13" s="116" t="s">
+        <v>845</v>
+      </c>
+      <c r="C13" s="116" t="s">
+        <v>846</v>
+      </c>
+      <c r="D13" s="116" t="s">
+        <v>847</v>
+      </c>
+      <c r="E13" s="117" t="s">
+        <v>848</v>
+      </c>
+      <c r="F13" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G13" s="118" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="116" t="s">
+        <v>849</v>
+      </c>
+      <c r="B14" s="116" t="s">
+        <v>850</v>
+      </c>
+      <c r="C14" s="116" t="s">
+        <v>851</v>
+      </c>
+      <c r="D14" s="116" t="s">
+        <v>852</v>
+      </c>
+      <c r="E14" s="117" t="s">
+        <v>853</v>
+      </c>
+      <c r="F14" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G14" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="116" t="s">
+        <v>854</v>
+      </c>
+      <c r="B15" s="116" t="s">
+        <v>855</v>
+      </c>
+      <c r="C15" s="116" t="s">
+        <v>856</v>
+      </c>
+      <c r="D15" s="116" t="s">
+        <v>857</v>
+      </c>
+      <c r="E15" s="117" t="s">
+        <v>858</v>
+      </c>
+      <c r="F15" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G15" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="116" t="s">
+        <v>859</v>
+      </c>
+      <c r="B16" s="116" t="s">
+        <v>860</v>
+      </c>
+      <c r="C16" s="116" t="s">
+        <v>861</v>
+      </c>
+      <c r="D16" s="116" t="s">
+        <v>862</v>
+      </c>
+      <c r="E16" s="117" t="s">
+        <v>863</v>
+      </c>
+      <c r="F16" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G16" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="116" t="s">
+        <v>864</v>
+      </c>
+      <c r="B17" s="116" t="s">
+        <v>865</v>
+      </c>
+      <c r="C17" s="116" t="s">
+        <v>866</v>
+      </c>
+      <c r="D17" s="116" t="s">
+        <v>867</v>
+      </c>
+      <c r="E17" s="117" t="s">
+        <v>868</v>
+      </c>
+      <c r="F17" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="G17" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="116" t="s">
+        <v>869</v>
+      </c>
+      <c r="B18" s="116" t="s">
+        <v>870</v>
+      </c>
+      <c r="C18" s="116" t="s">
+        <v>871</v>
+      </c>
+      <c r="D18" s="116" t="s">
+        <v>867</v>
+      </c>
+      <c r="E18" s="117" t="s">
+        <v>872</v>
+      </c>
+      <c r="F18" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G18" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="116" t="s">
+        <v>873</v>
+      </c>
+      <c r="B19" s="116" t="s">
+        <v>874</v>
+      </c>
+      <c r="C19" s="116" t="s">
+        <v>875</v>
+      </c>
+      <c r="D19" s="116" t="s">
+        <v>876</v>
+      </c>
+      <c r="E19" s="117" t="s">
+        <v>877</v>
+      </c>
+      <c r="F19" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G19" s="118" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="116" t="s">
+        <v>878</v>
+      </c>
+      <c r="B20" s="116" t="s">
+        <v>879</v>
+      </c>
+      <c r="C20" s="116" t="s">
+        <v>880</v>
+      </c>
+      <c r="D20" s="116" t="s">
+        <v>876</v>
+      </c>
+      <c r="E20" s="117" t="s">
+        <v>881</v>
+      </c>
+      <c r="F20" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G20" s="116" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="116" t="s">
+        <v>882</v>
+      </c>
+      <c r="B21" s="116" t="s">
+        <v>883</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>884</v>
+      </c>
+      <c r="D21" s="116" t="s">
+        <v>885</v>
+      </c>
+      <c r="E21" s="119" t="s">
+        <v>394</v>
+      </c>
+      <c r="F21" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G21" s="118" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="116" t="s">
+        <v>886</v>
+      </c>
+      <c r="B22" s="116" t="s">
+        <v>887</v>
+      </c>
+      <c r="C22" s="116" t="s">
+        <v>888</v>
+      </c>
+      <c r="D22" s="116" t="s">
+        <v>889</v>
+      </c>
+      <c r="E22" s="119" t="s">
+        <v>394</v>
+      </c>
+      <c r="F22" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="G22" s="118" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="116" t="s">
+        <v>890</v>
+      </c>
+      <c r="B23" s="116" t="s">
+        <v>891</v>
+      </c>
+      <c r="C23" s="116" t="s">
+        <v>884</v>
+      </c>
+      <c r="D23" s="116" t="s">
+        <v>857</v>
+      </c>
+      <c r="E23" s="119" t="s">
+        <v>394</v>
+      </c>
+      <c r="F23" s="116" t="s">
+        <v>793</v>
+      </c>
+      <c r="G23" s="118" t="s">
+        <v>395</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF2E75B6"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="111" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="112" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="120" t="s">
+        <v>894</v>
+      </c>
+      <c r="B4" s="120" t="s">
+        <v>895</v>
+      </c>
+      <c r="C4" s="120" t="s">
+        <v>896</v>
+      </c>
+      <c r="D4" s="120" t="s">
+        <v>897</v>
+      </c>
+      <c r="E4" s="120" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="116" t="s">
+        <v>899</v>
+      </c>
+      <c r="B5" s="116" t="s">
+        <v>900</v>
+      </c>
+      <c r="C5" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="116" t="s">
+        <v>901</v>
+      </c>
+      <c r="E5" s="121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="116" t="s">
+        <v>899</v>
+      </c>
+      <c r="B6" s="116" t="s">
+        <v>903</v>
+      </c>
+      <c r="C6" s="116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="116" t="s">
+        <v>904</v>
+      </c>
+      <c r="E6" s="122" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="116" t="s">
+        <v>782</v>
+      </c>
+      <c r="B7" s="116" t="s">
+        <v>906</v>
+      </c>
+      <c r="C7" s="116" t="n">
+        <v>9</v>
+      </c>
+      <c r="D7" s="116" t="s">
+        <v>907</v>
+      </c>
+      <c r="E7" s="121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="116" t="s">
+        <v>782</v>
+      </c>
+      <c r="B8" s="116" t="s">
+        <v>796</v>
+      </c>
+      <c r="C8" s="116" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" s="116" t="s">
+        <v>908</v>
+      </c>
+      <c r="E8" s="122" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="116" t="s">
+        <v>909</v>
+      </c>
+      <c r="B9" s="116" t="s">
+        <v>910</v>
+      </c>
+      <c r="C9" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D9" s="116" t="s">
+        <v>911</v>
+      </c>
+      <c r="E9" s="123" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="116" t="s">
+        <v>909</v>
+      </c>
+      <c r="B10" s="116" t="s">
+        <v>913</v>
+      </c>
+      <c r="C10" s="116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="116" t="s">
+        <v>904</v>
+      </c>
+      <c r="E10" s="122" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="116" t="s">
+        <v>914</v>
+      </c>
+      <c r="B11" s="116" t="s">
+        <v>915</v>
+      </c>
+      <c r="C11" s="116" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="116" t="s">
+        <v>904</v>
+      </c>
+      <c r="E11" s="123" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="116" t="s">
+        <v>914</v>
+      </c>
+      <c r="B12" s="116" t="s">
+        <v>917</v>
+      </c>
+      <c r="C12" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" s="116" t="s">
+        <v>908</v>
+      </c>
+      <c r="E12" s="123" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="116" t="s">
+        <v>914</v>
+      </c>
+      <c r="B13" s="116" t="s">
+        <v>919</v>
+      </c>
+      <c r="C13" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="116" t="s">
+        <v>920</v>
+      </c>
+      <c r="E13" s="121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="116" t="s">
+        <v>914</v>
+      </c>
+      <c r="B14" s="116" t="s">
+        <v>921</v>
+      </c>
+      <c r="C14" s="116" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="116" t="s">
+        <v>904</v>
+      </c>
+      <c r="E14" s="122" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="116" t="s">
+        <v>922</v>
+      </c>
+      <c r="B15" s="116" t="s">
+        <v>923</v>
+      </c>
+      <c r="C15" s="116" t="n">
+        <v>9</v>
+      </c>
+      <c r="D15" s="116" t="s">
+        <v>924</v>
+      </c>
+      <c r="E15" s="121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="116" t="s">
+        <v>922</v>
+      </c>
+      <c r="B16" s="116" t="s">
+        <v>925</v>
+      </c>
+      <c r="C16" s="116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="116" t="s">
+        <v>904</v>
+      </c>
+      <c r="E16" s="122" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="116" t="s">
+        <v>922</v>
+      </c>
+      <c r="B17" s="116" t="s">
+        <v>926</v>
+      </c>
+      <c r="C17" s="116" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" s="116" t="s">
+        <v>907</v>
+      </c>
+      <c r="E17" s="121" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="112" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="120" t="s">
+        <v>928</v>
+      </c>
+      <c r="B20" s="120" t="s">
+        <v>784</v>
+      </c>
+      <c r="C20" s="120" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="120" t="s">
+        <v>929</v>
+      </c>
+      <c r="E20" s="120" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="116" t="s">
+        <v>931</v>
+      </c>
+      <c r="B21" s="116" t="s">
+        <v>932</v>
+      </c>
+      <c r="C21" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="D21" s="116" t="s">
+        <v>348</v>
+      </c>
+      <c r="E21" s="116" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="116" t="s">
+        <v>934</v>
+      </c>
+      <c r="B22" s="116" t="s">
+        <v>935</v>
+      </c>
+      <c r="C22" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="116" t="s">
+        <v>335</v>
+      </c>
+      <c r="E22" s="116" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="116" t="s">
+        <v>937</v>
+      </c>
+      <c r="B23" s="116" t="s">
+        <v>938</v>
+      </c>
+      <c r="C23" s="116" t="s">
+        <v>939</v>
+      </c>
+      <c r="D23" s="116" t="s">
+        <v>338</v>
+      </c>
+      <c r="E23" s="116" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="116" t="s">
+        <v>941</v>
+      </c>
+      <c r="B24" s="116" t="s">
+        <v>942</v>
+      </c>
+      <c r="C24" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="D24" s="116" t="s">
+        <v>943</v>
+      </c>
+      <c r="E24" s="116" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="116" t="s">
+        <v>945</v>
+      </c>
+      <c r="B25" s="116" t="s">
+        <v>946</v>
+      </c>
+      <c r="C25" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="D25" s="116" t="s">
+        <v>947</v>
+      </c>
+      <c r="E25" s="116" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="116" t="s">
+        <v>949</v>
+      </c>
+      <c r="B26" s="116" t="s">
+        <v>950</v>
+      </c>
+      <c r="C26" s="116" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="116" t="s">
+        <v>348</v>
+      </c>
+      <c r="E26" s="116" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="112" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="120" t="s">
+        <v>953</v>
+      </c>
+      <c r="B29" s="120" t="s">
+        <v>245</v>
+      </c>
+      <c r="C29" s="120" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="120" t="s">
+        <v>800</v>
+      </c>
+      <c r="E29" s="120" t="s">
+        <v>954</v>
+      </c>
+      <c r="F29" s="120" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="62" t="s">
+        <v>956</v>
+      </c>
+      <c r="B30" s="124" t="n">
+        <v>7</v>
+      </c>
+      <c r="C30" s="125" t="n">
+        <v>9</v>
+      </c>
+      <c r="D30" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="E30" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="F30" s="124" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="62" t="s">
+        <v>957</v>
+      </c>
+      <c r="B31" s="125" t="n">
+        <v>8</v>
+      </c>
+      <c r="C31" s="124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="E31" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="F31" s="124" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="62" t="s">
+        <v>958</v>
+      </c>
+      <c r="B32" s="125" t="n">
+        <v>8</v>
+      </c>
+      <c r="C32" s="127" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="125" t="n">
+        <v>9</v>
+      </c>
+      <c r="E32" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="F32" s="127" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="62" t="s">
+        <v>201</v>
+      </c>
+      <c r="B33" s="125" t="n">
+        <v>9</v>
+      </c>
+      <c r="C33" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="E33" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="F33" s="127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="62" t="s">
+        <v>424</v>
+      </c>
+      <c r="B34" s="125" t="n">
+        <v>9</v>
+      </c>
+      <c r="C34" s="124" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="E34" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="F34" s="127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="62" t="s">
+        <v>959</v>
+      </c>
+      <c r="B35" s="125" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="124" t="n">
+        <v>7</v>
+      </c>
+      <c r="E35" s="127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="62" t="s">
+        <v>960</v>
+      </c>
+      <c r="B36" s="124" t="n">
+        <v>6</v>
+      </c>
+      <c r="C36" s="127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="E36" s="126" t="s">
+        <v>831</v>
+      </c>
+      <c r="F36" s="127" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="35"/>
@@ -7272,7 +9284,6 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>51</v>
@@ -7505,7 +9516,6 @@
         <v>31190</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>68</v>
@@ -7712,8 +9722,6 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
         <v>75</v>
@@ -7939,15 +9947,6 @@
         <v>401</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7982,7 +9981,6 @@
         <v>85</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>86</v>
@@ -8230,7 +10228,6 @@
         <v>0.193454670029791</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>93</v>
@@ -8368,7 +10365,6 @@
         <v>0.245</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
         <v>97</v>
@@ -8547,7 +10543,6 @@
         <v>-34823.124</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
         <v>102</v>
@@ -8630,7 +10625,6 @@
         <v>0.147</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>104</v>
@@ -8745,7 +10739,6 @@
         <v>-9348.24348</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
         <v>107</v>
@@ -8828,7 +10821,6 @@
         <v>1419548.084</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
         <v>109</v>
@@ -8945,7 +10937,6 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>113</v>
@@ -9193,7 +11184,6 @@
         <v>132800</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>121</v>
@@ -9304,7 +11294,6 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30" t="s">
         <v>125</v>
@@ -9346,7 +11335,6 @@
         <v>198200</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>126</v>
@@ -9498,7 +11486,6 @@
         <v>53500</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
         <v>131</v>
@@ -9577,7 +11564,6 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30" t="s">
         <v>134</v>
@@ -9619,7 +11605,6 @@
         <v>64800</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
         <v>135</v>
@@ -9675,7 +11660,6 @@
         <v>133400</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="34" t="s">
         <v>137</v>
@@ -9751,7 +11735,6 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>139</v>
@@ -9949,7 +11932,6 @@
         <v>-3167.945</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>145</v>
@@ -9991,7 +11973,6 @@
         <v>56621.34152</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
         <v>146</v>
@@ -10079,7 +12060,6 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>149</v>
@@ -10121,7 +12101,6 @@
         <v>-500</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30" t="s">
         <v>150</v>
@@ -10279,7 +12258,6 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>154</v>
@@ -10500,7 +12478,6 @@
         <v>0.119999776619924</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
         <v>160</v>
@@ -10686,7 +12663,6 @@
         <v>165</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
         <v>166</v>
@@ -10765,8 +12741,6 @@
         <v>3334.5039445</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>174</v>
@@ -10877,7 +12851,6 @@
         <v>4.11160516886318E-017</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
         <v>178</v>
@@ -10922,7 +12895,6 @@
         <v>3.45440059019227E-020</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
         <v>183</v>
@@ -11040,7 +13012,6 @@
         <v>191</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
         <v>192</v>
@@ -11187,7 +13158,6 @@
         <v>214</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
         <v>215</v>
@@ -11206,7 +13176,6 @@
         <v>665</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
         <v>188</v>
@@ -11242,7 +13211,7 @@
     <tabColor rgb="FFED7D31"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -11257,7 +13226,6 @@
         <v>218</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
         <v>219</v>
@@ -11388,7 +13356,6 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="30" t="s">
         <v>234</v>
@@ -11410,10 +13377,6 @@
         <v>16157.3333333333</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
